--- a/Lista_Precios_Base.xlsx
+++ b/Lista_Precios_Base.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CodeBrew/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\OneDrive - Alsea - Europa\Nube_EnriqueCesar\GitHub\CodeBrew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="385" documentId="13_ncr:1_{7FC43AD6-D4C1-4CD2-998E-2CAF80AA025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCA57615-636F-4E49-8280-49E3C1C17B9C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71BEC85-4C4D-4198-A748-8E3A4E39F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3777" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3774" uniqueCount="1209">
   <si>
     <t>WC26Stan20IceF</t>
   </si>
@@ -3696,12 +3696,6 @@
   </si>
   <si>
     <t>WC26Gl20Silicone</t>
-  </si>
-  <si>
-    <t>CCUP 16OZ SS HAPPY FARM CHILLAX PONY AND FLOWERS</t>
-  </si>
-  <si>
-    <t>SII26SSCC16Pony</t>
   </si>
   <si>
     <t>WTBL 16OZ SS HAPPY JUMPING PONY AND FLOWERS</t>
@@ -3895,8 +3889,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G113" totalsRowShown="0">
-  <autoFilter ref="A1:G113" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G112" totalsRowShown="0">
+  <autoFilter ref="A1:G112" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3FD2C0CF-4866-4870-AD33-E904DA8BA849}" name="SKU INTL"/>
     <tableColumn id="2" xr3:uid="{39846DA6-B590-4416-838E-B359114E50F9}" name="CÓDIGO DIA"/>
@@ -4256,7 +4250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8718E42-507B-44AF-801B-0B0250CAF160}">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" bestFit="1" customWidth="1"/>
@@ -4292,10 +4286,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>11176587</v>
+        <v>1176593</v>
       </c>
       <c r="B2">
-        <v>16720</v>
+        <v>16793</v>
       </c>
       <c r="C2" t="s">
         <v>1201</v>
@@ -4307,7 +4301,7 @@
         <v>1202</v>
       </c>
       <c r="F2">
-        <v>50740</v>
+        <v>50741</v>
       </c>
       <c r="G2">
         <v>649</v>
@@ -4315,10 +4309,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1176593</v>
+        <v>11176592</v>
       </c>
       <c r="B3">
-        <v>16793</v>
+        <v>16779</v>
       </c>
       <c r="C3" t="s">
         <v>1203</v>
@@ -4330,7 +4324,7 @@
         <v>1204</v>
       </c>
       <c r="F3">
-        <v>50741</v>
+        <v>50742</v>
       </c>
       <c r="G3">
         <v>649</v>
@@ -4338,10 +4332,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>11176592</v>
+        <v>11176586</v>
       </c>
       <c r="B4">
-        <v>16779</v>
+        <v>16719</v>
       </c>
       <c r="C4" t="s">
         <v>1205</v>
@@ -4353,18 +4347,18 @@
         <v>1206</v>
       </c>
       <c r="F4">
-        <v>50742</v>
+        <v>50743</v>
       </c>
       <c r="G4">
-        <v>649</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>11176586</v>
+        <v>11176597</v>
       </c>
       <c r="B5">
-        <v>16719</v>
+        <v>16784</v>
       </c>
       <c r="C5" t="s">
         <v>1207</v>
@@ -4376,76 +4370,76 @@
         <v>1208</v>
       </c>
       <c r="F5">
-        <v>50743</v>
+        <v>50745</v>
       </c>
       <c r="G5">
-        <v>669</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>11176597</v>
+        <v>11178956</v>
       </c>
       <c r="B6">
-        <v>16784</v>
+        <v>16916</v>
       </c>
       <c r="C6" t="s">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="D6" t="s">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="E6" t="s">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="F6">
-        <v>50745</v>
+        <v>50735</v>
       </c>
       <c r="G6">
-        <v>369</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>11178956</v>
+        <v>11178933</v>
       </c>
       <c r="B7">
-        <v>16916</v>
+        <v>16881</v>
       </c>
       <c r="C7" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D7" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E7" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F7">
-        <v>50735</v>
+        <v>50736</v>
       </c>
       <c r="G7">
-        <v>999</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>11178933</v>
+        <v>11178934</v>
       </c>
       <c r="B8">
-        <v>16881</v>
+        <v>16884</v>
       </c>
       <c r="C8" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D8" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E8" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="F8">
-        <v>50736</v>
+        <v>50737</v>
       </c>
       <c r="G8">
         <v>529</v>
@@ -4453,505 +4447,505 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>11178934</v>
+        <v>11178935</v>
       </c>
       <c r="B9">
-        <v>16884</v>
+        <v>16920</v>
       </c>
       <c r="C9" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D9" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="E9" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="F9">
-        <v>50737</v>
+        <v>50738</v>
       </c>
       <c r="G9">
-        <v>529</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>11178935</v>
+        <v>11178941</v>
       </c>
       <c r="B10">
-        <v>16920</v>
+        <v>16900</v>
       </c>
       <c r="C10" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D10" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="E10" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="F10">
-        <v>50738</v>
+        <v>50739</v>
       </c>
       <c r="G10">
-        <v>459</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>11178941</v>
+        <v>11178917</v>
       </c>
       <c r="B11">
-        <v>16900</v>
+        <v>16921</v>
       </c>
       <c r="C11" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D11" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="E11" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="F11">
-        <v>50739</v>
+        <v>58808</v>
       </c>
       <c r="G11">
-        <v>649</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11178917</v>
+        <v>11178969</v>
       </c>
       <c r="B12">
-        <v>16921</v>
+        <v>16910</v>
       </c>
       <c r="C12" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D12" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E12" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="F12">
-        <v>58808</v>
+        <v>58827</v>
       </c>
       <c r="G12">
-        <v>479</v>
+        <v>679</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11178969</v>
+        <v>11178918</v>
       </c>
       <c r="B13">
-        <v>16910</v>
+        <v>16923</v>
       </c>
       <c r="C13" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D13" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="E13" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F13">
-        <v>58827</v>
+        <v>58832</v>
       </c>
       <c r="G13">
-        <v>679</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11178918</v>
+        <v>11178946</v>
       </c>
       <c r="B14">
-        <v>16923</v>
+        <v>16913</v>
       </c>
       <c r="C14" t="s">
-        <v>1199</v>
+        <v>1175</v>
       </c>
       <c r="D14" t="s">
-        <v>1200</v>
+        <v>1176</v>
       </c>
       <c r="E14" t="s">
-        <v>1200</v>
+        <v>1176</v>
       </c>
       <c r="F14">
-        <v>58832</v>
+        <v>58814</v>
       </c>
       <c r="G14">
-        <v>489</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>11178946</v>
+        <v>11178973</v>
       </c>
       <c r="B15">
-        <v>16913</v>
+        <v>16925</v>
       </c>
       <c r="C15" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="D15" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="E15" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="F15">
-        <v>58814</v>
+        <v>58815</v>
       </c>
       <c r="G15">
-        <v>689</v>
+        <v>649</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11178973</v>
+        <v>11178959</v>
       </c>
       <c r="B16">
-        <v>16925</v>
+        <v>16897</v>
       </c>
       <c r="C16" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D16" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="E16" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="F16">
-        <v>58815</v>
+        <v>58816</v>
       </c>
       <c r="G16">
-        <v>649</v>
+        <v>659</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>11178959</v>
+        <v>11178928</v>
       </c>
       <c r="B17">
-        <v>16897</v>
+        <v>16880</v>
       </c>
       <c r="C17" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D17" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="E17" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="F17">
-        <v>58816</v>
+        <v>58817</v>
       </c>
       <c r="G17">
-        <v>659</v>
+        <v>549</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>11178928</v>
+        <v>11178965</v>
       </c>
       <c r="B18">
-        <v>16880</v>
+        <v>16904</v>
       </c>
       <c r="C18" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D18" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="E18" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="F18">
-        <v>58817</v>
+        <v>58818</v>
       </c>
       <c r="G18">
-        <v>549</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>11178965</v>
+        <v>11178937</v>
       </c>
       <c r="B19">
-        <v>16904</v>
+        <v>16901</v>
       </c>
       <c r="C19" t="s">
-        <v>1183</v>
+        <v>1052</v>
       </c>
       <c r="D19" t="s">
-        <v>1184</v>
+        <v>1053</v>
       </c>
       <c r="E19" t="s">
-        <v>1184</v>
+        <v>1053</v>
       </c>
       <c r="F19">
-        <v>58818</v>
+        <v>58819</v>
       </c>
       <c r="G19">
-        <v>535</v>
+        <v>739</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>11178937</v>
+        <v>11178948</v>
       </c>
       <c r="B20">
-        <v>16901</v>
+        <v>16915</v>
       </c>
       <c r="C20" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="D20" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="E20" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F20">
-        <v>58819</v>
+        <v>58821</v>
       </c>
       <c r="G20">
-        <v>739</v>
+        <v>899</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>11178948</v>
+      <c r="A21" t="s">
+        <v>1</v>
       </c>
       <c r="B21">
-        <v>16915</v>
+        <v>16971</v>
       </c>
       <c r="C21" t="s">
-        <v>1054</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="E21" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F21">
-        <v>58821</v>
+        <v>58846</v>
       </c>
       <c r="G21">
-        <v>899</v>
+        <v>869</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>1</v>
+      <c r="A22">
+        <v>11178944</v>
       </c>
       <c r="B22">
-        <v>16971</v>
+        <v>16909</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>1056</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>1056</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>58846</v>
+        <v>58826</v>
       </c>
       <c r="G22">
-        <v>869</v>
+        <v>679</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11178944</v>
+        <v>11178952</v>
       </c>
       <c r="B23">
-        <v>16909</v>
+        <v>16875</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F23">
-        <v>58826</v>
+        <v>58828</v>
       </c>
       <c r="G23">
-        <v>679</v>
+        <v>689</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11178952</v>
+        <v>11178971</v>
       </c>
       <c r="B24">
-        <v>16875</v>
+        <v>16911</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>58828</v>
+        <v>58829</v>
       </c>
       <c r="G24">
-        <v>689</v>
+        <v>679</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11178971</v>
+        <v>11178920</v>
       </c>
       <c r="B25">
-        <v>16911</v>
+        <v>16902</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F25">
-        <v>58829</v>
+        <v>58830</v>
       </c>
       <c r="G25">
-        <v>679</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>11178920</v>
+        <v>11178922</v>
       </c>
       <c r="B26">
-        <v>16902</v>
+        <v>16879</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>58830</v>
+        <v>58831</v>
       </c>
       <c r="G26">
-        <v>369</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11178922</v>
+        <v>11178945</v>
       </c>
       <c r="B27">
-        <v>16879</v>
+        <v>16924</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>58831</v>
+        <v>58835</v>
       </c>
       <c r="G27">
-        <v>349</v>
+        <v>899</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>11178945</v>
+        <v>11179005</v>
       </c>
       <c r="B28">
-        <v>16924</v>
+        <v>16906</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>58835</v>
+        <v>58823</v>
       </c>
       <c r="G28">
-        <v>899</v>
+        <v>889</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11179005</v>
+        <v>11178930</v>
       </c>
       <c r="B29">
-        <v>16906</v>
+        <v>16882</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>58823</v>
+        <v>58824</v>
       </c>
       <c r="G29">
-        <v>889</v>
+        <v>535</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>11178930</v>
+        <v>11178966</v>
       </c>
       <c r="B30">
-        <v>16882</v>
+        <v>16905</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F30">
-        <v>58824</v>
+        <v>58825</v>
       </c>
       <c r="G30">
         <v>535</v>
@@ -4959,94 +4953,94 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11178966</v>
+        <v>11187369</v>
       </c>
       <c r="B31">
-        <v>16905</v>
+        <v>16908</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>58825</v>
+        <v>58848</v>
       </c>
       <c r="G31">
-        <v>535</v>
+        <v>869</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11187369</v>
+        <v>11187370</v>
       </c>
       <c r="B32">
-        <v>16908</v>
+        <v>16958</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F32">
-        <v>58848</v>
+        <v>58838</v>
       </c>
       <c r="G32">
-        <v>869</v>
+        <v>679</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11187370</v>
+        <v>11187372</v>
       </c>
       <c r="B33">
-        <v>16958</v>
+        <v>16959</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F33">
-        <v>58838</v>
+        <v>58839</v>
       </c>
       <c r="G33">
-        <v>679</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>11187372</v>
+      <c r="A34" t="s">
+        <v>1</v>
       </c>
       <c r="B34">
-        <v>16959</v>
+        <v>16978</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>58839</v>
+        <v>58836</v>
       </c>
       <c r="G34">
-        <v>369</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -5054,22 +5048,22 @@
         <v>1</v>
       </c>
       <c r="B35">
-        <v>16978</v>
+        <v>16955</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F35">
-        <v>58836</v>
+        <v>58840</v>
       </c>
       <c r="G35">
-        <v>189</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -5080,88 +5074,88 @@
         <v>16955</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F36">
-        <v>58840</v>
+        <v>58842</v>
       </c>
       <c r="G36">
         <v>1099</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>1</v>
+      <c r="A37">
+        <v>11178949</v>
       </c>
       <c r="B37">
-        <v>16955</v>
+        <v>16912</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F37">
-        <v>58842</v>
+        <v>58822</v>
       </c>
       <c r="G37">
-        <v>1099</v>
+        <v>679</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>11178949</v>
+        <v>11178957</v>
       </c>
       <c r="B38">
-        <v>16912</v>
+        <v>16919</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F38">
-        <v>58822</v>
+        <v>58820</v>
       </c>
       <c r="G38">
-        <v>679</v>
+        <v>999</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>11178957</v>
+      <c r="A39" t="s">
+        <v>1</v>
       </c>
       <c r="B39">
-        <v>16919</v>
+        <v>16780</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F39">
-        <v>58820</v>
+        <v>58753</v>
       </c>
       <c r="G39">
-        <v>999</v>
+        <v>689</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -5169,19 +5163,19 @@
         <v>1</v>
       </c>
       <c r="B40">
-        <v>16780</v>
+        <v>16781</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F40">
-        <v>58753</v>
+        <v>58755</v>
       </c>
       <c r="G40">
         <v>689</v>
@@ -5192,338 +5186,335 @@
         <v>1</v>
       </c>
       <c r="B41">
-        <v>16781</v>
+        <v>16721</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F41">
-        <v>58755</v>
+        <v>58757</v>
       </c>
       <c r="G41">
-        <v>689</v>
+        <v>649</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>1</v>
+      <c r="A42">
+        <v>11179003</v>
       </c>
       <c r="B42">
-        <v>16721</v>
+        <v>16885</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F42">
-        <v>58757</v>
+        <v>58812</v>
       </c>
       <c r="G42">
-        <v>649</v>
+        <v>499</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>11179003</v>
+        <v>11179004</v>
       </c>
       <c r="B43">
-        <v>16885</v>
+        <v>16899</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F43">
-        <v>58812</v>
+        <v>58813</v>
       </c>
       <c r="G43">
-        <v>499</v>
+        <v>699</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>11179004</v>
+        <v>11178954</v>
       </c>
       <c r="B44">
-        <v>16899</v>
+        <v>16877</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F44">
-        <v>58813</v>
+        <v>58777</v>
       </c>
       <c r="G44">
-        <v>699</v>
+        <v>719</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>11178954</v>
+        <v>11178943</v>
       </c>
       <c r="B45">
-        <v>16877</v>
+        <v>16918</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F45">
-        <v>58777</v>
+        <v>58802</v>
       </c>
       <c r="G45">
-        <v>719</v>
+        <v>689</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>11178943</v>
+        <v>11178970</v>
       </c>
       <c r="B46">
-        <v>16918</v>
+        <v>16896</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F46">
-        <v>58802</v>
+        <v>58803</v>
       </c>
       <c r="G46">
-        <v>689</v>
+        <v>699</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>11178970</v>
+        <v>11178953</v>
       </c>
       <c r="B47">
-        <v>16896</v>
+        <v>16876</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F47">
-        <v>58803</v>
+        <v>58804</v>
       </c>
       <c r="G47">
-        <v>699</v>
+        <v>689</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>11178953</v>
+        <v>11178921</v>
       </c>
       <c r="B48">
-        <v>16876</v>
+        <v>16878</v>
       </c>
       <c r="C48" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E48" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F48">
-        <v>58804</v>
+        <v>58805</v>
       </c>
       <c r="G48">
-        <v>689</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>11178921</v>
+        <v>11178926</v>
       </c>
       <c r="B49">
-        <v>16878</v>
+        <v>16903</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E49" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F49">
-        <v>58805</v>
+        <v>58806</v>
       </c>
       <c r="G49">
-        <v>349</v>
+        <v>529</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>11178926</v>
+        <v>11178964</v>
       </c>
       <c r="B50">
-        <v>16903</v>
+        <v>16883</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F50">
-        <v>58806</v>
+        <v>58807</v>
       </c>
       <c r="G50">
-        <v>529</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>11178964</v>
+        <v>11178972</v>
       </c>
       <c r="B51">
-        <v>16883</v>
+        <v>16917</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F51">
-        <v>58807</v>
+        <v>58809</v>
       </c>
       <c r="G51">
-        <v>249</v>
+        <v>889</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>11178972</v>
+        <v>11178938</v>
       </c>
       <c r="B52">
-        <v>16917</v>
+        <v>16898</v>
       </c>
       <c r="C52" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E52" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F52">
-        <v>58809</v>
+        <v>58810</v>
       </c>
       <c r="G52">
-        <v>889</v>
+        <v>599</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>11178938</v>
+        <v>11178919</v>
       </c>
       <c r="B53">
-        <v>16898</v>
+        <v>16922</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E53" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F53">
-        <v>58810</v>
+        <v>58811</v>
       </c>
       <c r="G53">
-        <v>599</v>
+        <v>439</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>11178919</v>
+        <v>11176705</v>
       </c>
       <c r="B54">
-        <v>16922</v>
+        <v>16678</v>
       </c>
       <c r="C54" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E54" t="s">
-        <v>73</v>
-      </c>
-      <c r="F54">
-        <v>58811</v>
-      </c>
-      <c r="G54">
-        <v>439</v>
+        <v>75</v>
+      </c>
+      <c r="F54" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>11176705</v>
+        <v>11176712</v>
       </c>
       <c r="B55">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="C55" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D55" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E55" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F55" t="s">
         <v>76</v>
@@ -5531,45 +5522,48 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>11176712</v>
+        <v>11178947</v>
       </c>
       <c r="B56">
-        <v>16679</v>
+        <v>16914</v>
       </c>
       <c r="C56" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D56" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
-      </c>
-      <c r="F56" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="F56">
+        <v>58795</v>
+      </c>
+      <c r="G56">
+        <v>899</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>11178947</v>
+      <c r="A57" t="s">
+        <v>1</v>
       </c>
       <c r="B57">
-        <v>16914</v>
+        <v>16531</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D57" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E57" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F57">
-        <v>58795</v>
+        <v>58769</v>
       </c>
       <c r="G57">
-        <v>899</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -5583,13 +5577,13 @@
         <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E58" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F58">
-        <v>58769</v>
+        <v>58775</v>
       </c>
       <c r="G58">
         <v>1099</v>
@@ -5600,22 +5594,22 @@
         <v>1</v>
       </c>
       <c r="B59">
-        <v>16531</v>
+        <v>16532</v>
       </c>
       <c r="C59" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D59" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E59" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F59">
-        <v>58775</v>
+        <v>58771</v>
       </c>
       <c r="G59">
-        <v>1099</v>
+        <v>999</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -5629,522 +5623,522 @@
         <v>84</v>
       </c>
       <c r="D60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F60">
-        <v>58771</v>
+        <v>58773</v>
       </c>
       <c r="G60">
-        <v>999</v>
+        <v>899</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>1</v>
+      <c r="A61">
+        <v>11177964</v>
       </c>
       <c r="B61">
-        <v>16532</v>
+        <v>16607</v>
       </c>
       <c r="C61" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F61">
-        <v>58773</v>
+        <v>58785</v>
       </c>
       <c r="G61">
-        <v>899</v>
+        <v>669</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>11177964</v>
+        <v>11177937</v>
       </c>
       <c r="B62">
-        <v>16607</v>
+        <v>16611</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D62" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F62">
-        <v>58785</v>
+        <v>58761</v>
       </c>
       <c r="G62">
-        <v>669</v>
+        <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>11177937</v>
+        <v>11176721</v>
       </c>
       <c r="B63">
-        <v>16611</v>
+        <v>16662</v>
       </c>
       <c r="C63" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E63" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F63">
-        <v>58761</v>
+        <v>58779</v>
       </c>
       <c r="G63">
-        <v>539</v>
+        <v>969</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>11176721</v>
+        <v>11176711</v>
       </c>
       <c r="B64">
-        <v>16662</v>
+        <v>16669</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E64" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F64">
-        <v>58779</v>
+        <v>58765</v>
       </c>
       <c r="G64">
-        <v>969</v>
+        <v>569</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>11176711</v>
+        <v>11176700</v>
       </c>
       <c r="B65">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="C65" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F65">
-        <v>58765</v>
+        <v>58783</v>
       </c>
       <c r="G65">
-        <v>569</v>
+        <v>399</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>11176700</v>
+        <v>11176703</v>
       </c>
       <c r="B66">
-        <v>16670</v>
+        <v>16673</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D66" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E66" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F66">
-        <v>58783</v>
+        <v>58797</v>
       </c>
       <c r="G66">
-        <v>399</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>11176703</v>
+        <v>11176704</v>
       </c>
       <c r="B67">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="C67" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E67" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F67">
-        <v>58797</v>
+        <v>58798</v>
       </c>
       <c r="G67">
-        <v>369</v>
+        <v>499</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>11176704</v>
+        <v>11176722</v>
       </c>
       <c r="B68">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F68">
-        <v>58798</v>
+        <v>58799</v>
       </c>
       <c r="G68">
-        <v>499</v>
+        <v>689</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>11176722</v>
+        <v>11176718</v>
       </c>
       <c r="B69">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E69" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F69">
-        <v>58799</v>
+        <v>58800</v>
       </c>
       <c r="G69">
-        <v>689</v>
+        <v>669</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>11176718</v>
+        <v>11176723</v>
       </c>
       <c r="B70">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F70">
-        <v>58800</v>
+        <v>58801</v>
       </c>
       <c r="G70">
-        <v>669</v>
+        <v>889</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>11176723</v>
+        <v>11176724</v>
       </c>
       <c r="B71">
-        <v>16677</v>
+        <v>16672</v>
       </c>
       <c r="C71" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E71" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F71">
-        <v>58801</v>
+        <v>58763</v>
       </c>
       <c r="G71">
-        <v>889</v>
+        <v>999</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>11176724</v>
+        <v>11176717</v>
       </c>
       <c r="B72">
-        <v>16672</v>
+        <v>16671</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D72" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E72" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F72">
-        <v>58763</v>
+        <v>58796</v>
       </c>
       <c r="G72">
-        <v>999</v>
+        <v>489</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>11176717</v>
+        <v>11176716</v>
       </c>
       <c r="B73">
-        <v>16671</v>
+        <v>16668</v>
       </c>
       <c r="C73" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E73" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F73">
-        <v>58796</v>
+        <v>58781</v>
       </c>
       <c r="G73">
-        <v>489</v>
+        <v>899</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>11176716</v>
+        <v>11176612</v>
       </c>
       <c r="B74">
-        <v>16668</v>
+        <v>16608</v>
       </c>
       <c r="C74" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D74" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E74" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F74">
-        <v>58781</v>
+        <v>52575</v>
       </c>
       <c r="G74">
-        <v>899</v>
+        <v>659</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>11176612</v>
+        <v>11176610</v>
       </c>
       <c r="B75">
-        <v>16608</v>
+        <v>16609</v>
       </c>
       <c r="C75" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D75" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F75">
-        <v>52575</v>
+        <v>52577</v>
       </c>
       <c r="G75">
-        <v>659</v>
+        <v>717</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>11176610</v>
+        <v>11176710</v>
       </c>
       <c r="B76">
-        <v>16609</v>
+        <v>16664</v>
       </c>
       <c r="C76" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D76" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E76" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F76">
-        <v>52577</v>
+        <v>58791</v>
       </c>
       <c r="G76">
-        <v>717</v>
+        <v>529</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>11176710</v>
+        <v>11176701</v>
       </c>
       <c r="B77">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="C77" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D77" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E77" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F77">
-        <v>58791</v>
+        <v>58792</v>
       </c>
       <c r="G77">
-        <v>529</v>
+        <v>489</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>11176701</v>
+        <v>11176702</v>
       </c>
       <c r="B78">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="C78" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E78" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F78">
-        <v>58792</v>
+        <v>58793</v>
       </c>
       <c r="G78">
-        <v>489</v>
+        <v>459</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>11176702</v>
+        <v>11176715</v>
       </c>
       <c r="B79">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="C79" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E79" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F79">
-        <v>58793</v>
+        <v>58794</v>
       </c>
       <c r="G79">
-        <v>459</v>
+        <v>679</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>11176715</v>
+        <v>11176699</v>
       </c>
       <c r="B80">
-        <v>16667</v>
+        <v>16663</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D80" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E80" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F80">
-        <v>58794</v>
+        <v>58767</v>
       </c>
       <c r="G80">
-        <v>679</v>
+        <v>499</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>11176699</v>
+        <v>11177607</v>
       </c>
       <c r="B81">
-        <v>16663</v>
+        <v>16680</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E81" t="s">
-        <v>126</v>
-      </c>
-      <c r="F81">
-        <v>58767</v>
+        <v>128</v>
+      </c>
+      <c r="F81" t="s">
+        <v>129</v>
       </c>
       <c r="G81">
-        <v>499</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>11177607</v>
+      <c r="A82" t="s">
+        <v>1</v>
       </c>
       <c r="B82">
-        <v>16680</v>
+        <v>16729</v>
       </c>
       <c r="C82" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D82" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E82" t="s">
-        <v>128</v>
-      </c>
-      <c r="F82" t="s">
-        <v>129</v>
+        <v>131</v>
+      </c>
+      <c r="F82">
+        <v>52617</v>
       </c>
       <c r="G82">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -6152,387 +6146,387 @@
         <v>1</v>
       </c>
       <c r="B83">
-        <v>16729</v>
+        <v>16771</v>
       </c>
       <c r="C83" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E83" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F83">
-        <v>52617</v>
+        <v>52615</v>
       </c>
       <c r="G83">
-        <v>59</v>
+        <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>1</v>
+      <c r="A84">
+        <v>11176714</v>
       </c>
       <c r="B84">
-        <v>16771</v>
+        <v>16659</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D84" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E84" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F84">
-        <v>52615</v>
+        <v>52609</v>
       </c>
       <c r="G84">
-        <v>109</v>
+        <v>677</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>11176714</v>
+        <v>11176719</v>
       </c>
       <c r="B85">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D85" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E85" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F85">
-        <v>52609</v>
+        <v>52610</v>
       </c>
       <c r="G85">
-        <v>677</v>
+        <v>739</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>11176719</v>
+        <v>11176708</v>
       </c>
       <c r="B86">
-        <v>16660</v>
+        <v>16658</v>
       </c>
       <c r="C86" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E86" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F86">
-        <v>52610</v>
+        <v>52608</v>
       </c>
       <c r="G86">
-        <v>739</v>
+        <v>567</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>11176708</v>
+        <v>11176720</v>
       </c>
       <c r="B87">
-        <v>16658</v>
+        <v>16661</v>
       </c>
       <c r="C87" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D87" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E87" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F87">
-        <v>52608</v>
+        <v>52612</v>
       </c>
       <c r="G87">
-        <v>567</v>
+        <v>839</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>11176720</v>
+        <v>11174775</v>
       </c>
       <c r="B88">
-        <v>16661</v>
+        <v>16551</v>
       </c>
       <c r="C88" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D88" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E88" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F88">
-        <v>52612</v>
+        <v>52596</v>
       </c>
       <c r="G88">
-        <v>839</v>
+        <v>457</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>11174775</v>
+        <v>11177276</v>
       </c>
       <c r="B89">
-        <v>16551</v>
+        <v>16559</v>
       </c>
       <c r="C89" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D89" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E89" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F89">
-        <v>52596</v>
+        <v>52597</v>
       </c>
       <c r="G89">
-        <v>457</v>
+        <v>689</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>11177276</v>
+        <v>11174806</v>
       </c>
       <c r="B90">
-        <v>16559</v>
+        <v>16557</v>
       </c>
       <c r="C90" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E90" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F90">
-        <v>52597</v>
+        <v>52598</v>
       </c>
       <c r="G90">
-        <v>689</v>
+        <v>729</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>11174806</v>
+        <v>11174811</v>
       </c>
       <c r="B91">
-        <v>16557</v>
+        <v>16546</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E91" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F91">
-        <v>52598</v>
+        <v>52600</v>
       </c>
       <c r="G91">
-        <v>729</v>
+        <v>839</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>11174811</v>
+      <c r="A92" t="s">
+        <v>1</v>
       </c>
       <c r="B92">
-        <v>16546</v>
+        <v>16775</v>
       </c>
       <c r="C92" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D92" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E92" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F92">
-        <v>52600</v>
+        <v>52606</v>
       </c>
       <c r="G92">
-        <v>839</v>
+        <v>169</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+      <c r="A93">
+        <v>11174791</v>
+      </c>
+      <c r="B93">
+        <v>16572</v>
+      </c>
+      <c r="C93" t="s">
+        <v>152</v>
+      </c>
+      <c r="D93" t="s">
+        <v>153</v>
+      </c>
+      <c r="E93" t="s">
+        <v>153</v>
+      </c>
+      <c r="F93">
+        <v>52582</v>
+      </c>
+      <c r="G93">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>1</v>
       </c>
-      <c r="B93">
-        <v>16775</v>
-      </c>
-      <c r="C93" t="s">
-        <v>150</v>
-      </c>
-      <c r="D93" t="s">
-        <v>151</v>
-      </c>
-      <c r="E93" t="s">
-        <v>151</v>
-      </c>
-      <c r="F93">
-        <v>52606</v>
-      </c>
-      <c r="G93">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>11174791</v>
-      </c>
       <c r="B94">
-        <v>16572</v>
+        <v>16770</v>
       </c>
       <c r="C94" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D94" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E94" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F94">
-        <v>52582</v>
+        <v>52616</v>
       </c>
       <c r="G94">
-        <v>59</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>1</v>
+      <c r="A95">
+        <v>11174803</v>
       </c>
       <c r="B95">
-        <v>16770</v>
+        <v>16549</v>
       </c>
       <c r="C95" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D95" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E95" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F95">
-        <v>52616</v>
+        <v>52591</v>
       </c>
       <c r="G95">
-        <v>109</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>11174803</v>
+        <v>11174810</v>
       </c>
       <c r="B96">
-        <v>16549</v>
+        <v>16555</v>
       </c>
       <c r="C96" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D96" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E96" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F96">
-        <v>52591</v>
+        <v>52595</v>
       </c>
       <c r="G96">
-        <v>1399</v>
+        <v>999</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>11174810</v>
+        <v>11174776</v>
       </c>
       <c r="B97">
-        <v>16555</v>
+        <v>16550</v>
       </c>
       <c r="C97" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D97" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E97" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F97">
-        <v>52595</v>
+        <v>52585</v>
       </c>
       <c r="G97">
-        <v>999</v>
+        <v>429</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>11174776</v>
+        <v>11174801</v>
       </c>
       <c r="B98">
-        <v>16550</v>
+        <v>16548</v>
       </c>
       <c r="C98" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D98" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E98" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F98">
-        <v>52585</v>
+        <v>52586</v>
       </c>
       <c r="G98">
-        <v>429</v>
+        <v>689</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>11174801</v>
+        <v>11177275</v>
       </c>
       <c r="B99">
-        <v>16548</v>
+        <v>16558</v>
       </c>
       <c r="C99" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D99" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E99" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F99">
-        <v>52586</v>
+        <v>52587</v>
       </c>
       <c r="G99">
         <v>689</v>
@@ -6540,206 +6534,206 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>11177275</v>
+        <v>11175037</v>
       </c>
       <c r="B100">
-        <v>16558</v>
+        <v>16573</v>
       </c>
       <c r="C100" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D100" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E100" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F100">
-        <v>52587</v>
+        <v>52588</v>
       </c>
       <c r="G100">
-        <v>689</v>
+        <v>444</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>11175037</v>
+        <v>11174795</v>
       </c>
       <c r="B101">
-        <v>16573</v>
+        <v>16543</v>
       </c>
       <c r="C101" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D101" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E101" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F101">
-        <v>52588</v>
+        <v>52589</v>
       </c>
       <c r="G101">
-        <v>444</v>
+        <v>549</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>11174795</v>
+      <c r="A102" t="s">
+        <v>1</v>
       </c>
       <c r="B102">
-        <v>16543</v>
+        <v>16769</v>
       </c>
       <c r="C102" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D102" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E102" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F102">
-        <v>52589</v>
+        <v>52614</v>
       </c>
       <c r="G102">
-        <v>549</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>1</v>
+      <c r="A103">
+        <v>11174779</v>
       </c>
       <c r="B103">
-        <v>16769</v>
+        <v>16540</v>
       </c>
       <c r="C103" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D103" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E103" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F103">
-        <v>52614</v>
+        <v>52584</v>
       </c>
       <c r="G103">
-        <v>109</v>
+        <v>567</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>11174779</v>
+        <v>11174804</v>
       </c>
       <c r="B104">
-        <v>16540</v>
+        <v>16541</v>
       </c>
       <c r="C104" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D104" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E104" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F104">
-        <v>52584</v>
+        <v>52593</v>
       </c>
       <c r="G104">
-        <v>567</v>
+        <v>889</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>11174804</v>
+        <v>11174798</v>
       </c>
       <c r="B105">
-        <v>16541</v>
+        <v>16552</v>
       </c>
       <c r="C105" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D105" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E105" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F105">
-        <v>52593</v>
+        <v>52578</v>
       </c>
       <c r="G105">
-        <v>889</v>
+        <v>649</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>11174798</v>
+        <v>11174808</v>
       </c>
       <c r="B106">
-        <v>16552</v>
+        <v>16545</v>
       </c>
       <c r="C106" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D106" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E106" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F106">
-        <v>52578</v>
+        <v>52579</v>
       </c>
       <c r="G106">
-        <v>649</v>
+        <v>749</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>11174808</v>
+        <v>11177274</v>
       </c>
       <c r="B107">
-        <v>16545</v>
+        <v>16547</v>
       </c>
       <c r="C107" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E107" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F107">
-        <v>52579</v>
+        <v>52580</v>
       </c>
       <c r="G107">
-        <v>749</v>
+        <v>669</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>11177274</v>
+        <v>11174800</v>
       </c>
       <c r="B108">
-        <v>16547</v>
+        <v>16553</v>
       </c>
       <c r="C108" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E108" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F108">
-        <v>52580</v>
+        <v>52581</v>
       </c>
       <c r="G108">
         <v>669</v>
@@ -6747,116 +6741,93 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>11174800</v>
+        <v>11174807</v>
       </c>
       <c r="B109">
-        <v>16553</v>
+        <v>16554</v>
       </c>
       <c r="C109" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D109" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E109" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F109">
-        <v>52581</v>
+        <v>52601</v>
       </c>
       <c r="G109">
-        <v>669</v>
+        <v>649</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>11174807</v>
+        <v>11177277</v>
       </c>
       <c r="B110">
-        <v>16554</v>
+        <v>16544</v>
       </c>
       <c r="C110" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D110" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E110" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F110">
-        <v>52601</v>
+        <v>52602</v>
       </c>
       <c r="G110">
-        <v>649</v>
+        <v>489</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>11177277</v>
+        <v>11174790</v>
       </c>
       <c r="B111">
-        <v>16544</v>
+        <v>16542</v>
       </c>
       <c r="C111" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D111" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E111" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F111">
-        <v>52602</v>
+        <v>52603</v>
       </c>
       <c r="G111">
-        <v>489</v>
+        <v>349</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>11174790</v>
+        <v>11174799</v>
       </c>
       <c r="B112">
-        <v>16542</v>
+        <v>16556</v>
       </c>
       <c r="C112" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D112" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E112" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F112">
-        <v>52603</v>
+        <v>52604</v>
       </c>
       <c r="G112">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <v>11174799</v>
-      </c>
-      <c r="B113">
-        <v>16556</v>
-      </c>
-      <c r="C113" t="s">
-        <v>190</v>
-      </c>
-      <c r="D113" t="s">
-        <v>191</v>
-      </c>
-      <c r="E113" t="s">
-        <v>191</v>
-      </c>
-      <c r="F113">
-        <v>52604</v>
-      </c>
-      <c r="G113">
         <v>609</v>
       </c>
     </row>

--- a/Lista_Precios_Base.xlsx
+++ b/Lista_Precios_Base.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\OneDrive - Alsea - Europa\Nube_EnriqueCesar\GitHub\CodeBrew\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CodeBrew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71BEC85-4C4D-4198-A748-8E3A4E39F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{C71BEC85-4C4D-4198-A748-8E3A4E39F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B02FD59-DF14-45EC-A8BF-C263F1BCFCBE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3774" uniqueCount="1209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3777" uniqueCount="1211">
   <si>
     <t>WC26Stan20IceF</t>
   </si>
@@ -3721,6 +3721,12 @@
   </si>
   <si>
     <t>SII26BearPony</t>
+  </si>
+  <si>
+    <t>CCUP 16OZ SS HAPPY FARM CHILLAX PONY AND FLOWERS</t>
+  </si>
+  <si>
+    <t>SII26SSCC16Pony</t>
   </si>
 </sst>
 </file>
@@ -3889,8 +3895,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G112" totalsRowShown="0">
-  <autoFilter ref="A1:G112" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G113" totalsRowShown="0">
+  <autoFilter ref="A1:G113" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3FD2C0CF-4866-4870-AD33-E904DA8BA849}" name="SKU INTL"/>
     <tableColumn id="2" xr3:uid="{39846DA6-B590-4416-838E-B359114E50F9}" name="CÓDIGO DIA"/>
@@ -4250,7 +4256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8718E42-507B-44AF-801B-0B0250CAF160}">
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" bestFit="1" customWidth="1"/>
@@ -4286,22 +4292,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1176593</v>
+        <v>11176587</v>
       </c>
       <c r="B2">
-        <v>16793</v>
+        <v>16720</v>
       </c>
       <c r="C2" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="D2" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="E2" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="F2">
-        <v>50741</v>
+        <v>50740</v>
       </c>
       <c r="G2">
         <v>649</v>
@@ -4309,22 +4315,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>11176592</v>
+        <v>1176593</v>
       </c>
       <c r="B3">
-        <v>16779</v>
+        <v>16793</v>
       </c>
       <c r="C3" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D3" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="E3" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F3">
-        <v>50742</v>
+        <v>50741</v>
       </c>
       <c r="G3">
         <v>649</v>
@@ -4332,114 +4338,114 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>11176586</v>
+        <v>11176592</v>
       </c>
       <c r="B4">
-        <v>16719</v>
+        <v>16779</v>
       </c>
       <c r="C4" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="D4" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="E4" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F4">
-        <v>50743</v>
+        <v>50742</v>
       </c>
       <c r="G4">
-        <v>669</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>11176597</v>
+        <v>11176586</v>
       </c>
       <c r="B5">
-        <v>16784</v>
+        <v>16719</v>
       </c>
       <c r="C5" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D5" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="E5" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="F5">
-        <v>50745</v>
+        <v>50743</v>
       </c>
       <c r="G5">
-        <v>369</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>11178956</v>
+        <v>11176597</v>
       </c>
       <c r="B6">
-        <v>16916</v>
+        <v>16784</v>
       </c>
       <c r="C6" t="s">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="D6" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="E6" t="s">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="F6">
-        <v>50735</v>
+        <v>50745</v>
       </c>
       <c r="G6">
-        <v>999</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>11178933</v>
+        <v>11178956</v>
       </c>
       <c r="B7">
-        <v>16881</v>
+        <v>16916</v>
       </c>
       <c r="C7" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="D7" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="E7" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="F7">
-        <v>50736</v>
+        <v>50735</v>
       </c>
       <c r="G7">
-        <v>529</v>
+        <v>999</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>11178934</v>
+        <v>11178933</v>
       </c>
       <c r="B8">
-        <v>16884</v>
+        <v>16881</v>
       </c>
       <c r="C8" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="D8" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="E8" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="F8">
-        <v>50737</v>
+        <v>50736</v>
       </c>
       <c r="G8">
         <v>529</v>
@@ -4447,505 +4453,505 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>11178935</v>
+        <v>11178934</v>
       </c>
       <c r="B9">
-        <v>16920</v>
+        <v>16884</v>
       </c>
       <c r="C9" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="D9" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E9" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="F9">
-        <v>50738</v>
+        <v>50737</v>
       </c>
       <c r="G9">
-        <v>459</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>11178941</v>
+        <v>11178935</v>
       </c>
       <c r="B10">
-        <v>16900</v>
+        <v>16920</v>
       </c>
       <c r="C10" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="D10" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="E10" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="F10">
-        <v>50739</v>
+        <v>50738</v>
       </c>
       <c r="G10">
-        <v>649</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>11178917</v>
+        <v>11178941</v>
       </c>
       <c r="B11">
-        <v>16921</v>
+        <v>16900</v>
       </c>
       <c r="C11" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="D11" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E11" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="F11">
-        <v>58808</v>
+        <v>50739</v>
       </c>
       <c r="G11">
-        <v>479</v>
+        <v>649</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11178969</v>
+        <v>11178917</v>
       </c>
       <c r="B12">
-        <v>16910</v>
+        <v>16921</v>
       </c>
       <c r="C12" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D12" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="E12" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F12">
-        <v>58827</v>
+        <v>58808</v>
       </c>
       <c r="G12">
-        <v>679</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11178918</v>
+        <v>11178969</v>
       </c>
       <c r="B13">
-        <v>16923</v>
+        <v>16910</v>
       </c>
       <c r="C13" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="D13" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="E13" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="F13">
-        <v>58832</v>
+        <v>58827</v>
       </c>
       <c r="G13">
-        <v>489</v>
+        <v>679</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11178946</v>
+        <v>11178918</v>
       </c>
       <c r="B14">
-        <v>16913</v>
+        <v>16923</v>
       </c>
       <c r="C14" t="s">
-        <v>1175</v>
+        <v>1199</v>
       </c>
       <c r="D14" t="s">
-        <v>1176</v>
+        <v>1200</v>
       </c>
       <c r="E14" t="s">
-        <v>1176</v>
+        <v>1200</v>
       </c>
       <c r="F14">
-        <v>58814</v>
+        <v>58832</v>
       </c>
       <c r="G14">
-        <v>689</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>11178973</v>
+        <v>11178946</v>
       </c>
       <c r="B15">
-        <v>16925</v>
+        <v>16913</v>
       </c>
       <c r="C15" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D15" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="E15" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="F15">
-        <v>58815</v>
+        <v>58814</v>
       </c>
       <c r="G15">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11178959</v>
+        <v>11178973</v>
       </c>
       <c r="B16">
-        <v>16897</v>
+        <v>16925</v>
       </c>
       <c r="C16" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="D16" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="E16" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="F16">
-        <v>58816</v>
+        <v>58815</v>
       </c>
       <c r="G16">
-        <v>659</v>
+        <v>649</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>11178928</v>
+        <v>11178959</v>
       </c>
       <c r="B17">
-        <v>16880</v>
+        <v>16897</v>
       </c>
       <c r="C17" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D17" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E17" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F17">
-        <v>58817</v>
+        <v>58816</v>
       </c>
       <c r="G17">
-        <v>549</v>
+        <v>659</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>11178965</v>
+        <v>11178928</v>
       </c>
       <c r="B18">
-        <v>16904</v>
+        <v>16880</v>
       </c>
       <c r="C18" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="D18" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="E18" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F18">
-        <v>58818</v>
+        <v>58817</v>
       </c>
       <c r="G18">
-        <v>535</v>
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>11178937</v>
+        <v>11178965</v>
       </c>
       <c r="B19">
-        <v>16901</v>
+        <v>16904</v>
       </c>
       <c r="C19" t="s">
-        <v>1052</v>
+        <v>1183</v>
       </c>
       <c r="D19" t="s">
-        <v>1053</v>
+        <v>1184</v>
       </c>
       <c r="E19" t="s">
-        <v>1053</v>
+        <v>1184</v>
       </c>
       <c r="F19">
-        <v>58819</v>
+        <v>58818</v>
       </c>
       <c r="G19">
-        <v>739</v>
+        <v>535</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
+        <v>11178937</v>
+      </c>
+      <c r="B20">
+        <v>16901</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F20">
+        <v>58819</v>
+      </c>
+      <c r="G20">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>11178948</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>16915</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>1054</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>1055</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>1055</v>
       </c>
-      <c r="F20">
+      <c r="F21">
         <v>58821</v>
       </c>
-      <c r="G20">
+      <c r="G21">
         <v>899</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>1</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>16971</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>28</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>1056</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>1056</v>
       </c>
-      <c r="F21">
+      <c r="F22">
         <v>58846</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>869</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>11178944</v>
-      </c>
-      <c r="B22">
-        <v>16909</v>
-      </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22">
-        <v>58826</v>
-      </c>
-      <c r="G22">
-        <v>679</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11178952</v>
+        <v>11178944</v>
       </c>
       <c r="B23">
-        <v>16875</v>
+        <v>16909</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>58828</v>
+        <v>58826</v>
       </c>
       <c r="G23">
-        <v>689</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11178971</v>
+        <v>11178952</v>
       </c>
       <c r="B24">
-        <v>16911</v>
+        <v>16875</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F24">
-        <v>58829</v>
+        <v>58828</v>
       </c>
       <c r="G24">
-        <v>679</v>
+        <v>689</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11178920</v>
+        <v>11178971</v>
       </c>
       <c r="B25">
-        <v>16902</v>
+        <v>16911</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F25">
-        <v>58830</v>
+        <v>58829</v>
       </c>
       <c r="G25">
-        <v>369</v>
+        <v>679</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>11178922</v>
+        <v>11178920</v>
       </c>
       <c r="B26">
-        <v>16879</v>
+        <v>16902</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>58831</v>
+        <v>58830</v>
       </c>
       <c r="G26">
-        <v>349</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11178945</v>
+        <v>11178922</v>
       </c>
       <c r="B27">
-        <v>16924</v>
+        <v>16879</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>58835</v>
+        <v>58831</v>
       </c>
       <c r="G27">
-        <v>899</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>11179005</v>
+        <v>11178945</v>
       </c>
       <c r="B28">
-        <v>16906</v>
+        <v>16924</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>58823</v>
+        <v>58835</v>
       </c>
       <c r="G28">
-        <v>889</v>
+        <v>899</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11178930</v>
+        <v>11179005</v>
       </c>
       <c r="B29">
-        <v>16882</v>
+        <v>16906</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>58824</v>
+        <v>58823</v>
       </c>
       <c r="G29">
-        <v>535</v>
+        <v>889</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>11178966</v>
+        <v>11178930</v>
       </c>
       <c r="B30">
-        <v>16905</v>
+        <v>16882</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F30">
-        <v>58825</v>
+        <v>58824</v>
       </c>
       <c r="G30">
         <v>535</v>
@@ -4953,94 +4959,94 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11187369</v>
+        <v>11178966</v>
       </c>
       <c r="B31">
-        <v>16908</v>
+        <v>16905</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F31">
-        <v>58848</v>
+        <v>58825</v>
       </c>
       <c r="G31">
-        <v>869</v>
+        <v>535</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11187370</v>
+        <v>11187369</v>
       </c>
       <c r="B32">
-        <v>16958</v>
+        <v>16908</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F32">
-        <v>58838</v>
+        <v>58848</v>
       </c>
       <c r="G32">
-        <v>679</v>
+        <v>869</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
+        <v>11187370</v>
+      </c>
+      <c r="B33">
+        <v>16958</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33">
+        <v>58838</v>
+      </c>
+      <c r="G33">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>11187372</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>16959</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>32</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>33</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E34" t="s">
         <v>33</v>
       </c>
-      <c r="F33">
+      <c r="F34">
         <v>58839</v>
       </c>
-      <c r="G33">
+      <c r="G34">
         <v>369</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34">
-        <v>16978</v>
-      </c>
-      <c r="C34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" t="s">
-        <v>35</v>
-      </c>
-      <c r="F34">
-        <v>58836</v>
-      </c>
-      <c r="G34">
-        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -5048,22 +5054,22 @@
         <v>1</v>
       </c>
       <c r="B35">
-        <v>16955</v>
+        <v>16978</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F35">
-        <v>58840</v>
+        <v>58836</v>
       </c>
       <c r="G35">
-        <v>1099</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -5074,88 +5080,88 @@
         <v>16955</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F36">
-        <v>58842</v>
+        <v>58840</v>
       </c>
       <c r="G36">
         <v>1099</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>11178949</v>
+      <c r="A37" t="s">
+        <v>1</v>
       </c>
       <c r="B37">
-        <v>16912</v>
+        <v>16955</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F37">
-        <v>58822</v>
+        <v>58842</v>
       </c>
       <c r="G37">
-        <v>679</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
+        <v>11178949</v>
+      </c>
+      <c r="B38">
+        <v>16912</v>
+      </c>
+      <c r="C38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38">
+        <v>58822</v>
+      </c>
+      <c r="G38">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>11178957</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>16919</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>42</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>43</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E39" t="s">
         <v>43</v>
       </c>
-      <c r="F38">
+      <c r="F39">
         <v>58820</v>
       </c>
-      <c r="G38">
+      <c r="G39">
         <v>999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39">
-        <v>16780</v>
-      </c>
-      <c r="C39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D39" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" t="s">
-        <v>45</v>
-      </c>
-      <c r="F39">
-        <v>58753</v>
-      </c>
-      <c r="G39">
-        <v>689</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -5163,19 +5169,19 @@
         <v>1</v>
       </c>
       <c r="B40">
-        <v>16781</v>
+        <v>16780</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F40">
-        <v>58755</v>
+        <v>58753</v>
       </c>
       <c r="G40">
         <v>689</v>
@@ -5186,335 +5192,338 @@
         <v>1</v>
       </c>
       <c r="B41">
+        <v>16781</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41">
+        <v>58755</v>
+      </c>
+      <c r="G41">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42">
         <v>16721</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>48</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>49</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" t="s">
         <v>49</v>
       </c>
-      <c r="F41">
+      <c r="F42">
         <v>58757</v>
       </c>
-      <c r="G41">
+      <c r="G42">
         <v>649</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>11179003</v>
-      </c>
-      <c r="B42">
-        <v>16885</v>
-      </c>
-      <c r="C42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" t="s">
-        <v>51</v>
-      </c>
-      <c r="F42">
-        <v>58812</v>
-      </c>
-      <c r="G42">
-        <v>499</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>11179004</v>
+        <v>11179003</v>
       </c>
       <c r="B43">
-        <v>16899</v>
+        <v>16885</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F43">
-        <v>58813</v>
+        <v>58812</v>
       </c>
       <c r="G43">
-        <v>699</v>
+        <v>499</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>11178954</v>
+        <v>11179004</v>
       </c>
       <c r="B44">
-        <v>16877</v>
+        <v>16899</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F44">
-        <v>58777</v>
+        <v>58813</v>
       </c>
       <c r="G44">
-        <v>719</v>
+        <v>699</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>11178943</v>
+        <v>11178954</v>
       </c>
       <c r="B45">
-        <v>16918</v>
+        <v>16877</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F45">
-        <v>58802</v>
+        <v>58777</v>
       </c>
       <c r="G45">
-        <v>689</v>
+        <v>719</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>11178970</v>
+        <v>11178943</v>
       </c>
       <c r="B46">
-        <v>16896</v>
+        <v>16918</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D46" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F46">
-        <v>58803</v>
+        <v>58802</v>
       </c>
       <c r="G46">
-        <v>699</v>
+        <v>689</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>11178953</v>
+        <v>11178970</v>
       </c>
       <c r="B47">
-        <v>16876</v>
+        <v>16896</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F47">
-        <v>58804</v>
+        <v>58803</v>
       </c>
       <c r="G47">
-        <v>689</v>
+        <v>699</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>11178921</v>
+        <v>11178953</v>
       </c>
       <c r="B48">
-        <v>16878</v>
+        <v>16876</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F48">
-        <v>58805</v>
+        <v>58804</v>
       </c>
       <c r="G48">
-        <v>349</v>
+        <v>689</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>11178926</v>
+        <v>11178921</v>
       </c>
       <c r="B49">
-        <v>16903</v>
+        <v>16878</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F49">
-        <v>58806</v>
+        <v>58805</v>
       </c>
       <c r="G49">
-        <v>529</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>11178964</v>
+        <v>11178926</v>
       </c>
       <c r="B50">
-        <v>16883</v>
+        <v>16903</v>
       </c>
       <c r="C50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F50">
-        <v>58807</v>
+        <v>58806</v>
       </c>
       <c r="G50">
-        <v>249</v>
+        <v>529</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>11178972</v>
+        <v>11178964</v>
       </c>
       <c r="B51">
-        <v>16917</v>
+        <v>16883</v>
       </c>
       <c r="C51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F51">
-        <v>58809</v>
+        <v>58807</v>
       </c>
       <c r="G51">
-        <v>889</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>11178938</v>
+        <v>11178972</v>
       </c>
       <c r="B52">
-        <v>16898</v>
+        <v>16917</v>
       </c>
       <c r="C52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D52" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E52" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F52">
-        <v>58810</v>
+        <v>58809</v>
       </c>
       <c r="G52">
-        <v>599</v>
+        <v>889</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>11178919</v>
+        <v>11178938</v>
       </c>
       <c r="B53">
-        <v>16922</v>
+        <v>16898</v>
       </c>
       <c r="C53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F53">
-        <v>58811</v>
+        <v>58810</v>
       </c>
       <c r="G53">
-        <v>439</v>
+        <v>599</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>11176705</v>
+        <v>11178919</v>
       </c>
       <c r="B54">
-        <v>16678</v>
+        <v>16922</v>
       </c>
       <c r="C54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D54" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
-      </c>
-      <c r="F54" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="F54">
+        <v>58811</v>
+      </c>
+      <c r="G54">
+        <v>439</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>11176712</v>
+        <v>11176705</v>
       </c>
       <c r="B55">
-        <v>16679</v>
+        <v>16678</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E55" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F55" t="s">
         <v>76</v>
@@ -5522,48 +5531,45 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
+        <v>11176712</v>
+      </c>
+      <c r="B56">
+        <v>16679</v>
+      </c>
+      <c r="C56" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" t="s">
+        <v>78</v>
+      </c>
+      <c r="F56" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57">
         <v>11178947</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>16914</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C57" t="s">
         <v>79</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D57" t="s">
         <v>80</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E57" t="s">
         <v>80</v>
       </c>
-      <c r="F56">
+      <c r="F57">
         <v>58795</v>
       </c>
-      <c r="G56">
+      <c r="G57">
         <v>899</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57">
-        <v>16531</v>
-      </c>
-      <c r="C57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" t="s">
-        <v>82</v>
-      </c>
-      <c r="E57" t="s">
-        <v>82</v>
-      </c>
-      <c r="F57">
-        <v>58769</v>
-      </c>
-      <c r="G57">
-        <v>1099</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -5577,13 +5583,13 @@
         <v>81</v>
       </c>
       <c r="D58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F58">
-        <v>58775</v>
+        <v>58769</v>
       </c>
       <c r="G58">
         <v>1099</v>
@@ -5594,22 +5600,22 @@
         <v>1</v>
       </c>
       <c r="B59">
-        <v>16532</v>
+        <v>16531</v>
       </c>
       <c r="C59" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F59">
-        <v>58771</v>
+        <v>58775</v>
       </c>
       <c r="G59">
-        <v>999</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -5623,522 +5629,522 @@
         <v>84</v>
       </c>
       <c r="D60" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60">
+        <v>58771</v>
+      </c>
+      <c r="G60">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>1</v>
+      </c>
+      <c r="B61">
+        <v>16532</v>
+      </c>
+      <c r="C61" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" t="s">
         <v>86</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E61" t="s">
         <v>86</v>
       </c>
-      <c r="F60">
+      <c r="F61">
         <v>58773</v>
       </c>
-      <c r="G60">
+      <c r="G61">
         <v>899</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>11177964</v>
-      </c>
-      <c r="B61">
-        <v>16607</v>
-      </c>
-      <c r="C61" t="s">
-        <v>87</v>
-      </c>
-      <c r="D61" t="s">
-        <v>88</v>
-      </c>
-      <c r="E61" t="s">
-        <v>88</v>
-      </c>
-      <c r="F61">
-        <v>58785</v>
-      </c>
-      <c r="G61">
-        <v>669</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>11177937</v>
+        <v>11177964</v>
       </c>
       <c r="B62">
-        <v>16611</v>
+        <v>16607</v>
       </c>
       <c r="C62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E62" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F62">
-        <v>58761</v>
+        <v>58785</v>
       </c>
       <c r="G62">
-        <v>539</v>
+        <v>669</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>11176721</v>
+        <v>11177937</v>
       </c>
       <c r="B63">
-        <v>16662</v>
+        <v>16611</v>
       </c>
       <c r="C63" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D63" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F63">
-        <v>58779</v>
+        <v>58761</v>
       </c>
       <c r="G63">
-        <v>969</v>
+        <v>539</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>11176711</v>
+        <v>11176721</v>
       </c>
       <c r="B64">
-        <v>16669</v>
+        <v>16662</v>
       </c>
       <c r="C64" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D64" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E64" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F64">
-        <v>58765</v>
+        <v>58779</v>
       </c>
       <c r="G64">
-        <v>569</v>
+        <v>969</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>11176700</v>
+        <v>11176711</v>
       </c>
       <c r="B65">
-        <v>16670</v>
+        <v>16669</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D65" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E65" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F65">
-        <v>58783</v>
+        <v>58765</v>
       </c>
       <c r="G65">
-        <v>399</v>
+        <v>569</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>11176703</v>
+        <v>11176700</v>
       </c>
       <c r="B66">
-        <v>16673</v>
+        <v>16670</v>
       </c>
       <c r="C66" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F66">
-        <v>58797</v>
+        <v>58783</v>
       </c>
       <c r="G66">
-        <v>369</v>
+        <v>399</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>11176704</v>
+        <v>11176703</v>
       </c>
       <c r="B67">
-        <v>16674</v>
+        <v>16673</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D67" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E67" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F67">
-        <v>58798</v>
+        <v>58797</v>
       </c>
       <c r="G67">
-        <v>499</v>
+        <v>369</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>11176722</v>
+        <v>11176704</v>
       </c>
       <c r="B68">
-        <v>16675</v>
+        <v>16674</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D68" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E68" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F68">
-        <v>58799</v>
+        <v>58798</v>
       </c>
       <c r="G68">
-        <v>689</v>
+        <v>499</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>11176718</v>
+        <v>11176722</v>
       </c>
       <c r="B69">
-        <v>16676</v>
+        <v>16675</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D69" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E69" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F69">
-        <v>58800</v>
+        <v>58799</v>
       </c>
       <c r="G69">
-        <v>669</v>
+        <v>689</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>11176723</v>
+        <v>11176718</v>
       </c>
       <c r="B70">
-        <v>16677</v>
+        <v>16676</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E70" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F70">
-        <v>58801</v>
+        <v>58800</v>
       </c>
       <c r="G70">
-        <v>889</v>
+        <v>669</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>11176724</v>
+        <v>11176723</v>
       </c>
       <c r="B71">
-        <v>16672</v>
+        <v>16677</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D71" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E71" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F71">
-        <v>58763</v>
+        <v>58801</v>
       </c>
       <c r="G71">
-        <v>999</v>
+        <v>889</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>11176717</v>
+        <v>11176724</v>
       </c>
       <c r="B72">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="C72" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E72" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F72">
-        <v>58796</v>
+        <v>58763</v>
       </c>
       <c r="G72">
-        <v>489</v>
+        <v>999</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>11176716</v>
+        <v>11176717</v>
       </c>
       <c r="B73">
-        <v>16668</v>
+        <v>16671</v>
       </c>
       <c r="C73" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D73" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E73" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F73">
-        <v>58781</v>
+        <v>58796</v>
       </c>
       <c r="G73">
-        <v>899</v>
+        <v>489</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>11176612</v>
+        <v>11176716</v>
       </c>
       <c r="B74">
-        <v>16608</v>
+        <v>16668</v>
       </c>
       <c r="C74" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D74" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F74">
-        <v>52575</v>
+        <v>58781</v>
       </c>
       <c r="G74">
-        <v>659</v>
+        <v>899</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>11176610</v>
+        <v>11176612</v>
       </c>
       <c r="B75">
-        <v>16609</v>
+        <v>16608</v>
       </c>
       <c r="C75" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F75">
-        <v>52577</v>
+        <v>52575</v>
       </c>
       <c r="G75">
-        <v>717</v>
+        <v>659</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>11176710</v>
+        <v>11176610</v>
       </c>
       <c r="B76">
-        <v>16664</v>
+        <v>16609</v>
       </c>
       <c r="C76" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D76" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E76" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F76">
-        <v>58791</v>
+        <v>52577</v>
       </c>
       <c r="G76">
-        <v>529</v>
+        <v>717</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>11176701</v>
+        <v>11176710</v>
       </c>
       <c r="B77">
-        <v>16665</v>
+        <v>16664</v>
       </c>
       <c r="C77" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E77" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F77">
-        <v>58792</v>
+        <v>58791</v>
       </c>
       <c r="G77">
-        <v>489</v>
+        <v>529</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>11176702</v>
+        <v>11176701</v>
       </c>
       <c r="B78">
-        <v>16666</v>
+        <v>16665</v>
       </c>
       <c r="C78" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D78" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E78" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F78">
-        <v>58793</v>
+        <v>58792</v>
       </c>
       <c r="G78">
-        <v>459</v>
+        <v>489</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>11176715</v>
+        <v>11176702</v>
       </c>
       <c r="B79">
-        <v>16667</v>
+        <v>16666</v>
       </c>
       <c r="C79" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D79" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E79" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F79">
-        <v>58794</v>
+        <v>58793</v>
       </c>
       <c r="G79">
-        <v>679</v>
+        <v>459</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>11176699</v>
+        <v>11176715</v>
       </c>
       <c r="B80">
-        <v>16663</v>
+        <v>16667</v>
       </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D80" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E80" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F80">
-        <v>58767</v>
+        <v>58794</v>
       </c>
       <c r="G80">
-        <v>499</v>
+        <v>679</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
+        <v>11176699</v>
+      </c>
+      <c r="B81">
+        <v>16663</v>
+      </c>
+      <c r="C81" t="s">
+        <v>125</v>
+      </c>
+      <c r="D81" t="s">
+        <v>126</v>
+      </c>
+      <c r="E81" t="s">
+        <v>126</v>
+      </c>
+      <c r="F81">
+        <v>58767</v>
+      </c>
+      <c r="G81">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82">
         <v>11177607</v>
       </c>
-      <c r="B81">
+      <c r="B82">
         <v>16680</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C82" t="s">
         <v>127</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D82" t="s">
         <v>128</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E82" t="s">
         <v>128</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F82" t="s">
         <v>129</v>
       </c>
-      <c r="G81">
+      <c r="G82">
         <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>1</v>
-      </c>
-      <c r="B82">
-        <v>16729</v>
-      </c>
-      <c r="C82" t="s">
-        <v>130</v>
-      </c>
-      <c r="D82" t="s">
-        <v>131</v>
-      </c>
-      <c r="E82" t="s">
-        <v>131</v>
-      </c>
-      <c r="F82">
-        <v>52617</v>
-      </c>
-      <c r="G82">
-        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -6146,387 +6152,387 @@
         <v>1</v>
       </c>
       <c r="B83">
+        <v>16729</v>
+      </c>
+      <c r="C83" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" t="s">
+        <v>131</v>
+      </c>
+      <c r="E83" t="s">
+        <v>131</v>
+      </c>
+      <c r="F83">
+        <v>52617</v>
+      </c>
+      <c r="G83">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>1</v>
+      </c>
+      <c r="B84">
         <v>16771</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C84" t="s">
         <v>132</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D84" t="s">
         <v>133</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E84" t="s">
         <v>133</v>
       </c>
-      <c r="F83">
+      <c r="F84">
         <v>52615</v>
       </c>
-      <c r="G83">
+      <c r="G84">
         <v>109</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>11176714</v>
-      </c>
-      <c r="B84">
-        <v>16659</v>
-      </c>
-      <c r="C84" t="s">
-        <v>134</v>
-      </c>
-      <c r="D84" t="s">
-        <v>135</v>
-      </c>
-      <c r="E84" t="s">
-        <v>135</v>
-      </c>
-      <c r="F84">
-        <v>52609</v>
-      </c>
-      <c r="G84">
-        <v>677</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>11176719</v>
+        <v>11176714</v>
       </c>
       <c r="B85">
-        <v>16660</v>
+        <v>16659</v>
       </c>
       <c r="C85" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D85" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E85" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F85">
-        <v>52610</v>
+        <v>52609</v>
       </c>
       <c r="G85">
-        <v>739</v>
+        <v>677</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>11176708</v>
+        <v>11176719</v>
       </c>
       <c r="B86">
-        <v>16658</v>
+        <v>16660</v>
       </c>
       <c r="C86" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D86" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E86" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F86">
-        <v>52608</v>
+        <v>52610</v>
       </c>
       <c r="G86">
-        <v>567</v>
+        <v>739</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>11176720</v>
+        <v>11176708</v>
       </c>
       <c r="B87">
-        <v>16661</v>
+        <v>16658</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D87" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E87" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F87">
-        <v>52612</v>
+        <v>52608</v>
       </c>
       <c r="G87">
-        <v>839</v>
+        <v>567</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>11174775</v>
+        <v>11176720</v>
       </c>
       <c r="B88">
-        <v>16551</v>
+        <v>16661</v>
       </c>
       <c r="C88" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D88" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E88" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F88">
-        <v>52596</v>
+        <v>52612</v>
       </c>
       <c r="G88">
-        <v>457</v>
+        <v>839</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>11177276</v>
+        <v>11174775</v>
       </c>
       <c r="B89">
-        <v>16559</v>
+        <v>16551</v>
       </c>
       <c r="C89" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D89" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E89" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F89">
-        <v>52597</v>
+        <v>52596</v>
       </c>
       <c r="G89">
-        <v>689</v>
+        <v>457</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>11174806</v>
+        <v>11177276</v>
       </c>
       <c r="B90">
-        <v>16557</v>
+        <v>16559</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D90" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E90" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F90">
-        <v>52598</v>
+        <v>52597</v>
       </c>
       <c r="G90">
-        <v>729</v>
+        <v>689</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
+        <v>11174806</v>
+      </c>
+      <c r="B91">
+        <v>16557</v>
+      </c>
+      <c r="C91" t="s">
+        <v>146</v>
+      </c>
+      <c r="D91" t="s">
+        <v>147</v>
+      </c>
+      <c r="E91" t="s">
+        <v>147</v>
+      </c>
+      <c r="F91">
+        <v>52598</v>
+      </c>
+      <c r="G91">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92">
         <v>11174811</v>
       </c>
-      <c r="B91">
+      <c r="B92">
         <v>16546</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C92" t="s">
         <v>148</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D92" t="s">
         <v>149</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E92" t="s">
         <v>149</v>
       </c>
-      <c r="F91">
+      <c r="F92">
         <v>52600</v>
       </c>
-      <c r="G91">
+      <c r="G92">
         <v>839</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>1</v>
       </c>
-      <c r="B92">
+      <c r="B93">
         <v>16775</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C93" t="s">
         <v>150</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D93" t="s">
         <v>151</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E93" t="s">
         <v>151</v>
       </c>
-      <c r="F92">
+      <c r="F93">
         <v>52606</v>
       </c>
-      <c r="G92">
+      <c r="G93">
         <v>169</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94">
         <v>11174791</v>
       </c>
-      <c r="B93">
+      <c r="B94">
         <v>16572</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C94" t="s">
         <v>152</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D94" t="s">
         <v>153</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E94" t="s">
         <v>153</v>
       </c>
-      <c r="F93">
+      <c r="F94">
         <v>52582</v>
       </c>
-      <c r="G93">
+      <c r="G94">
         <v>59</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>1</v>
       </c>
-      <c r="B94">
+      <c r="B95">
         <v>16770</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C95" t="s">
         <v>154</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D95" t="s">
         <v>155</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E95" t="s">
         <v>155</v>
       </c>
-      <c r="F94">
+      <c r="F95">
         <v>52616</v>
       </c>
-      <c r="G94">
+      <c r="G95">
         <v>109</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>11174803</v>
-      </c>
-      <c r="B95">
-        <v>16549</v>
-      </c>
-      <c r="C95" t="s">
-        <v>156</v>
-      </c>
-      <c r="D95" t="s">
-        <v>157</v>
-      </c>
-      <c r="E95" t="s">
-        <v>157</v>
-      </c>
-      <c r="F95">
-        <v>52591</v>
-      </c>
-      <c r="G95">
-        <v>1399</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>11174810</v>
+        <v>11174803</v>
       </c>
       <c r="B96">
-        <v>16555</v>
+        <v>16549</v>
       </c>
       <c r="C96" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D96" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E96" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F96">
-        <v>52595</v>
+        <v>52591</v>
       </c>
       <c r="G96">
-        <v>999</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>11174776</v>
+        <v>11174810</v>
       </c>
       <c r="B97">
-        <v>16550</v>
+        <v>16555</v>
       </c>
       <c r="C97" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D97" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E97" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F97">
-        <v>52585</v>
+        <v>52595</v>
       </c>
       <c r="G97">
-        <v>429</v>
+        <v>999</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>11174801</v>
+        <v>11174776</v>
       </c>
       <c r="B98">
-        <v>16548</v>
+        <v>16550</v>
       </c>
       <c r="C98" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D98" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E98" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F98">
-        <v>52586</v>
+        <v>52585</v>
       </c>
       <c r="G98">
-        <v>689</v>
+        <v>429</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>11177275</v>
+        <v>11174801</v>
       </c>
       <c r="B99">
-        <v>16558</v>
+        <v>16548</v>
       </c>
       <c r="C99" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D99" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E99" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F99">
-        <v>52587</v>
+        <v>52586</v>
       </c>
       <c r="G99">
         <v>689</v>
@@ -6534,206 +6540,206 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>11175037</v>
+        <v>11177275</v>
       </c>
       <c r="B100">
-        <v>16573</v>
+        <v>16558</v>
       </c>
       <c r="C100" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D100" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E100" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F100">
-        <v>52588</v>
+        <v>52587</v>
       </c>
       <c r="G100">
-        <v>444</v>
+        <v>689</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
+        <v>11175037</v>
+      </c>
+      <c r="B101">
+        <v>16573</v>
+      </c>
+      <c r="C101" t="s">
+        <v>166</v>
+      </c>
+      <c r="D101" t="s">
+        <v>167</v>
+      </c>
+      <c r="E101" t="s">
+        <v>167</v>
+      </c>
+      <c r="F101">
+        <v>52588</v>
+      </c>
+      <c r="G101">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102">
         <v>11174795</v>
       </c>
-      <c r="B101">
+      <c r="B102">
         <v>16543</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" t="s">
         <v>168</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D102" t="s">
         <v>169</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E102" t="s">
         <v>169</v>
       </c>
-      <c r="F101">
+      <c r="F102">
         <v>52589</v>
       </c>
-      <c r="G101">
+      <c r="G102">
         <v>549</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
         <v>1</v>
       </c>
-      <c r="B102">
+      <c r="B103">
         <v>16769</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C103" t="s">
         <v>170</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D103" t="s">
         <v>171</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E103" t="s">
         <v>171</v>
       </c>
-      <c r="F102">
+      <c r="F103">
         <v>52614</v>
       </c>
-      <c r="G102">
+      <c r="G103">
         <v>109</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>11174779</v>
-      </c>
-      <c r="B103">
-        <v>16540</v>
-      </c>
-      <c r="C103" t="s">
-        <v>172</v>
-      </c>
-      <c r="D103" t="s">
-        <v>173</v>
-      </c>
-      <c r="E103" t="s">
-        <v>173</v>
-      </c>
-      <c r="F103">
-        <v>52584</v>
-      </c>
-      <c r="G103">
-        <v>567</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>11174804</v>
+        <v>11174779</v>
       </c>
       <c r="B104">
-        <v>16541</v>
+        <v>16540</v>
       </c>
       <c r="C104" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D104" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E104" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F104">
-        <v>52593</v>
+        <v>52584</v>
       </c>
       <c r="G104">
-        <v>889</v>
+        <v>567</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>11174798</v>
+        <v>11174804</v>
       </c>
       <c r="B105">
-        <v>16552</v>
+        <v>16541</v>
       </c>
       <c r="C105" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D105" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E105" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F105">
-        <v>52578</v>
+        <v>52593</v>
       </c>
       <c r="G105">
-        <v>649</v>
+        <v>889</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>11174808</v>
+        <v>11174798</v>
       </c>
       <c r="B106">
-        <v>16545</v>
+        <v>16552</v>
       </c>
       <c r="C106" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D106" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E106" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F106">
-        <v>52579</v>
+        <v>52578</v>
       </c>
       <c r="G106">
-        <v>749</v>
+        <v>649</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>11177274</v>
+        <v>11174808</v>
       </c>
       <c r="B107">
-        <v>16547</v>
+        <v>16545</v>
       </c>
       <c r="C107" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D107" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E107" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F107">
-        <v>52580</v>
+        <v>52579</v>
       </c>
       <c r="G107">
-        <v>669</v>
+        <v>749</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>11174800</v>
+        <v>11177274</v>
       </c>
       <c r="B108">
-        <v>16553</v>
+        <v>16547</v>
       </c>
       <c r="C108" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D108" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E108" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F108">
-        <v>52581</v>
+        <v>52580</v>
       </c>
       <c r="G108">
         <v>669</v>
@@ -6741,93 +6747,116 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>11174807</v>
+        <v>11174800</v>
       </c>
       <c r="B109">
-        <v>16554</v>
+        <v>16553</v>
       </c>
       <c r="C109" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E109" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F109">
-        <v>52601</v>
+        <v>52581</v>
       </c>
       <c r="G109">
-        <v>649</v>
+        <v>669</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>11177277</v>
+        <v>11174807</v>
       </c>
       <c r="B110">
-        <v>16544</v>
+        <v>16554</v>
       </c>
       <c r="C110" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D110" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E110" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F110">
-        <v>52602</v>
+        <v>52601</v>
       </c>
       <c r="G110">
-        <v>489</v>
+        <v>649</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>11174790</v>
+        <v>11177277</v>
       </c>
       <c r="B111">
-        <v>16542</v>
+        <v>16544</v>
       </c>
       <c r="C111" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D111" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E111" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F111">
-        <v>52603</v>
+        <v>52602</v>
       </c>
       <c r="G111">
-        <v>349</v>
+        <v>489</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
+        <v>11174790</v>
+      </c>
+      <c r="B112">
+        <v>16542</v>
+      </c>
+      <c r="C112" t="s">
+        <v>188</v>
+      </c>
+      <c r="D112" t="s">
+        <v>189</v>
+      </c>
+      <c r="E112" t="s">
+        <v>189</v>
+      </c>
+      <c r="F112">
+        <v>52603</v>
+      </c>
+      <c r="G112">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113">
         <v>11174799</v>
       </c>
-      <c r="B112">
+      <c r="B113">
         <v>16556</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C113" t="s">
         <v>190</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D113" t="s">
         <v>191</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E113" t="s">
         <v>191</v>
       </c>
-      <c r="F112">
+      <c r="F113">
         <v>52604</v>
       </c>
-      <c r="G112">
+      <c r="G113">
         <v>609</v>
       </c>
     </row>

--- a/Lista_Precios_Base.xlsx
+++ b/Lista_Precios_Base.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CodeBrew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{C71BEC85-4C4D-4198-A748-8E3A4E39F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B02FD59-DF14-45EC-A8BF-C263F1BCFCBE}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{C71BEC85-4C4D-4198-A748-8E3A4E39F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5FFC640-5066-48A9-ADF1-E37FA6B48571}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3777" uniqueCount="1211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="1219">
   <si>
     <t>WC26Stan20IceF</t>
   </si>
@@ -3727,6 +3727,30 @@
   </si>
   <si>
     <t>SII26SSCC16Pony</t>
+  </si>
+  <si>
+    <t>WTBL20SS BEARISTA RESORT BEACH</t>
+  </si>
+  <si>
+    <t>SII26BTL20Resort</t>
+  </si>
+  <si>
+    <t>TMBL16SS BEARISTA RSRT FRNTDSK</t>
+  </si>
+  <si>
+    <t>SII26SS16Resort</t>
+  </si>
+  <si>
+    <t>SS VAC CLD CUP SOFT TOUCH 24OZ LAC CORE FY25</t>
+  </si>
+  <si>
+    <t>SII26SSCC24White</t>
+  </si>
+  <si>
+    <t>Imán México</t>
+  </si>
+  <si>
+    <t>IMÁN MÉXICO</t>
   </si>
 </sst>
 </file>
@@ -3895,8 +3919,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G113" totalsRowShown="0">
-  <autoFilter ref="A1:G113" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G117" totalsRowShown="0">
+  <autoFilter ref="A1:G117" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3FD2C0CF-4866-4870-AD33-E904DA8BA849}" name="SKU INTL"/>
     <tableColumn id="2" xr3:uid="{39846DA6-B590-4416-838E-B359114E50F9}" name="CÓDIGO DIA"/>
@@ -4256,7 +4280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8718E42-507B-44AF-801B-0B0250CAF160}">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" bestFit="1" customWidth="1"/>
@@ -4292,45 +4316,45 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>11176587</v>
+        <v>11179885</v>
       </c>
       <c r="B2">
-        <v>16720</v>
+        <v>16777</v>
       </c>
       <c r="C2" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D2" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E2" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="F2">
-        <v>50740</v>
+        <v>50746</v>
       </c>
       <c r="G2">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1176593</v>
+        <v>11179880</v>
       </c>
       <c r="B3">
-        <v>16793</v>
+        <v>16610</v>
       </c>
       <c r="C3" t="s">
-        <v>1201</v>
+        <v>1213</v>
       </c>
       <c r="D3" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="E3" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="F3">
-        <v>50741</v>
+        <v>50747</v>
       </c>
       <c r="G3">
         <v>649</v>
@@ -4338,830 +4362,830 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>11176592</v>
+        <v>11157547</v>
       </c>
       <c r="B4">
-        <v>16779</v>
+        <v>15857</v>
       </c>
       <c r="C4" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="D4" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
       <c r="E4" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
       <c r="F4">
-        <v>50742</v>
+        <v>58834</v>
       </c>
       <c r="G4">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>11176586</v>
+      <c r="A5" t="s">
+        <v>76</v>
       </c>
       <c r="B5">
-        <v>16719</v>
+        <v>16977</v>
       </c>
       <c r="C5" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="D5" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="E5" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="F5">
-        <v>50743</v>
+        <v>58751</v>
       </c>
       <c r="G5">
-        <v>669</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>11176597</v>
+        <v>11176587</v>
       </c>
       <c r="B6">
-        <v>16784</v>
+        <v>16720</v>
       </c>
       <c r="C6" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="D6" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="E6" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="F6">
-        <v>50745</v>
+        <v>50740</v>
       </c>
       <c r="G6">
-        <v>369</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>11178956</v>
+        <v>1176593</v>
       </c>
       <c r="B7">
-        <v>16916</v>
+        <v>16793</v>
       </c>
       <c r="C7" t="s">
-        <v>1185</v>
+        <v>1201</v>
       </c>
       <c r="D7" t="s">
-        <v>1186</v>
+        <v>1202</v>
       </c>
       <c r="E7" t="s">
-        <v>1186</v>
+        <v>1202</v>
       </c>
       <c r="F7">
-        <v>50735</v>
+        <v>50741</v>
       </c>
       <c r="G7">
-        <v>999</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>11178933</v>
+        <v>11176592</v>
       </c>
       <c r="B8">
-        <v>16881</v>
+        <v>16779</v>
       </c>
       <c r="C8" t="s">
-        <v>1187</v>
+        <v>1203</v>
       </c>
       <c r="D8" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="E8" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="F8">
-        <v>50736</v>
+        <v>50742</v>
       </c>
       <c r="G8">
-        <v>529</v>
+        <v>649</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>11178934</v>
+        <v>11176586</v>
       </c>
       <c r="B9">
-        <v>16884</v>
+        <v>16719</v>
       </c>
       <c r="C9" t="s">
-        <v>1189</v>
+        <v>1205</v>
       </c>
       <c r="D9" t="s">
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="E9" t="s">
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="F9">
-        <v>50737</v>
+        <v>50743</v>
       </c>
       <c r="G9">
-        <v>529</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>11178935</v>
+        <v>11176597</v>
       </c>
       <c r="B10">
-        <v>16920</v>
+        <v>16784</v>
       </c>
       <c r="C10" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="D10" t="s">
-        <v>1192</v>
+        <v>1208</v>
       </c>
       <c r="E10" t="s">
-        <v>1192</v>
+        <v>1208</v>
       </c>
       <c r="F10">
-        <v>50738</v>
+        <v>50745</v>
       </c>
       <c r="G10">
-        <v>459</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>11178941</v>
+        <v>11178956</v>
       </c>
       <c r="B11">
-        <v>16900</v>
+        <v>16916</v>
       </c>
       <c r="C11" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="D11" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="E11" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="F11">
-        <v>50739</v>
+        <v>50735</v>
       </c>
       <c r="G11">
-        <v>649</v>
+        <v>999</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11178917</v>
+        <v>11178933</v>
       </c>
       <c r="B12">
-        <v>16921</v>
+        <v>16881</v>
       </c>
       <c r="C12" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="D12" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
       <c r="E12" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
       <c r="F12">
-        <v>58808</v>
+        <v>50736</v>
       </c>
       <c r="G12">
-        <v>479</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11178969</v>
+        <v>11178934</v>
       </c>
       <c r="B13">
-        <v>16910</v>
+        <v>16884</v>
       </c>
       <c r="C13" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
       <c r="D13" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="E13" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="F13">
-        <v>58827</v>
+        <v>50737</v>
       </c>
       <c r="G13">
-        <v>679</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11178918</v>
+        <v>11178935</v>
       </c>
       <c r="B14">
-        <v>16923</v>
+        <v>16920</v>
       </c>
       <c r="C14" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
       <c r="D14" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="E14" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="F14">
-        <v>58832</v>
+        <v>50738</v>
       </c>
       <c r="G14">
-        <v>489</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>11178946</v>
+        <v>11178941</v>
       </c>
       <c r="B15">
-        <v>16913</v>
+        <v>16900</v>
       </c>
       <c r="C15" t="s">
-        <v>1175</v>
+        <v>1193</v>
       </c>
       <c r="D15" t="s">
-        <v>1176</v>
+        <v>1194</v>
       </c>
       <c r="E15" t="s">
-        <v>1176</v>
+        <v>1194</v>
       </c>
       <c r="F15">
-        <v>58814</v>
+        <v>50739</v>
       </c>
       <c r="G15">
-        <v>689</v>
+        <v>649</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11178973</v>
+        <v>11178917</v>
       </c>
       <c r="B16">
-        <v>16925</v>
+        <v>16921</v>
       </c>
       <c r="C16" t="s">
-        <v>1177</v>
+        <v>1195</v>
       </c>
       <c r="D16" t="s">
-        <v>1178</v>
+        <v>1196</v>
       </c>
       <c r="E16" t="s">
-        <v>1178</v>
+        <v>1196</v>
       </c>
       <c r="F16">
-        <v>58815</v>
+        <v>58808</v>
       </c>
       <c r="G16">
-        <v>649</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>11178959</v>
+        <v>11178969</v>
       </c>
       <c r="B17">
-        <v>16897</v>
+        <v>16910</v>
       </c>
       <c r="C17" t="s">
-        <v>1179</v>
+        <v>1197</v>
       </c>
       <c r="D17" t="s">
-        <v>1180</v>
+        <v>1198</v>
       </c>
       <c r="E17" t="s">
-        <v>1180</v>
+        <v>1198</v>
       </c>
       <c r="F17">
-        <v>58816</v>
+        <v>58827</v>
       </c>
       <c r="G17">
-        <v>659</v>
+        <v>679</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>11178928</v>
+        <v>11178918</v>
       </c>
       <c r="B18">
-        <v>16880</v>
+        <v>16923</v>
       </c>
       <c r="C18" t="s">
-        <v>1181</v>
+        <v>1199</v>
       </c>
       <c r="D18" t="s">
-        <v>1182</v>
+        <v>1200</v>
       </c>
       <c r="E18" t="s">
-        <v>1182</v>
+        <v>1200</v>
       </c>
       <c r="F18">
-        <v>58817</v>
+        <v>58832</v>
       </c>
       <c r="G18">
-        <v>549</v>
+        <v>489</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>11178965</v>
+        <v>11178946</v>
       </c>
       <c r="B19">
-        <v>16904</v>
+        <v>16913</v>
       </c>
       <c r="C19" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="D19" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="E19" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="F19">
-        <v>58818</v>
+        <v>58814</v>
       </c>
       <c r="G19">
-        <v>535</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>11178937</v>
+        <v>11178973</v>
       </c>
       <c r="B20">
-        <v>16901</v>
+        <v>16925</v>
       </c>
       <c r="C20" t="s">
-        <v>1052</v>
+        <v>1177</v>
       </c>
       <c r="D20" t="s">
-        <v>1053</v>
+        <v>1178</v>
       </c>
       <c r="E20" t="s">
-        <v>1053</v>
+        <v>1178</v>
       </c>
       <c r="F20">
-        <v>58819</v>
+        <v>58815</v>
       </c>
       <c r="G20">
-        <v>739</v>
+        <v>649</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>11178948</v>
+        <v>11178959</v>
       </c>
       <c r="B21">
-        <v>16915</v>
+        <v>16897</v>
       </c>
       <c r="C21" t="s">
-        <v>1054</v>
+        <v>1179</v>
       </c>
       <c r="D21" t="s">
-        <v>1055</v>
+        <v>1180</v>
       </c>
       <c r="E21" t="s">
-        <v>1055</v>
+        <v>1180</v>
       </c>
       <c r="F21">
-        <v>58821</v>
+        <v>58816</v>
       </c>
       <c r="G21">
-        <v>899</v>
+        <v>659</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>1</v>
+      <c r="A22">
+        <v>11178928</v>
       </c>
       <c r="B22">
-        <v>16971</v>
+        <v>16880</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>1181</v>
       </c>
       <c r="D22" t="s">
-        <v>1056</v>
+        <v>1182</v>
       </c>
       <c r="E22" t="s">
-        <v>1056</v>
+        <v>1182</v>
       </c>
       <c r="F22">
-        <v>58846</v>
+        <v>58817</v>
       </c>
       <c r="G22">
-        <v>869</v>
+        <v>549</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11178944</v>
+        <v>11178965</v>
       </c>
       <c r="B23">
-        <v>16909</v>
+        <v>16904</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>1183</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>1184</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>1184</v>
       </c>
       <c r="F23">
-        <v>58826</v>
+        <v>58818</v>
       </c>
       <c r="G23">
-        <v>679</v>
+        <v>535</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11178952</v>
+        <v>11178937</v>
       </c>
       <c r="B24">
-        <v>16875</v>
+        <v>16901</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>1052</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>1053</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>1053</v>
       </c>
       <c r="F24">
-        <v>58828</v>
+        <v>58819</v>
       </c>
       <c r="G24">
-        <v>689</v>
+        <v>739</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11178971</v>
+        <v>11178948</v>
       </c>
       <c r="B25">
-        <v>16911</v>
+        <v>16915</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>1054</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>1055</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>1055</v>
       </c>
       <c r="F25">
-        <v>58829</v>
+        <v>58821</v>
       </c>
       <c r="G25">
-        <v>679</v>
+        <v>899</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>11178920</v>
+      <c r="A26" t="s">
+        <v>1</v>
       </c>
       <c r="B26">
-        <v>16902</v>
+        <v>16971</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>1056</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>1056</v>
       </c>
       <c r="F26">
-        <v>58830</v>
+        <v>58846</v>
       </c>
       <c r="G26">
-        <v>369</v>
+        <v>869</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11178922</v>
+        <v>11178944</v>
       </c>
       <c r="B27">
-        <v>16879</v>
+        <v>16909</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>58831</v>
+        <v>58826</v>
       </c>
       <c r="G27">
-        <v>349</v>
+        <v>679</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>11178945</v>
+        <v>11178952</v>
       </c>
       <c r="B28">
-        <v>16924</v>
+        <v>16875</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F28">
-        <v>58835</v>
+        <v>58828</v>
       </c>
       <c r="G28">
-        <v>899</v>
+        <v>689</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11179005</v>
+        <v>11178971</v>
       </c>
       <c r="B29">
-        <v>16906</v>
+        <v>16911</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>58823</v>
+        <v>58829</v>
       </c>
       <c r="G29">
-        <v>889</v>
+        <v>679</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>11178930</v>
+        <v>11178920</v>
       </c>
       <c r="B30">
-        <v>16882</v>
+        <v>16902</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F30">
-        <v>58824</v>
+        <v>58830</v>
       </c>
       <c r="G30">
-        <v>535</v>
+        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11178966</v>
+        <v>11178922</v>
       </c>
       <c r="B31">
-        <v>16905</v>
+        <v>16879</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>58825</v>
+        <v>58831</v>
       </c>
       <c r="G31">
-        <v>535</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11187369</v>
+        <v>11178945</v>
       </c>
       <c r="B32">
-        <v>16908</v>
+        <v>16924</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>58848</v>
+        <v>58835</v>
       </c>
       <c r="G32">
-        <v>869</v>
+        <v>899</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11187370</v>
+        <v>11179005</v>
       </c>
       <c r="B33">
-        <v>16958</v>
+        <v>16906</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F33">
-        <v>58838</v>
+        <v>58823</v>
       </c>
       <c r="G33">
-        <v>679</v>
+        <v>889</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>11187372</v>
+        <v>11178930</v>
       </c>
       <c r="B34">
-        <v>16959</v>
+        <v>16882</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>58839</v>
+        <v>58824</v>
       </c>
       <c r="G34">
-        <v>369</v>
+        <v>535</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>1</v>
+      <c r="A35">
+        <v>11178966</v>
       </c>
       <c r="B35">
-        <v>16978</v>
+        <v>16905</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>58836</v>
+        <v>58825</v>
       </c>
       <c r="G35">
-        <v>189</v>
+        <v>535</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>1</v>
+      <c r="A36">
+        <v>11187369</v>
       </c>
       <c r="B36">
-        <v>16955</v>
+        <v>16908</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F36">
-        <v>58840</v>
+        <v>58848</v>
       </c>
       <c r="G36">
-        <v>1099</v>
+        <v>869</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>1</v>
+      <c r="A37">
+        <v>11187370</v>
       </c>
       <c r="B37">
-        <v>16955</v>
+        <v>16958</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F37">
-        <v>58842</v>
+        <v>58838</v>
       </c>
       <c r="G37">
-        <v>1099</v>
+        <v>679</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>11178949</v>
+        <v>11187372</v>
       </c>
       <c r="B38">
-        <v>16912</v>
+        <v>16959</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F38">
-        <v>58822</v>
+        <v>58839</v>
       </c>
       <c r="G38">
-        <v>679</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>11178957</v>
+      <c r="A39" t="s">
+        <v>1</v>
       </c>
       <c r="B39">
-        <v>16919</v>
+        <v>16978</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F39">
-        <v>58820</v>
+        <v>58836</v>
       </c>
       <c r="G39">
-        <v>999</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -5169,22 +5193,22 @@
         <v>1</v>
       </c>
       <c r="B40">
-        <v>16780</v>
+        <v>16955</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F40">
-        <v>58753</v>
+        <v>58840</v>
       </c>
       <c r="G40">
-        <v>689</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -5192,1600 +5216,1600 @@
         <v>1</v>
       </c>
       <c r="B41">
-        <v>16781</v>
+        <v>16955</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F41">
-        <v>58755</v>
+        <v>58842</v>
       </c>
       <c r="G41">
-        <v>689</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>1</v>
+      <c r="A42">
+        <v>11178949</v>
       </c>
       <c r="B42">
-        <v>16721</v>
+        <v>16912</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F42">
-        <v>58757</v>
+        <v>58822</v>
       </c>
       <c r="G42">
-        <v>649</v>
+        <v>679</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>11179003</v>
+        <v>11178957</v>
       </c>
       <c r="B43">
-        <v>16885</v>
+        <v>16919</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F43">
-        <v>58812</v>
+        <v>58820</v>
       </c>
       <c r="G43">
-        <v>499</v>
+        <v>999</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>11179004</v>
+      <c r="A44" t="s">
+        <v>1</v>
       </c>
       <c r="B44">
-        <v>16899</v>
+        <v>16780</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F44">
-        <v>58813</v>
+        <v>58753</v>
       </c>
       <c r="G44">
-        <v>699</v>
+        <v>689</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>11178954</v>
+      <c r="A45" t="s">
+        <v>1</v>
       </c>
       <c r="B45">
-        <v>16877</v>
+        <v>16781</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F45">
-        <v>58777</v>
+        <v>58755</v>
       </c>
       <c r="G45">
-        <v>719</v>
+        <v>689</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>11178943</v>
+      <c r="A46" t="s">
+        <v>1</v>
       </c>
       <c r="B46">
-        <v>16918</v>
+        <v>16721</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F46">
-        <v>58802</v>
+        <v>58757</v>
       </c>
       <c r="G46">
-        <v>689</v>
+        <v>649</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>11178970</v>
+        <v>11179003</v>
       </c>
       <c r="B47">
-        <v>16896</v>
+        <v>16885</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E47" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F47">
-        <v>58803</v>
+        <v>58812</v>
       </c>
       <c r="G47">
-        <v>699</v>
+        <v>499</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>11178953</v>
+        <v>11179004</v>
       </c>
       <c r="B48">
-        <v>16876</v>
+        <v>16899</v>
       </c>
       <c r="C48" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E48" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F48">
-        <v>58804</v>
+        <v>58813</v>
       </c>
       <c r="G48">
-        <v>689</v>
+        <v>699</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>11178921</v>
+        <v>11178954</v>
       </c>
       <c r="B49">
-        <v>16878</v>
+        <v>16877</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E49" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F49">
-        <v>58805</v>
+        <v>58777</v>
       </c>
       <c r="G49">
-        <v>349</v>
+        <v>719</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>11178926</v>
+        <v>11178943</v>
       </c>
       <c r="B50">
-        <v>16903</v>
+        <v>16918</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F50">
-        <v>58806</v>
+        <v>58802</v>
       </c>
       <c r="G50">
-        <v>529</v>
+        <v>689</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>11178964</v>
+        <v>11178970</v>
       </c>
       <c r="B51">
-        <v>16883</v>
+        <v>16896</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F51">
-        <v>58807</v>
+        <v>58803</v>
       </c>
       <c r="G51">
-        <v>249</v>
+        <v>699</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>11178972</v>
+        <v>11178953</v>
       </c>
       <c r="B52">
-        <v>16917</v>
+        <v>16876</v>
       </c>
       <c r="C52" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E52" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F52">
-        <v>58809</v>
+        <v>58804</v>
       </c>
       <c r="G52">
-        <v>889</v>
+        <v>689</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>11178938</v>
+        <v>11178921</v>
       </c>
       <c r="B53">
-        <v>16898</v>
+        <v>16878</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E53" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F53">
-        <v>58810</v>
+        <v>58805</v>
       </c>
       <c r="G53">
-        <v>599</v>
+        <v>349</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>11178919</v>
+        <v>11178926</v>
       </c>
       <c r="B54">
-        <v>16922</v>
+        <v>16903</v>
       </c>
       <c r="C54" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E54" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F54">
-        <v>58811</v>
+        <v>58806</v>
       </c>
       <c r="G54">
-        <v>439</v>
+        <v>529</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>11176705</v>
+        <v>11178964</v>
       </c>
       <c r="B55">
-        <v>16678</v>
+        <v>16883</v>
       </c>
       <c r="C55" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D55" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>75</v>
-      </c>
-      <c r="F55" t="s">
-        <v>76</v>
+        <v>67</v>
+      </c>
+      <c r="F55">
+        <v>58807</v>
+      </c>
+      <c r="G55">
+        <v>249</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>11176712</v>
+        <v>11178972</v>
       </c>
       <c r="B56">
-        <v>16679</v>
+        <v>16917</v>
       </c>
       <c r="C56" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D56" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
-      </c>
-      <c r="F56" t="s">
-        <v>76</v>
+        <v>69</v>
+      </c>
+      <c r="F56">
+        <v>58809</v>
+      </c>
+      <c r="G56">
+        <v>889</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
+        <v>11178938</v>
+      </c>
+      <c r="B57">
+        <v>16898</v>
+      </c>
+      <c r="C57" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" t="s">
+        <v>71</v>
+      </c>
+      <c r="F57">
+        <v>58810</v>
+      </c>
+      <c r="G57">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>11178919</v>
+      </c>
+      <c r="B58">
+        <v>16922</v>
+      </c>
+      <c r="C58" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" t="s">
+        <v>73</v>
+      </c>
+      <c r="F58">
+        <v>58811</v>
+      </c>
+      <c r="G58">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>11176705</v>
+      </c>
+      <c r="B59">
+        <v>16678</v>
+      </c>
+      <c r="C59" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" t="s">
+        <v>75</v>
+      </c>
+      <c r="F59" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>11176712</v>
+      </c>
+      <c r="B60">
+        <v>16679</v>
+      </c>
+      <c r="C60" t="s">
+        <v>77</v>
+      </c>
+      <c r="D60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" t="s">
+        <v>78</v>
+      </c>
+      <c r="F60" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61">
         <v>11178947</v>
       </c>
-      <c r="B57">
+      <c r="B61">
         <v>16914</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C61" t="s">
         <v>79</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D61" t="s">
         <v>80</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E61" t="s">
         <v>80</v>
       </c>
-      <c r="F57">
+      <c r="F61">
         <v>58795</v>
-      </c>
-      <c r="G57">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>1</v>
-      </c>
-      <c r="B58">
-        <v>16531</v>
-      </c>
-      <c r="C58" t="s">
-        <v>81</v>
-      </c>
-      <c r="D58" t="s">
-        <v>82</v>
-      </c>
-      <c r="E58" t="s">
-        <v>82</v>
-      </c>
-      <c r="F58">
-        <v>58769</v>
-      </c>
-      <c r="G58">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>1</v>
-      </c>
-      <c r="B59">
-        <v>16531</v>
-      </c>
-      <c r="C59" t="s">
-        <v>81</v>
-      </c>
-      <c r="D59" t="s">
-        <v>83</v>
-      </c>
-      <c r="E59" t="s">
-        <v>83</v>
-      </c>
-      <c r="F59">
-        <v>58775</v>
-      </c>
-      <c r="G59">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60">
-        <v>16532</v>
-      </c>
-      <c r="C60" t="s">
-        <v>84</v>
-      </c>
-      <c r="D60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" t="s">
-        <v>85</v>
-      </c>
-      <c r="F60">
-        <v>58771</v>
-      </c>
-      <c r="G60">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61">
-        <v>16532</v>
-      </c>
-      <c r="C61" t="s">
-        <v>84</v>
-      </c>
-      <c r="D61" t="s">
-        <v>86</v>
-      </c>
-      <c r="E61" t="s">
-        <v>86</v>
-      </c>
-      <c r="F61">
-        <v>58773</v>
       </c>
       <c r="G61">
         <v>899</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>11177964</v>
+      <c r="A62" t="s">
+        <v>1</v>
       </c>
       <c r="B62">
-        <v>16607</v>
+        <v>16531</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D62" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F62">
-        <v>58785</v>
+        <v>58769</v>
       </c>
       <c r="G62">
-        <v>669</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>11177937</v>
+      <c r="A63" t="s">
+        <v>1</v>
       </c>
       <c r="B63">
-        <v>16611</v>
+        <v>16531</v>
       </c>
       <c r="C63" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D63" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E63" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F63">
-        <v>58761</v>
+        <v>58775</v>
       </c>
       <c r="G63">
-        <v>539</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>11176721</v>
+      <c r="A64" t="s">
+        <v>1</v>
       </c>
       <c r="B64">
-        <v>16662</v>
+        <v>16532</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E64" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F64">
-        <v>58779</v>
+        <v>58771</v>
       </c>
       <c r="G64">
-        <v>969</v>
+        <v>999</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>11176711</v>
+      <c r="A65" t="s">
+        <v>1</v>
       </c>
       <c r="B65">
-        <v>16669</v>
+        <v>16532</v>
       </c>
       <c r="C65" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D65" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E65" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F65">
-        <v>58765</v>
+        <v>58773</v>
       </c>
       <c r="G65">
-        <v>569</v>
+        <v>899</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>11176700</v>
+        <v>11177964</v>
       </c>
       <c r="B66">
-        <v>16670</v>
+        <v>16607</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D66" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E66" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F66">
-        <v>58783</v>
+        <v>58785</v>
       </c>
       <c r="G66">
-        <v>399</v>
+        <v>669</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>11176703</v>
+        <v>11177937</v>
       </c>
       <c r="B67">
-        <v>16673</v>
+        <v>16611</v>
       </c>
       <c r="C67" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E67" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F67">
-        <v>58797</v>
+        <v>58761</v>
       </c>
       <c r="G67">
-        <v>369</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>11176704</v>
+        <v>11176721</v>
       </c>
       <c r="B68">
-        <v>16674</v>
+        <v>16662</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F68">
-        <v>58798</v>
+        <v>58779</v>
       </c>
       <c r="G68">
-        <v>499</v>
+        <v>969</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>11176722</v>
+        <v>11176711</v>
       </c>
       <c r="B69">
-        <v>16675</v>
+        <v>16669</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D69" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E69" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F69">
-        <v>58799</v>
+        <v>58765</v>
       </c>
       <c r="G69">
-        <v>689</v>
+        <v>569</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>11176718</v>
+        <v>11176700</v>
       </c>
       <c r="B70">
-        <v>16676</v>
+        <v>16670</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F70">
-        <v>58800</v>
+        <v>58783</v>
       </c>
       <c r="G70">
-        <v>669</v>
+        <v>399</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>11176723</v>
+        <v>11176703</v>
       </c>
       <c r="B71">
-        <v>16677</v>
+        <v>16673</v>
       </c>
       <c r="C71" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F71">
-        <v>58801</v>
+        <v>58797</v>
       </c>
       <c r="G71">
-        <v>889</v>
+        <v>369</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>11176724</v>
+        <v>11176704</v>
       </c>
       <c r="B72">
-        <v>16672</v>
+        <v>16674</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D72" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E72" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F72">
-        <v>58763</v>
+        <v>58798</v>
       </c>
       <c r="G72">
-        <v>999</v>
+        <v>499</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>11176717</v>
+        <v>11176722</v>
       </c>
       <c r="B73">
-        <v>16671</v>
+        <v>16675</v>
       </c>
       <c r="C73" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E73" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F73">
-        <v>58796</v>
+        <v>58799</v>
       </c>
       <c r="G73">
-        <v>489</v>
+        <v>689</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>11176716</v>
+        <v>11176718</v>
       </c>
       <c r="B74">
-        <v>16668</v>
+        <v>16676</v>
       </c>
       <c r="C74" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E74" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F74">
-        <v>58781</v>
+        <v>58800</v>
       </c>
       <c r="G74">
-        <v>899</v>
+        <v>669</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>11176612</v>
+        <v>11176723</v>
       </c>
       <c r="B75">
-        <v>16608</v>
+        <v>16677</v>
       </c>
       <c r="C75" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F75">
-        <v>52575</v>
+        <v>58801</v>
       </c>
       <c r="G75">
-        <v>659</v>
+        <v>889</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>11176610</v>
+        <v>11176724</v>
       </c>
       <c r="B76">
-        <v>16609</v>
+        <v>16672</v>
       </c>
       <c r="C76" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E76" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F76">
-        <v>52577</v>
+        <v>58763</v>
       </c>
       <c r="G76">
-        <v>717</v>
+        <v>999</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>11176710</v>
+        <v>11176717</v>
       </c>
       <c r="B77">
-        <v>16664</v>
+        <v>16671</v>
       </c>
       <c r="C77" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D77" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E77" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F77">
-        <v>58791</v>
+        <v>58796</v>
       </c>
       <c r="G77">
-        <v>529</v>
+        <v>489</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>11176701</v>
+        <v>11176716</v>
       </c>
       <c r="B78">
-        <v>16665</v>
+        <v>16668</v>
       </c>
       <c r="C78" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E78" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F78">
-        <v>58792</v>
+        <v>58781</v>
       </c>
       <c r="G78">
-        <v>489</v>
+        <v>899</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>11176702</v>
+        <v>11176612</v>
       </c>
       <c r="B79">
-        <v>16666</v>
+        <v>16608</v>
       </c>
       <c r="C79" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D79" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F79">
-        <v>58793</v>
+        <v>52575</v>
       </c>
       <c r="G79">
-        <v>459</v>
+        <v>659</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>11176715</v>
+        <v>11176610</v>
       </c>
       <c r="B80">
-        <v>16667</v>
+        <v>16609</v>
       </c>
       <c r="C80" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D80" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E80" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F80">
-        <v>58794</v>
+        <v>52577</v>
       </c>
       <c r="G80">
-        <v>679</v>
+        <v>717</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>11176699</v>
+        <v>11176710</v>
       </c>
       <c r="B81">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D81" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E81" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F81">
-        <v>58767</v>
+        <v>58791</v>
       </c>
       <c r="G81">
-        <v>499</v>
+        <v>529</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>11177607</v>
+        <v>11176701</v>
       </c>
       <c r="B82">
-        <v>16680</v>
+        <v>16665</v>
       </c>
       <c r="C82" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D82" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E82" t="s">
-        <v>128</v>
-      </c>
-      <c r="F82" t="s">
-        <v>129</v>
+        <v>120</v>
+      </c>
+      <c r="F82">
+        <v>58792</v>
       </c>
       <c r="G82">
-        <v>32</v>
+        <v>489</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>1</v>
+      <c r="A83">
+        <v>11176702</v>
       </c>
       <c r="B83">
-        <v>16729</v>
+        <v>16666</v>
       </c>
       <c r="C83" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D83" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E83" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F83">
-        <v>52617</v>
+        <v>58793</v>
       </c>
       <c r="G83">
-        <v>59</v>
+        <v>459</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>1</v>
+      <c r="A84">
+        <v>11176715</v>
       </c>
       <c r="B84">
-        <v>16771</v>
+        <v>16667</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D84" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E84" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F84">
-        <v>52615</v>
+        <v>58794</v>
       </c>
       <c r="G84">
-        <v>109</v>
+        <v>679</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>11176714</v>
+        <v>11176699</v>
       </c>
       <c r="B85">
-        <v>16659</v>
+        <v>16663</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D85" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E85" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F85">
-        <v>52609</v>
+        <v>58767</v>
       </c>
       <c r="G85">
-        <v>677</v>
+        <v>499</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>11176719</v>
+        <v>11177607</v>
       </c>
       <c r="B86">
-        <v>16660</v>
+        <v>16680</v>
       </c>
       <c r="C86" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D86" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E86" t="s">
-        <v>137</v>
-      </c>
-      <c r="F86">
-        <v>52610</v>
+        <v>128</v>
+      </c>
+      <c r="F86" t="s">
+        <v>129</v>
       </c>
       <c r="G86">
-        <v>739</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>11176708</v>
+      <c r="A87" t="s">
+        <v>1</v>
       </c>
       <c r="B87">
-        <v>16658</v>
+        <v>16729</v>
       </c>
       <c r="C87" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E87" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F87">
-        <v>52608</v>
+        <v>52617</v>
       </c>
       <c r="G87">
-        <v>567</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>11176720</v>
+      <c r="A88" t="s">
+        <v>1</v>
       </c>
       <c r="B88">
-        <v>16661</v>
+        <v>16771</v>
       </c>
       <c r="C88" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D88" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E88" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F88">
-        <v>52612</v>
+        <v>52615</v>
       </c>
       <c r="G88">
-        <v>839</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>11174775</v>
+        <v>11176714</v>
       </c>
       <c r="B89">
-        <v>16551</v>
+        <v>16659</v>
       </c>
       <c r="C89" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D89" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E89" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F89">
-        <v>52596</v>
+        <v>52609</v>
       </c>
       <c r="G89">
-        <v>457</v>
+        <v>677</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>11177276</v>
+        <v>11176719</v>
       </c>
       <c r="B90">
-        <v>16559</v>
+        <v>16660</v>
       </c>
       <c r="C90" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D90" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E90" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F90">
-        <v>52597</v>
+        <v>52610</v>
       </c>
       <c r="G90">
-        <v>689</v>
+        <v>739</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>11174806</v>
+        <v>11176708</v>
       </c>
       <c r="B91">
-        <v>16557</v>
+        <v>16658</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E91" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F91">
-        <v>52598</v>
+        <v>52608</v>
       </c>
       <c r="G91">
-        <v>729</v>
+        <v>567</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>11174811</v>
+        <v>11176720</v>
       </c>
       <c r="B92">
-        <v>16546</v>
+        <v>16661</v>
       </c>
       <c r="C92" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D92" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E92" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F92">
-        <v>52600</v>
+        <v>52612</v>
       </c>
       <c r="G92">
         <v>839</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>1</v>
+      <c r="A93">
+        <v>11174775</v>
       </c>
       <c r="B93">
-        <v>16775</v>
+        <v>16551</v>
       </c>
       <c r="C93" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D93" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E93" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F93">
-        <v>52606</v>
+        <v>52596</v>
       </c>
       <c r="G93">
-        <v>169</v>
+        <v>457</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>11174791</v>
+        <v>11177276</v>
       </c>
       <c r="B94">
-        <v>16572</v>
+        <v>16559</v>
       </c>
       <c r="C94" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D94" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E94" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F94">
-        <v>52582</v>
+        <v>52597</v>
       </c>
       <c r="G94">
-        <v>59</v>
+        <v>689</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>1</v>
+      <c r="A95">
+        <v>11174806</v>
       </c>
       <c r="B95">
-        <v>16770</v>
+        <v>16557</v>
       </c>
       <c r="C95" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D95" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E95" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F95">
-        <v>52616</v>
+        <v>52598</v>
       </c>
       <c r="G95">
-        <v>109</v>
+        <v>729</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>11174803</v>
+        <v>11174811</v>
       </c>
       <c r="B96">
-        <v>16549</v>
+        <v>16546</v>
       </c>
       <c r="C96" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D96" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E96" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F96">
-        <v>52591</v>
+        <v>52600</v>
       </c>
       <c r="G96">
-        <v>1399</v>
+        <v>839</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>11174810</v>
+      <c r="A97" t="s">
+        <v>1</v>
       </c>
       <c r="B97">
-        <v>16555</v>
+        <v>16775</v>
       </c>
       <c r="C97" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D97" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E97" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F97">
-        <v>52595</v>
+        <v>52606</v>
       </c>
       <c r="G97">
-        <v>999</v>
+        <v>169</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>11174776</v>
+        <v>11174791</v>
       </c>
       <c r="B98">
-        <v>16550</v>
+        <v>16572</v>
       </c>
       <c r="C98" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D98" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E98" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F98">
-        <v>52585</v>
+        <v>52582</v>
       </c>
       <c r="G98">
-        <v>429</v>
+        <v>59</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>11174801</v>
+      <c r="A99" t="s">
+        <v>1</v>
       </c>
       <c r="B99">
-        <v>16548</v>
+        <v>16770</v>
       </c>
       <c r="C99" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D99" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E99" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F99">
-        <v>52586</v>
+        <v>52616</v>
       </c>
       <c r="G99">
-        <v>689</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>11177275</v>
+        <v>11174803</v>
       </c>
       <c r="B100">
-        <v>16558</v>
+        <v>16549</v>
       </c>
       <c r="C100" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D100" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E100" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F100">
-        <v>52587</v>
+        <v>52591</v>
       </c>
       <c r="G100">
-        <v>689</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>11175037</v>
+        <v>11174810</v>
       </c>
       <c r="B101">
-        <v>16573</v>
+        <v>16555</v>
       </c>
       <c r="C101" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D101" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E101" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F101">
-        <v>52588</v>
+        <v>52595</v>
       </c>
       <c r="G101">
-        <v>444</v>
+        <v>999</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>11174795</v>
+        <v>11174776</v>
       </c>
       <c r="B102">
-        <v>16543</v>
+        <v>16550</v>
       </c>
       <c r="C102" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D102" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E102" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F102">
-        <v>52589</v>
+        <v>52585</v>
       </c>
       <c r="G102">
-        <v>549</v>
+        <v>429</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>1</v>
+      <c r="A103">
+        <v>11174801</v>
       </c>
       <c r="B103">
-        <v>16769</v>
+        <v>16548</v>
       </c>
       <c r="C103" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D103" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E103" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F103">
-        <v>52614</v>
+        <v>52586</v>
       </c>
       <c r="G103">
-        <v>109</v>
+        <v>689</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>11174779</v>
+        <v>11177275</v>
       </c>
       <c r="B104">
-        <v>16540</v>
+        <v>16558</v>
       </c>
       <c r="C104" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D104" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E104" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F104">
-        <v>52584</v>
+        <v>52587</v>
       </c>
       <c r="G104">
-        <v>567</v>
+        <v>689</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>11174804</v>
+        <v>11175037</v>
       </c>
       <c r="B105">
-        <v>16541</v>
+        <v>16573</v>
       </c>
       <c r="C105" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D105" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E105" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F105">
-        <v>52593</v>
+        <v>52588</v>
       </c>
       <c r="G105">
-        <v>889</v>
+        <v>444</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>11174798</v>
+        <v>11174795</v>
       </c>
       <c r="B106">
-        <v>16552</v>
+        <v>16543</v>
       </c>
       <c r="C106" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D106" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E106" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F106">
-        <v>52578</v>
+        <v>52589</v>
       </c>
       <c r="G106">
-        <v>649</v>
+        <v>549</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>11174808</v>
+      <c r="A107" t="s">
+        <v>1</v>
       </c>
       <c r="B107">
-        <v>16545</v>
+        <v>16769</v>
       </c>
       <c r="C107" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E107" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F107">
-        <v>52579</v>
+        <v>52614</v>
       </c>
       <c r="G107">
-        <v>749</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>11177274</v>
+        <v>11174779</v>
       </c>
       <c r="B108">
-        <v>16547</v>
+        <v>16540</v>
       </c>
       <c r="C108" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E108" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F108">
-        <v>52580</v>
+        <v>52584</v>
       </c>
       <c r="G108">
-        <v>669</v>
+        <v>567</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>11174800</v>
+        <v>11174804</v>
       </c>
       <c r="B109">
-        <v>16553</v>
+        <v>16541</v>
       </c>
       <c r="C109" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D109" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E109" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F109">
-        <v>52581</v>
+        <v>52593</v>
       </c>
       <c r="G109">
-        <v>669</v>
+        <v>889</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>11174807</v>
+        <v>11174798</v>
       </c>
       <c r="B110">
-        <v>16554</v>
+        <v>16552</v>
       </c>
       <c r="C110" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D110" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E110" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F110">
-        <v>52601</v>
+        <v>52578</v>
       </c>
       <c r="G110">
         <v>649</v>
@@ -6793,70 +6817,162 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>11177277</v>
+        <v>11174808</v>
       </c>
       <c r="B111">
-        <v>16544</v>
+        <v>16545</v>
       </c>
       <c r="C111" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D111" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E111" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F111">
-        <v>52602</v>
+        <v>52579</v>
       </c>
       <c r="G111">
-        <v>489</v>
+        <v>749</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>11174790</v>
+        <v>11177274</v>
       </c>
       <c r="B112">
-        <v>16542</v>
+        <v>16547</v>
       </c>
       <c r="C112" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D112" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E112" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F112">
-        <v>52603</v>
+        <v>52580</v>
       </c>
       <c r="G112">
-        <v>349</v>
+        <v>669</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113">
+        <v>11174800</v>
+      </c>
+      <c r="B113">
+        <v>16553</v>
+      </c>
+      <c r="C113" t="s">
+        <v>182</v>
+      </c>
+      <c r="D113" t="s">
+        <v>183</v>
+      </c>
+      <c r="E113" t="s">
+        <v>183</v>
+      </c>
+      <c r="F113">
+        <v>52581</v>
+      </c>
+      <c r="G113">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>11174807</v>
+      </c>
+      <c r="B114">
+        <v>16554</v>
+      </c>
+      <c r="C114" t="s">
+        <v>184</v>
+      </c>
+      <c r="D114" t="s">
+        <v>185</v>
+      </c>
+      <c r="E114" t="s">
+        <v>185</v>
+      </c>
+      <c r="F114">
+        <v>52601</v>
+      </c>
+      <c r="G114">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>11177277</v>
+      </c>
+      <c r="B115">
+        <v>16544</v>
+      </c>
+      <c r="C115" t="s">
+        <v>186</v>
+      </c>
+      <c r="D115" t="s">
+        <v>187</v>
+      </c>
+      <c r="E115" t="s">
+        <v>187</v>
+      </c>
+      <c r="F115">
+        <v>52602</v>
+      </c>
+      <c r="G115">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>11174790</v>
+      </c>
+      <c r="B116">
+        <v>16542</v>
+      </c>
+      <c r="C116" t="s">
+        <v>188</v>
+      </c>
+      <c r="D116" t="s">
+        <v>189</v>
+      </c>
+      <c r="E116" t="s">
+        <v>189</v>
+      </c>
+      <c r="F116">
+        <v>52603</v>
+      </c>
+      <c r="G116">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117">
         <v>11174799</v>
       </c>
-      <c r="B113">
+      <c r="B117">
         <v>16556</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C117" t="s">
         <v>190</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D117" t="s">
         <v>191</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E117" t="s">
         <v>191</v>
       </c>
-      <c r="F113">
+      <c r="F117">
         <v>52604</v>
       </c>
-      <c r="G113">
+      <c r="G117">
         <v>609</v>
       </c>
     </row>

--- a/Lista_Precios_Base.xlsx
+++ b/Lista_Precios_Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/GitHub/CodeBrew/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{C71BEC85-4C4D-4198-A748-8E3A4E39F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5FFC640-5066-48A9-ADF1-E37FA6B48571}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{C71BEC85-4C4D-4198-A748-8E3A4E39F792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE435291-95A0-48F2-990B-6B62E03D74AD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="1219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3802" uniqueCount="1227">
   <si>
     <t>WC26Stan20IceF</t>
   </si>
@@ -3751,6 +3751,30 @@
   </si>
   <si>
     <t>IMÁN MÉXICO</t>
+  </si>
+  <si>
+    <t>SS VAC WTR BTL TWIST TO SIP 20OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>SII26BTLSS20</t>
+  </si>
+  <si>
+    <t>SS VAC TMBLR PULL OUT HANDLE 20OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>SII26SS20Hand</t>
+  </si>
+  <si>
+    <t>SS TMBLR CHARM 12OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>SII26SS12Charm</t>
+  </si>
+  <si>
+    <t>SS TMBLR PLEATED 16OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>SII26SS16Pleat</t>
   </si>
 </sst>
 </file>
@@ -3919,8 +3943,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G117" totalsRowShown="0">
-  <autoFilter ref="A1:G117" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G121" totalsRowShown="0">
+  <autoFilter ref="A1:G121" xr:uid="{DCC0127D-E773-4753-9E86-7B8EA81062F2}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3FD2C0CF-4866-4870-AD33-E904DA8BA849}" name="SKU INTL"/>
     <tableColumn id="2" xr3:uid="{39846DA6-B590-4416-838E-B359114E50F9}" name="CÓDIGO DIA"/>
@@ -4280,7 +4304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8718E42-507B-44AF-801B-0B0250CAF160}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" bestFit="1" customWidth="1"/>
@@ -4316,22 +4340,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>11179885</v>
+        <v>11186659</v>
       </c>
       <c r="B2">
-        <v>16777</v>
+        <v>16999</v>
       </c>
       <c r="C2" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="D2" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="E2" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="F2">
-        <v>50746</v>
+        <v>50754</v>
       </c>
       <c r="G2">
         <v>689</v>
@@ -4339,114 +4363,114 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>11179880</v>
+        <v>11186658</v>
       </c>
       <c r="B3">
-        <v>16610</v>
+        <v>16998</v>
       </c>
       <c r="C3" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="D3" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="E3" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="F3">
-        <v>50747</v>
+        <v>50753</v>
       </c>
       <c r="G3">
-        <v>649</v>
+        <v>679</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>11157547</v>
+        <v>11186646</v>
       </c>
       <c r="B4">
-        <v>15857</v>
+        <v>16997</v>
       </c>
       <c r="C4" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="D4" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="E4" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="F4">
-        <v>58834</v>
+        <v>50751</v>
       </c>
       <c r="G4">
-        <v>689</v>
+        <v>679</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>76</v>
+      <c r="A5">
+        <v>11186650</v>
       </c>
       <c r="B5">
-        <v>16977</v>
+        <v>16995</v>
       </c>
       <c r="C5" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="D5" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="E5" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="F5">
-        <v>58751</v>
+        <v>50755</v>
       </c>
       <c r="G5">
-        <v>179</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>11176587</v>
+        <v>11179885</v>
       </c>
       <c r="B6">
-        <v>16720</v>
+        <v>16777</v>
       </c>
       <c r="C6" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D6" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E6" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="F6">
-        <v>50740</v>
+        <v>50746</v>
       </c>
       <c r="G6">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1176593</v>
+        <v>11179880</v>
       </c>
       <c r="B7">
-        <v>16793</v>
+        <v>16610</v>
       </c>
       <c r="C7" t="s">
-        <v>1201</v>
+        <v>1213</v>
       </c>
       <c r="D7" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="E7" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="F7">
-        <v>50741</v>
+        <v>50747</v>
       </c>
       <c r="G7">
         <v>649</v>
@@ -4454,830 +4478,830 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>11176592</v>
+        <v>11157547</v>
       </c>
       <c r="B8">
-        <v>16779</v>
+        <v>15857</v>
       </c>
       <c r="C8" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="D8" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
       <c r="E8" t="s">
-        <v>1204</v>
+        <v>1216</v>
       </c>
       <c r="F8">
-        <v>50742</v>
+        <v>58834</v>
       </c>
       <c r="G8">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>11176586</v>
+      <c r="A9" t="s">
+        <v>76</v>
       </c>
       <c r="B9">
-        <v>16719</v>
+        <v>16977</v>
       </c>
       <c r="C9" t="s">
-        <v>1205</v>
+        <v>1217</v>
       </c>
       <c r="D9" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="E9" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="F9">
-        <v>50743</v>
+        <v>58751</v>
       </c>
       <c r="G9">
-        <v>669</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>11176597</v>
+        <v>11176587</v>
       </c>
       <c r="B10">
-        <v>16784</v>
+        <v>16720</v>
       </c>
       <c r="C10" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="D10" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="E10" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="F10">
-        <v>50745</v>
+        <v>50740</v>
       </c>
       <c r="G10">
-        <v>369</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>11178956</v>
+        <v>1176593</v>
       </c>
       <c r="B11">
-        <v>16916</v>
+        <v>16793</v>
       </c>
       <c r="C11" t="s">
-        <v>1185</v>
+        <v>1201</v>
       </c>
       <c r="D11" t="s">
-        <v>1186</v>
+        <v>1202</v>
       </c>
       <c r="E11" t="s">
-        <v>1186</v>
+        <v>1202</v>
       </c>
       <c r="F11">
-        <v>50735</v>
+        <v>50741</v>
       </c>
       <c r="G11">
-        <v>999</v>
+        <v>649</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11178933</v>
+        <v>11176592</v>
       </c>
       <c r="B12">
-        <v>16881</v>
+        <v>16779</v>
       </c>
       <c r="C12" t="s">
-        <v>1187</v>
+        <v>1203</v>
       </c>
       <c r="D12" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="E12" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="F12">
-        <v>50736</v>
+        <v>50742</v>
       </c>
       <c r="G12">
-        <v>529</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11178934</v>
+        <v>11176586</v>
       </c>
       <c r="B13">
-        <v>16884</v>
+        <v>16719</v>
       </c>
       <c r="C13" t="s">
-        <v>1189</v>
+        <v>1205</v>
       </c>
       <c r="D13" t="s">
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="E13" t="s">
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="F13">
-        <v>50737</v>
+        <v>50743</v>
       </c>
       <c r="G13">
-        <v>529</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11178935</v>
+        <v>11176597</v>
       </c>
       <c r="B14">
-        <v>16920</v>
+        <v>16784</v>
       </c>
       <c r="C14" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="D14" t="s">
-        <v>1192</v>
+        <v>1208</v>
       </c>
       <c r="E14" t="s">
-        <v>1192</v>
+        <v>1208</v>
       </c>
       <c r="F14">
-        <v>50738</v>
+        <v>50745</v>
       </c>
       <c r="G14">
-        <v>459</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>11178941</v>
+        <v>11178956</v>
       </c>
       <c r="B15">
-        <v>16900</v>
+        <v>16916</v>
       </c>
       <c r="C15" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="D15" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="E15" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="F15">
-        <v>50739</v>
+        <v>50735</v>
       </c>
       <c r="G15">
-        <v>649</v>
+        <v>999</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11178917</v>
+        <v>11178933</v>
       </c>
       <c r="B16">
-        <v>16921</v>
+        <v>16881</v>
       </c>
       <c r="C16" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="D16" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
       <c r="F16">
-        <v>58808</v>
+        <v>50736</v>
       </c>
       <c r="G16">
-        <v>479</v>
+        <v>529</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>11178969</v>
+        <v>11178934</v>
       </c>
       <c r="B17">
-        <v>16910</v>
+        <v>16884</v>
       </c>
       <c r="C17" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
       <c r="D17" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="E17" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="F17">
-        <v>58827</v>
+        <v>50737</v>
       </c>
       <c r="G17">
-        <v>679</v>
+        <v>529</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>11178918</v>
+        <v>11178935</v>
       </c>
       <c r="B18">
-        <v>16923</v>
+        <v>16920</v>
       </c>
       <c r="C18" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
       <c r="D18" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="E18" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="F18">
-        <v>58832</v>
+        <v>50738</v>
       </c>
       <c r="G18">
-        <v>489</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>11178946</v>
+        <v>11178941</v>
       </c>
       <c r="B19">
-        <v>16913</v>
+        <v>16900</v>
       </c>
       <c r="C19" t="s">
-        <v>1175</v>
+        <v>1193</v>
       </c>
       <c r="D19" t="s">
-        <v>1176</v>
+        <v>1194</v>
       </c>
       <c r="E19" t="s">
-        <v>1176</v>
+        <v>1194</v>
       </c>
       <c r="F19">
-        <v>58814</v>
+        <v>50739</v>
       </c>
       <c r="G19">
-        <v>689</v>
+        <v>649</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>11178973</v>
+        <v>11178917</v>
       </c>
       <c r="B20">
-        <v>16925</v>
+        <v>16921</v>
       </c>
       <c r="C20" t="s">
-        <v>1177</v>
+        <v>1195</v>
       </c>
       <c r="D20" t="s">
-        <v>1178</v>
+        <v>1196</v>
       </c>
       <c r="E20" t="s">
-        <v>1178</v>
+        <v>1196</v>
       </c>
       <c r="F20">
-        <v>58815</v>
+        <v>58808</v>
       </c>
       <c r="G20">
-        <v>649</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>11178959</v>
+        <v>11178969</v>
       </c>
       <c r="B21">
-        <v>16897</v>
+        <v>16910</v>
       </c>
       <c r="C21" t="s">
-        <v>1179</v>
+        <v>1197</v>
       </c>
       <c r="D21" t="s">
-        <v>1180</v>
+        <v>1198</v>
       </c>
       <c r="E21" t="s">
-        <v>1180</v>
+        <v>1198</v>
       </c>
       <c r="F21">
-        <v>58816</v>
+        <v>58827</v>
       </c>
       <c r="G21">
-        <v>659</v>
+        <v>679</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>11178928</v>
+        <v>11178918</v>
       </c>
       <c r="B22">
-        <v>16880</v>
+        <v>16923</v>
       </c>
       <c r="C22" t="s">
-        <v>1181</v>
+        <v>1199</v>
       </c>
       <c r="D22" t="s">
-        <v>1182</v>
+        <v>1200</v>
       </c>
       <c r="E22" t="s">
-        <v>1182</v>
+        <v>1200</v>
       </c>
       <c r="F22">
-        <v>58817</v>
+        <v>58832</v>
       </c>
       <c r="G22">
-        <v>549</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11178965</v>
+        <v>11178946</v>
       </c>
       <c r="B23">
-        <v>16904</v>
+        <v>16913</v>
       </c>
       <c r="C23" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="D23" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="E23" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="F23">
-        <v>58818</v>
+        <v>58814</v>
       </c>
       <c r="G23">
-        <v>535</v>
+        <v>689</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11178937</v>
+        <v>11178973</v>
       </c>
       <c r="B24">
-        <v>16901</v>
+        <v>16925</v>
       </c>
       <c r="C24" t="s">
-        <v>1052</v>
+        <v>1177</v>
       </c>
       <c r="D24" t="s">
-        <v>1053</v>
+        <v>1178</v>
       </c>
       <c r="E24" t="s">
-        <v>1053</v>
+        <v>1178</v>
       </c>
       <c r="F24">
-        <v>58819</v>
+        <v>58815</v>
       </c>
       <c r="G24">
-        <v>739</v>
+        <v>649</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11178948</v>
+        <v>11178959</v>
       </c>
       <c r="B25">
-        <v>16915</v>
+        <v>16897</v>
       </c>
       <c r="C25" t="s">
-        <v>1054</v>
+        <v>1179</v>
       </c>
       <c r="D25" t="s">
-        <v>1055</v>
+        <v>1180</v>
       </c>
       <c r="E25" t="s">
-        <v>1055</v>
+        <v>1180</v>
       </c>
       <c r="F25">
-        <v>58821</v>
+        <v>58816</v>
       </c>
       <c r="G25">
-        <v>899</v>
+        <v>659</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>1</v>
+      <c r="A26">
+        <v>11178928</v>
       </c>
       <c r="B26">
-        <v>16971</v>
+        <v>16880</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>1181</v>
       </c>
       <c r="D26" t="s">
-        <v>1056</v>
+        <v>1182</v>
       </c>
       <c r="E26" t="s">
-        <v>1056</v>
+        <v>1182</v>
       </c>
       <c r="F26">
-        <v>58846</v>
+        <v>58817</v>
       </c>
       <c r="G26">
-        <v>869</v>
+        <v>549</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11178944</v>
+        <v>11178965</v>
       </c>
       <c r="B27">
-        <v>16909</v>
+        <v>16904</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>1183</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>1184</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>1184</v>
       </c>
       <c r="F27">
-        <v>58826</v>
+        <v>58818</v>
       </c>
       <c r="G27">
-        <v>679</v>
+        <v>535</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>11178952</v>
+        <v>11178937</v>
       </c>
       <c r="B28">
-        <v>16875</v>
+        <v>16901</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>1052</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>1053</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>1053</v>
       </c>
       <c r="F28">
-        <v>58828</v>
+        <v>58819</v>
       </c>
       <c r="G28">
-        <v>689</v>
+        <v>739</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11178971</v>
+        <v>11178948</v>
       </c>
       <c r="B29">
-        <v>16911</v>
+        <v>16915</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>1054</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>1055</v>
       </c>
       <c r="E29" t="s">
-        <v>16</v>
+        <v>1055</v>
       </c>
       <c r="F29">
-        <v>58829</v>
+        <v>58821</v>
       </c>
       <c r="G29">
-        <v>679</v>
+        <v>899</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>11178920</v>
+      <c r="A30" t="s">
+        <v>1</v>
       </c>
       <c r="B30">
-        <v>16902</v>
+        <v>16971</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>1056</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>1056</v>
       </c>
       <c r="F30">
-        <v>58830</v>
+        <v>58846</v>
       </c>
       <c r="G30">
-        <v>369</v>
+        <v>869</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11178922</v>
+        <v>11178944</v>
       </c>
       <c r="B31">
-        <v>16879</v>
+        <v>16909</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F31">
-        <v>58831</v>
+        <v>58826</v>
       </c>
       <c r="G31">
-        <v>349</v>
+        <v>679</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11178945</v>
+        <v>11178952</v>
       </c>
       <c r="B32">
-        <v>16924</v>
+        <v>16875</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F32">
-        <v>58835</v>
+        <v>58828</v>
       </c>
       <c r="G32">
-        <v>899</v>
+        <v>689</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11179005</v>
+        <v>11178971</v>
       </c>
       <c r="B33">
-        <v>16906</v>
+        <v>16911</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F33">
-        <v>58823</v>
+        <v>58829</v>
       </c>
       <c r="G33">
-        <v>889</v>
+        <v>679</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>11178930</v>
+        <v>11178920</v>
       </c>
       <c r="B34">
-        <v>16882</v>
+        <v>16902</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F34">
-        <v>58824</v>
+        <v>58830</v>
       </c>
       <c r="G34">
-        <v>535</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>11178966</v>
+        <v>11178922</v>
       </c>
       <c r="B35">
-        <v>16905</v>
+        <v>16879</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F35">
-        <v>58825</v>
+        <v>58831</v>
       </c>
       <c r="G35">
-        <v>535</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>11187369</v>
+        <v>11178945</v>
       </c>
       <c r="B36">
-        <v>16908</v>
+        <v>16924</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>58848</v>
+        <v>58835</v>
       </c>
       <c r="G36">
-        <v>869</v>
+        <v>899</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>11187370</v>
+        <v>11179005</v>
       </c>
       <c r="B37">
-        <v>16958</v>
+        <v>16906</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F37">
-        <v>58838</v>
+        <v>58823</v>
       </c>
       <c r="G37">
-        <v>679</v>
+        <v>889</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>11187372</v>
+        <v>11178930</v>
       </c>
       <c r="B38">
-        <v>16959</v>
+        <v>16882</v>
       </c>
       <c r="C38" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F38">
-        <v>58839</v>
+        <v>58824</v>
       </c>
       <c r="G38">
-        <v>369</v>
+        <v>535</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>1</v>
+      <c r="A39">
+        <v>11178966</v>
       </c>
       <c r="B39">
-        <v>16978</v>
+        <v>16905</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F39">
-        <v>58836</v>
+        <v>58825</v>
       </c>
       <c r="G39">
-        <v>189</v>
+        <v>535</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>1</v>
+      <c r="A40">
+        <v>11187369</v>
       </c>
       <c r="B40">
-        <v>16955</v>
+        <v>16908</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F40">
-        <v>58840</v>
+        <v>58848</v>
       </c>
       <c r="G40">
-        <v>1099</v>
+        <v>869</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>1</v>
+      <c r="A41">
+        <v>11187370</v>
       </c>
       <c r="B41">
-        <v>16955</v>
+        <v>16958</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F41">
-        <v>58842</v>
+        <v>58838</v>
       </c>
       <c r="G41">
-        <v>1099</v>
+        <v>679</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>11178949</v>
+        <v>11187372</v>
       </c>
       <c r="B42">
-        <v>16912</v>
+        <v>16959</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E42" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F42">
-        <v>58822</v>
+        <v>58839</v>
       </c>
       <c r="G42">
-        <v>679</v>
+        <v>369</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>11178957</v>
+      <c r="A43" t="s">
+        <v>1</v>
       </c>
       <c r="B43">
-        <v>16919</v>
+        <v>16978</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F43">
-        <v>58820</v>
+        <v>58836</v>
       </c>
       <c r="G43">
-        <v>999</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -5285,22 +5309,22 @@
         <v>1</v>
       </c>
       <c r="B44">
-        <v>16780</v>
+        <v>16955</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E44" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F44">
-        <v>58753</v>
+        <v>58840</v>
       </c>
       <c r="G44">
-        <v>689</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -5308,1600 +5332,1600 @@
         <v>1</v>
       </c>
       <c r="B45">
-        <v>16781</v>
+        <v>16955</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F45">
-        <v>58755</v>
+        <v>58842</v>
       </c>
       <c r="G45">
-        <v>689</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>1</v>
+      <c r="A46">
+        <v>11178949</v>
       </c>
       <c r="B46">
-        <v>16721</v>
+        <v>16912</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D46" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F46">
-        <v>58757</v>
+        <v>58822</v>
       </c>
       <c r="G46">
-        <v>649</v>
+        <v>679</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>11179003</v>
+        <v>11178957</v>
       </c>
       <c r="B47">
-        <v>16885</v>
+        <v>16919</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F47">
-        <v>58812</v>
+        <v>58820</v>
       </c>
       <c r="G47">
-        <v>499</v>
+        <v>999</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>11179004</v>
+      <c r="A48" t="s">
+        <v>1</v>
       </c>
       <c r="B48">
-        <v>16899</v>
+        <v>16780</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F48">
-        <v>58813</v>
+        <v>58753</v>
       </c>
       <c r="G48">
-        <v>699</v>
+        <v>689</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>11178954</v>
+      <c r="A49" t="s">
+        <v>1</v>
       </c>
       <c r="B49">
-        <v>16877</v>
+        <v>16781</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F49">
-        <v>58777</v>
+        <v>58755</v>
       </c>
       <c r="G49">
-        <v>719</v>
+        <v>689</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>11178943</v>
+      <c r="A50" t="s">
+        <v>1</v>
       </c>
       <c r="B50">
-        <v>16918</v>
+        <v>16721</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F50">
-        <v>58802</v>
+        <v>58757</v>
       </c>
       <c r="G50">
-        <v>689</v>
+        <v>649</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>11178970</v>
+        <v>11179003</v>
       </c>
       <c r="B51">
-        <v>16896</v>
+        <v>16885</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E51" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F51">
-        <v>58803</v>
+        <v>58812</v>
       </c>
       <c r="G51">
-        <v>699</v>
+        <v>499</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>11178953</v>
+        <v>11179004</v>
       </c>
       <c r="B52">
-        <v>16876</v>
+        <v>16899</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E52" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F52">
-        <v>58804</v>
+        <v>58813</v>
       </c>
       <c r="G52">
-        <v>689</v>
+        <v>699</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>11178921</v>
+        <v>11178954</v>
       </c>
       <c r="B53">
-        <v>16878</v>
+        <v>16877</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D53" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E53" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F53">
-        <v>58805</v>
+        <v>58777</v>
       </c>
       <c r="G53">
-        <v>349</v>
+        <v>719</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>11178926</v>
+        <v>11178943</v>
       </c>
       <c r="B54">
-        <v>16903</v>
+        <v>16918</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F54">
-        <v>58806</v>
+        <v>58802</v>
       </c>
       <c r="G54">
-        <v>529</v>
+        <v>689</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>11178964</v>
+        <v>11178970</v>
       </c>
       <c r="B55">
-        <v>16883</v>
+        <v>16896</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F55">
-        <v>58807</v>
+        <v>58803</v>
       </c>
       <c r="G55">
-        <v>249</v>
+        <v>699</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>11178972</v>
+        <v>11178953</v>
       </c>
       <c r="B56">
-        <v>16917</v>
+        <v>16876</v>
       </c>
       <c r="C56" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E56" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F56">
-        <v>58809</v>
+        <v>58804</v>
       </c>
       <c r="G56">
-        <v>889</v>
+        <v>689</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>11178938</v>
+        <v>11178921</v>
       </c>
       <c r="B57">
-        <v>16898</v>
+        <v>16878</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E57" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F57">
-        <v>58810</v>
+        <v>58805</v>
       </c>
       <c r="G57">
-        <v>599</v>
+        <v>349</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>11178919</v>
+        <v>11178926</v>
       </c>
       <c r="B58">
-        <v>16922</v>
+        <v>16903</v>
       </c>
       <c r="C58" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F58">
-        <v>58811</v>
+        <v>58806</v>
       </c>
       <c r="G58">
-        <v>439</v>
+        <v>529</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>11176705</v>
+        <v>11178964</v>
       </c>
       <c r="B59">
-        <v>16678</v>
+        <v>16883</v>
       </c>
       <c r="C59" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E59" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" t="s">
-        <v>76</v>
+        <v>67</v>
+      </c>
+      <c r="F59">
+        <v>58807</v>
+      </c>
+      <c r="G59">
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>11176712</v>
+        <v>11178972</v>
       </c>
       <c r="B60">
-        <v>16679</v>
+        <v>16917</v>
       </c>
       <c r="C60" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E60" t="s">
-        <v>78</v>
-      </c>
-      <c r="F60" t="s">
-        <v>76</v>
+        <v>69</v>
+      </c>
+      <c r="F60">
+        <v>58809</v>
+      </c>
+      <c r="G60">
+        <v>889</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
+        <v>11178938</v>
+      </c>
+      <c r="B61">
+        <v>16898</v>
+      </c>
+      <c r="C61" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" t="s">
+        <v>71</v>
+      </c>
+      <c r="F61">
+        <v>58810</v>
+      </c>
+      <c r="G61">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>11178919</v>
+      </c>
+      <c r="B62">
+        <v>16922</v>
+      </c>
+      <c r="C62" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62">
+        <v>58811</v>
+      </c>
+      <c r="G62">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>11176705</v>
+      </c>
+      <c r="B63">
+        <v>16678</v>
+      </c>
+      <c r="C63" t="s">
+        <v>74</v>
+      </c>
+      <c r="D63" t="s">
+        <v>75</v>
+      </c>
+      <c r="E63" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>11176712</v>
+      </c>
+      <c r="B64">
+        <v>16679</v>
+      </c>
+      <c r="C64" t="s">
+        <v>77</v>
+      </c>
+      <c r="D64" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" t="s">
+        <v>78</v>
+      </c>
+      <c r="F64" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65">
         <v>11178947</v>
       </c>
-      <c r="B61">
+      <c r="B65">
         <v>16914</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C65" t="s">
         <v>79</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D65" t="s">
         <v>80</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E65" t="s">
         <v>80</v>
       </c>
-      <c r="F61">
+      <c r="F65">
         <v>58795</v>
-      </c>
-      <c r="G61">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>1</v>
-      </c>
-      <c r="B62">
-        <v>16531</v>
-      </c>
-      <c r="C62" t="s">
-        <v>81</v>
-      </c>
-      <c r="D62" t="s">
-        <v>82</v>
-      </c>
-      <c r="E62" t="s">
-        <v>82</v>
-      </c>
-      <c r="F62">
-        <v>58769</v>
-      </c>
-      <c r="G62">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>1</v>
-      </c>
-      <c r="B63">
-        <v>16531</v>
-      </c>
-      <c r="C63" t="s">
-        <v>81</v>
-      </c>
-      <c r="D63" t="s">
-        <v>83</v>
-      </c>
-      <c r="E63" t="s">
-        <v>83</v>
-      </c>
-      <c r="F63">
-        <v>58775</v>
-      </c>
-      <c r="G63">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64">
-        <v>16532</v>
-      </c>
-      <c r="C64" t="s">
-        <v>84</v>
-      </c>
-      <c r="D64" t="s">
-        <v>85</v>
-      </c>
-      <c r="E64" t="s">
-        <v>85</v>
-      </c>
-      <c r="F64">
-        <v>58771</v>
-      </c>
-      <c r="G64">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>1</v>
-      </c>
-      <c r="B65">
-        <v>16532</v>
-      </c>
-      <c r="C65" t="s">
-        <v>84</v>
-      </c>
-      <c r="D65" t="s">
-        <v>86</v>
-      </c>
-      <c r="E65" t="s">
-        <v>86</v>
-      </c>
-      <c r="F65">
-        <v>58773</v>
       </c>
       <c r="G65">
         <v>899</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>11177964</v>
+      <c r="A66" t="s">
+        <v>1</v>
       </c>
       <c r="B66">
-        <v>16607</v>
+        <v>16531</v>
       </c>
       <c r="C66" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D66" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E66" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F66">
-        <v>58785</v>
+        <v>58769</v>
       </c>
       <c r="G66">
-        <v>669</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>11177937</v>
+      <c r="A67" t="s">
+        <v>1</v>
       </c>
       <c r="B67">
-        <v>16611</v>
+        <v>16531</v>
       </c>
       <c r="C67" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E67" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F67">
-        <v>58761</v>
+        <v>58775</v>
       </c>
       <c r="G67">
-        <v>539</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>11176721</v>
+      <c r="A68" t="s">
+        <v>1</v>
       </c>
       <c r="B68">
-        <v>16662</v>
+        <v>16532</v>
       </c>
       <c r="C68" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D68" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E68" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F68">
-        <v>58779</v>
+        <v>58771</v>
       </c>
       <c r="G68">
-        <v>969</v>
+        <v>999</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>11176711</v>
+      <c r="A69" t="s">
+        <v>1</v>
       </c>
       <c r="B69">
-        <v>16669</v>
+        <v>16532</v>
       </c>
       <c r="C69" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D69" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E69" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F69">
-        <v>58765</v>
+        <v>58773</v>
       </c>
       <c r="G69">
-        <v>569</v>
+        <v>899</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>11176700</v>
+        <v>11177964</v>
       </c>
       <c r="B70">
-        <v>16670</v>
+        <v>16607</v>
       </c>
       <c r="C70" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D70" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E70" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F70">
-        <v>58783</v>
+        <v>58785</v>
       </c>
       <c r="G70">
-        <v>399</v>
+        <v>669</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>11176703</v>
+        <v>11177937</v>
       </c>
       <c r="B71">
-        <v>16673</v>
+        <v>16611</v>
       </c>
       <c r="C71" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D71" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E71" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F71">
-        <v>58797</v>
+        <v>58761</v>
       </c>
       <c r="G71">
-        <v>369</v>
+        <v>539</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>11176704</v>
+        <v>11176721</v>
       </c>
       <c r="B72">
-        <v>16674</v>
+        <v>16662</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D72" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E72" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F72">
-        <v>58798</v>
+        <v>58779</v>
       </c>
       <c r="G72">
-        <v>499</v>
+        <v>969</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>11176722</v>
+        <v>11176711</v>
       </c>
       <c r="B73">
-        <v>16675</v>
+        <v>16669</v>
       </c>
       <c r="C73" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D73" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E73" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F73">
-        <v>58799</v>
+        <v>58765</v>
       </c>
       <c r="G73">
-        <v>689</v>
+        <v>569</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>11176718</v>
+        <v>11176700</v>
       </c>
       <c r="B74">
-        <v>16676</v>
+        <v>16670</v>
       </c>
       <c r="C74" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E74" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F74">
-        <v>58800</v>
+        <v>58783</v>
       </c>
       <c r="G74">
-        <v>669</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>11176723</v>
+        <v>11176703</v>
       </c>
       <c r="B75">
-        <v>16677</v>
+        <v>16673</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E75" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F75">
-        <v>58801</v>
+        <v>58797</v>
       </c>
       <c r="G75">
-        <v>889</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>11176724</v>
+        <v>11176704</v>
       </c>
       <c r="B76">
-        <v>16672</v>
+        <v>16674</v>
       </c>
       <c r="C76" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D76" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E76" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F76">
-        <v>58763</v>
+        <v>58798</v>
       </c>
       <c r="G76">
-        <v>999</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>11176717</v>
+        <v>11176722</v>
       </c>
       <c r="B77">
-        <v>16671</v>
+        <v>16675</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E77" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F77">
-        <v>58796</v>
+        <v>58799</v>
       </c>
       <c r="G77">
-        <v>489</v>
+        <v>689</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>11176716</v>
+        <v>11176718</v>
       </c>
       <c r="B78">
-        <v>16668</v>
+        <v>16676</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D78" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E78" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F78">
-        <v>58781</v>
+        <v>58800</v>
       </c>
       <c r="G78">
-        <v>899</v>
+        <v>669</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>11176612</v>
+        <v>11176723</v>
       </c>
       <c r="B79">
-        <v>16608</v>
+        <v>16677</v>
       </c>
       <c r="C79" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D79" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F79">
-        <v>52575</v>
+        <v>58801</v>
       </c>
       <c r="G79">
-        <v>659</v>
+        <v>889</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>11176610</v>
+        <v>11176724</v>
       </c>
       <c r="B80">
-        <v>16609</v>
+        <v>16672</v>
       </c>
       <c r="C80" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D80" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E80" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F80">
-        <v>52577</v>
+        <v>58763</v>
       </c>
       <c r="G80">
-        <v>717</v>
+        <v>999</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>11176710</v>
+        <v>11176717</v>
       </c>
       <c r="B81">
-        <v>16664</v>
+        <v>16671</v>
       </c>
       <c r="C81" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D81" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E81" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F81">
-        <v>58791</v>
+        <v>58796</v>
       </c>
       <c r="G81">
-        <v>529</v>
+        <v>489</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>11176701</v>
+        <v>11176716</v>
       </c>
       <c r="B82">
-        <v>16665</v>
+        <v>16668</v>
       </c>
       <c r="C82" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D82" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E82" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F82">
-        <v>58792</v>
+        <v>58781</v>
       </c>
       <c r="G82">
-        <v>489</v>
+        <v>899</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>11176702</v>
+        <v>11176612</v>
       </c>
       <c r="B83">
-        <v>16666</v>
+        <v>16608</v>
       </c>
       <c r="C83" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D83" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F83">
-        <v>58793</v>
+        <v>52575</v>
       </c>
       <c r="G83">
-        <v>459</v>
+        <v>659</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>11176715</v>
+        <v>11176610</v>
       </c>
       <c r="B84">
-        <v>16667</v>
+        <v>16609</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D84" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E84" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F84">
-        <v>58794</v>
+        <v>52577</v>
       </c>
       <c r="G84">
-        <v>679</v>
+        <v>717</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>11176699</v>
+        <v>11176710</v>
       </c>
       <c r="B85">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E85" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F85">
-        <v>58767</v>
+        <v>58791</v>
       </c>
       <c r="G85">
-        <v>499</v>
+        <v>529</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>11177607</v>
+        <v>11176701</v>
       </c>
       <c r="B86">
-        <v>16680</v>
+        <v>16665</v>
       </c>
       <c r="C86" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E86" t="s">
-        <v>128</v>
-      </c>
-      <c r="F86" t="s">
-        <v>129</v>
+        <v>120</v>
+      </c>
+      <c r="F86">
+        <v>58792</v>
       </c>
       <c r="G86">
-        <v>32</v>
+        <v>489</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>1</v>
+      <c r="A87">
+        <v>11176702</v>
       </c>
       <c r="B87">
-        <v>16729</v>
+        <v>16666</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D87" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E87" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F87">
-        <v>52617</v>
+        <v>58793</v>
       </c>
       <c r="G87">
-        <v>59</v>
+        <v>459</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>1</v>
+      <c r="A88">
+        <v>11176715</v>
       </c>
       <c r="B88">
-        <v>16771</v>
+        <v>16667</v>
       </c>
       <c r="C88" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D88" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E88" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F88">
-        <v>52615</v>
+        <v>58794</v>
       </c>
       <c r="G88">
-        <v>109</v>
+        <v>679</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>11176714</v>
+        <v>11176699</v>
       </c>
       <c r="B89">
-        <v>16659</v>
+        <v>16663</v>
       </c>
       <c r="C89" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D89" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E89" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="F89">
-        <v>52609</v>
+        <v>58767</v>
       </c>
       <c r="G89">
-        <v>677</v>
+        <v>499</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>11176719</v>
+        <v>11177607</v>
       </c>
       <c r="B90">
-        <v>16660</v>
+        <v>16680</v>
       </c>
       <c r="C90" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D90" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E90" t="s">
-        <v>137</v>
-      </c>
-      <c r="F90">
-        <v>52610</v>
+        <v>128</v>
+      </c>
+      <c r="F90" t="s">
+        <v>129</v>
       </c>
       <c r="G90">
-        <v>739</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>11176708</v>
+      <c r="A91" t="s">
+        <v>1</v>
       </c>
       <c r="B91">
-        <v>16658</v>
+        <v>16729</v>
       </c>
       <c r="C91" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D91" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E91" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F91">
-        <v>52608</v>
+        <v>52617</v>
       </c>
       <c r="G91">
-        <v>567</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>11176720</v>
+      <c r="A92" t="s">
+        <v>1</v>
       </c>
       <c r="B92">
-        <v>16661</v>
+        <v>16771</v>
       </c>
       <c r="C92" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D92" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E92" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F92">
-        <v>52612</v>
+        <v>52615</v>
       </c>
       <c r="G92">
-        <v>839</v>
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>11174775</v>
+        <v>11176714</v>
       </c>
       <c r="B93">
-        <v>16551</v>
+        <v>16659</v>
       </c>
       <c r="C93" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D93" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E93" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F93">
-        <v>52596</v>
+        <v>52609</v>
       </c>
       <c r="G93">
-        <v>457</v>
+        <v>677</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>11177276</v>
+        <v>11176719</v>
       </c>
       <c r="B94">
-        <v>16559</v>
+        <v>16660</v>
       </c>
       <c r="C94" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E94" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F94">
-        <v>52597</v>
+        <v>52610</v>
       </c>
       <c r="G94">
-        <v>689</v>
+        <v>739</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>11174806</v>
+        <v>11176708</v>
       </c>
       <c r="B95">
-        <v>16557</v>
+        <v>16658</v>
       </c>
       <c r="C95" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D95" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E95" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F95">
-        <v>52598</v>
+        <v>52608</v>
       </c>
       <c r="G95">
-        <v>729</v>
+        <v>567</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>11174811</v>
+        <v>11176720</v>
       </c>
       <c r="B96">
-        <v>16546</v>
+        <v>16661</v>
       </c>
       <c r="C96" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D96" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E96" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F96">
-        <v>52600</v>
+        <v>52612</v>
       </c>
       <c r="G96">
         <v>839</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>1</v>
+      <c r="A97">
+        <v>11174775</v>
       </c>
       <c r="B97">
-        <v>16775</v>
+        <v>16551</v>
       </c>
       <c r="C97" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D97" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E97" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F97">
-        <v>52606</v>
+        <v>52596</v>
       </c>
       <c r="G97">
-        <v>169</v>
+        <v>457</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>11174791</v>
+        <v>11177276</v>
       </c>
       <c r="B98">
-        <v>16572</v>
+        <v>16559</v>
       </c>
       <c r="C98" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E98" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F98">
-        <v>52582</v>
+        <v>52597</v>
       </c>
       <c r="G98">
-        <v>59</v>
+        <v>689</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>1</v>
+      <c r="A99">
+        <v>11174806</v>
       </c>
       <c r="B99">
-        <v>16770</v>
+        <v>16557</v>
       </c>
       <c r="C99" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D99" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E99" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F99">
-        <v>52616</v>
+        <v>52598</v>
       </c>
       <c r="G99">
-        <v>109</v>
+        <v>729</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>11174803</v>
+        <v>11174811</v>
       </c>
       <c r="B100">
-        <v>16549</v>
+        <v>16546</v>
       </c>
       <c r="C100" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D100" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E100" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F100">
-        <v>52591</v>
+        <v>52600</v>
       </c>
       <c r="G100">
-        <v>1399</v>
+        <v>839</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>11174810</v>
+      <c r="A101" t="s">
+        <v>1</v>
       </c>
       <c r="B101">
-        <v>16555</v>
+        <v>16775</v>
       </c>
       <c r="C101" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D101" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E101" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F101">
-        <v>52595</v>
+        <v>52606</v>
       </c>
       <c r="G101">
-        <v>999</v>
+        <v>169</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>11174776</v>
+        <v>11174791</v>
       </c>
       <c r="B102">
-        <v>16550</v>
+        <v>16572</v>
       </c>
       <c r="C102" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D102" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E102" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F102">
-        <v>52585</v>
+        <v>52582</v>
       </c>
       <c r="G102">
-        <v>429</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>11174801</v>
+      <c r="A103" t="s">
+        <v>1</v>
       </c>
       <c r="B103">
-        <v>16548</v>
+        <v>16770</v>
       </c>
       <c r="C103" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D103" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E103" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F103">
-        <v>52586</v>
+        <v>52616</v>
       </c>
       <c r="G103">
-        <v>689</v>
+        <v>109</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>11177275</v>
+        <v>11174803</v>
       </c>
       <c r="B104">
-        <v>16558</v>
+        <v>16549</v>
       </c>
       <c r="C104" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D104" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E104" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F104">
-        <v>52587</v>
+        <v>52591</v>
       </c>
       <c r="G104">
-        <v>689</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>11175037</v>
+        <v>11174810</v>
       </c>
       <c r="B105">
-        <v>16573</v>
+        <v>16555</v>
       </c>
       <c r="C105" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D105" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E105" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F105">
-        <v>52588</v>
+        <v>52595</v>
       </c>
       <c r="G105">
-        <v>444</v>
+        <v>999</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>11174795</v>
+        <v>11174776</v>
       </c>
       <c r="B106">
-        <v>16543</v>
+        <v>16550</v>
       </c>
       <c r="C106" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D106" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E106" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F106">
-        <v>52589</v>
+        <v>52585</v>
       </c>
       <c r="G106">
-        <v>549</v>
+        <v>429</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>1</v>
+      <c r="A107">
+        <v>11174801</v>
       </c>
       <c r="B107">
-        <v>16769</v>
+        <v>16548</v>
       </c>
       <c r="C107" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D107" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E107" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F107">
-        <v>52614</v>
+        <v>52586</v>
       </c>
       <c r="G107">
-        <v>109</v>
+        <v>689</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>11174779</v>
+        <v>11177275</v>
       </c>
       <c r="B108">
-        <v>16540</v>
+        <v>16558</v>
       </c>
       <c r="C108" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D108" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E108" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F108">
-        <v>52584</v>
+        <v>52587</v>
       </c>
       <c r="G108">
-        <v>567</v>
+        <v>689</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>11174804</v>
+        <v>11175037</v>
       </c>
       <c r="B109">
-        <v>16541</v>
+        <v>16573</v>
       </c>
       <c r="C109" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D109" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E109" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F109">
-        <v>52593</v>
+        <v>52588</v>
       </c>
       <c r="G109">
-        <v>889</v>
+        <v>444</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>11174798</v>
+        <v>11174795</v>
       </c>
       <c r="B110">
-        <v>16552</v>
+        <v>16543</v>
       </c>
       <c r="C110" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D110" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E110" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F110">
-        <v>52578</v>
+        <v>52589</v>
       </c>
       <c r="G110">
-        <v>649</v>
+        <v>549</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>11174808</v>
+      <c r="A111" t="s">
+        <v>1</v>
       </c>
       <c r="B111">
-        <v>16545</v>
+        <v>16769</v>
       </c>
       <c r="C111" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D111" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E111" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F111">
-        <v>52579</v>
+        <v>52614</v>
       </c>
       <c r="G111">
-        <v>749</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>11177274</v>
+        <v>11174779</v>
       </c>
       <c r="B112">
-        <v>16547</v>
+        <v>16540</v>
       </c>
       <c r="C112" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D112" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E112" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F112">
-        <v>52580</v>
+        <v>52584</v>
       </c>
       <c r="G112">
-        <v>669</v>
+        <v>567</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>11174800</v>
+        <v>11174804</v>
       </c>
       <c r="B113">
-        <v>16553</v>
+        <v>16541</v>
       </c>
       <c r="C113" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D113" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E113" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F113">
-        <v>52581</v>
+        <v>52593</v>
       </c>
       <c r="G113">
-        <v>669</v>
+        <v>889</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>11174807</v>
+        <v>11174798</v>
       </c>
       <c r="B114">
-        <v>16554</v>
+        <v>16552</v>
       </c>
       <c r="C114" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D114" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E114" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F114">
-        <v>52601</v>
+        <v>52578</v>
       </c>
       <c r="G114">
         <v>649</v>
@@ -6909,70 +6933,162 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>11177277</v>
+        <v>11174808</v>
       </c>
       <c r="B115">
-        <v>16544</v>
+        <v>16545</v>
       </c>
       <c r="C115" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D115" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E115" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F115">
-        <v>52602</v>
+        <v>52579</v>
       </c>
       <c r="G115">
-        <v>489</v>
+        <v>749</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>11174790</v>
+        <v>11177274</v>
       </c>
       <c r="B116">
-        <v>16542</v>
+        <v>16547</v>
       </c>
       <c r="C116" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D116" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E116" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F116">
-        <v>52603</v>
+        <v>52580</v>
       </c>
       <c r="G116">
-        <v>349</v>
+        <v>669</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117">
+        <v>11174800</v>
+      </c>
+      <c r="B117">
+        <v>16553</v>
+      </c>
+      <c r="C117" t="s">
+        <v>182</v>
+      </c>
+      <c r="D117" t="s">
+        <v>183</v>
+      </c>
+      <c r="E117" t="s">
+        <v>183</v>
+      </c>
+      <c r="F117">
+        <v>52581</v>
+      </c>
+      <c r="G117">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>11174807</v>
+      </c>
+      <c r="B118">
+        <v>16554</v>
+      </c>
+      <c r="C118" t="s">
+        <v>184</v>
+      </c>
+      <c r="D118" t="s">
+        <v>185</v>
+      </c>
+      <c r="E118" t="s">
+        <v>185</v>
+      </c>
+      <c r="F118">
+        <v>52601</v>
+      </c>
+      <c r="G118">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>11177277</v>
+      </c>
+      <c r="B119">
+        <v>16544</v>
+      </c>
+      <c r="C119" t="s">
+        <v>186</v>
+      </c>
+      <c r="D119" t="s">
+        <v>187</v>
+      </c>
+      <c r="E119" t="s">
+        <v>187</v>
+      </c>
+      <c r="F119">
+        <v>52602</v>
+      </c>
+      <c r="G119">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>11174790</v>
+      </c>
+      <c r="B120">
+        <v>16542</v>
+      </c>
+      <c r="C120" t="s">
+        <v>188</v>
+      </c>
+      <c r="D120" t="s">
+        <v>189</v>
+      </c>
+      <c r="E120" t="s">
+        <v>189</v>
+      </c>
+      <c r="F120">
+        <v>52603</v>
+      </c>
+      <c r="G120">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121">
         <v>11174799</v>
       </c>
-      <c r="B117">
+      <c r="B121">
         <v>16556</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C121" t="s">
         <v>190</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D121" t="s">
         <v>191</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E121" t="s">
         <v>191</v>
       </c>
-      <c r="F117">
+      <c r="F121">
         <v>52604</v>
       </c>
-      <c r="G117">
+      <c r="G121">
         <v>609</v>
       </c>
     </row>

--- a/Lista_Precios_Base.xlsx
+++ b/Lista_Precios_Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12838C2-5CCE-481A-865A-C2BB2E010773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85DE6FD-027A-42E7-B838-BE50112981DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Campaña" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9767" uniqueCount="3452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9791" uniqueCount="3453">
   <si>
     <t>SKU INTL</t>
   </si>
@@ -10444,6 +10444,9 @@
   </si>
   <si>
     <t>Grab &amp; Go</t>
+  </si>
+  <si>
+    <t>SII26GlCCColor</t>
   </si>
 </sst>
 </file>
@@ -10632,7 +10635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -10684,12 +10687,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10822,8 +10819,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G121" totalsRowShown="0">
-  <autoFilter ref="A1:G121" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G127" totalsRowShown="0">
+  <autoFilter ref="A1:G127" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU INTL"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CÓDIGO DIA"/>
@@ -11124,7 +11121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" customWidth="1"/>
@@ -11159,230 +11156,230 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>11186659</v>
+      <c r="A2" t="s">
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>16999</v>
+        <v>17357</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>3349</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>3452</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>3452</v>
       </c>
       <c r="F2">
-        <v>50754</v>
+        <v>50749</v>
       </c>
       <c r="G2">
-        <v>689</v>
+        <v>489</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>11186658</v>
+      <c r="A3" t="s">
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>16998</v>
+        <v>17358</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>3350</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>3452</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>3452</v>
       </c>
       <c r="F3">
-        <v>50753</v>
+        <v>50749</v>
       </c>
       <c r="G3">
-        <v>679</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>11186646</v>
+      <c r="A4" t="s">
+        <v>21</v>
       </c>
       <c r="B4">
-        <v>16997</v>
+        <v>17359</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>3351</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>3452</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>3452</v>
       </c>
       <c r="F4">
-        <v>50751</v>
+        <v>50749</v>
       </c>
       <c r="G4">
-        <v>679</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>11186650</v>
+      <c r="A5" t="s">
+        <v>21</v>
       </c>
       <c r="B5">
-        <v>16995</v>
+        <v>17360</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>3352</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>3452</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>3452</v>
       </c>
       <c r="F5">
-        <v>50755</v>
+        <v>50749</v>
       </c>
       <c r="G5">
-        <v>649</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>11179885</v>
+      <c r="A6" t="s">
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>16777</v>
+        <v>17361</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>3353</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>3452</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>3452</v>
       </c>
       <c r="F6">
-        <v>50746</v>
+        <v>50749</v>
       </c>
       <c r="G6">
-        <v>689</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>11179880</v>
+      <c r="A7" t="s">
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>16610</v>
+        <v>17362</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>3354</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>3452</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>3452</v>
       </c>
       <c r="F7">
-        <v>50747</v>
+        <v>50749</v>
       </c>
       <c r="G7">
-        <v>649</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>11157547</v>
+        <v>11186659</v>
       </c>
       <c r="B8">
-        <v>15857</v>
+        <v>16999</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>58834</v>
+        <v>50754</v>
       </c>
       <c r="G8">
         <v>689</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>21</v>
+      <c r="A9">
+        <v>11186658</v>
       </c>
       <c r="B9">
-        <v>16977</v>
+        <v>16998</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>58751</v>
+        <v>50753</v>
       </c>
       <c r="G9">
-        <v>179</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>11176587</v>
+        <v>11186646</v>
       </c>
       <c r="B10">
-        <v>16720</v>
+        <v>16997</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>50740</v>
+        <v>50751</v>
       </c>
       <c r="G10">
-        <v>649</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1176593</v>
+        <v>11186650</v>
       </c>
       <c r="B11">
-        <v>16793</v>
+        <v>16995</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>50741</v>
+        <v>50755</v>
       </c>
       <c r="G11">
         <v>649</v>
@@ -11390,853 +11387,853 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11176592</v>
+        <v>11179885</v>
       </c>
       <c r="B12">
-        <v>16779</v>
+        <v>16777</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>50742</v>
+        <v>50746</v>
       </c>
       <c r="G12">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11176586</v>
+        <v>11179880</v>
       </c>
       <c r="B13">
-        <v>16719</v>
+        <v>16610</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>50743</v>
+        <v>50747</v>
       </c>
       <c r="G13">
-        <v>669</v>
+        <v>649</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11176597</v>
+        <v>11157547</v>
       </c>
       <c r="B14">
-        <v>16784</v>
+        <v>15857</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>50745</v>
+        <v>58834</v>
       </c>
       <c r="G14">
-        <v>369</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>11178956</v>
+      <c r="A15" t="s">
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>16916</v>
+        <v>16977</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>50735</v>
+        <v>58751</v>
       </c>
       <c r="G15">
-        <v>999</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11178933</v>
+        <v>11176587</v>
       </c>
       <c r="B16">
-        <v>16881</v>
+        <v>16720</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>50736</v>
+        <v>50740</v>
       </c>
       <c r="G16">
-        <v>529</v>
+        <v>649</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>11178934</v>
+        <v>1176593</v>
       </c>
       <c r="B17">
-        <v>16884</v>
+        <v>16793</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>50737</v>
+        <v>50741</v>
       </c>
       <c r="G17">
-        <v>529</v>
+        <v>649</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>11178935</v>
+        <v>11176592</v>
       </c>
       <c r="B18">
-        <v>16920</v>
+        <v>16779</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>50738</v>
+        <v>50742</v>
       </c>
       <c r="G18">
-        <v>459</v>
+        <v>649</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>11178941</v>
+        <v>11176586</v>
       </c>
       <c r="B19">
-        <v>16900</v>
+        <v>16719</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F19">
-        <v>50739</v>
+        <v>50743</v>
       </c>
       <c r="G19">
-        <v>649</v>
+        <v>669</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>11178917</v>
+        <v>11176597</v>
       </c>
       <c r="B20">
-        <v>16921</v>
+        <v>16784</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>58808</v>
+        <v>50745</v>
       </c>
       <c r="G20">
-        <v>479</v>
+        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>11178969</v>
+        <v>11178956</v>
       </c>
       <c r="B21">
-        <v>16910</v>
+        <v>16916</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F21">
-        <v>58827</v>
+        <v>50735</v>
       </c>
       <c r="G21">
-        <v>679</v>
+        <v>999</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>11178918</v>
+        <v>11178933</v>
       </c>
       <c r="B22">
-        <v>16923</v>
+        <v>16881</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F22">
-        <v>58832</v>
+        <v>50736</v>
       </c>
       <c r="G22">
-        <v>489</v>
+        <v>529</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11178946</v>
+        <v>11178934</v>
       </c>
       <c r="B23">
-        <v>16913</v>
+        <v>16884</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F23">
-        <v>58814</v>
+        <v>50737</v>
       </c>
       <c r="G23">
-        <v>689</v>
+        <v>529</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11178973</v>
+        <v>11178935</v>
       </c>
       <c r="B24">
-        <v>16925</v>
+        <v>16920</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F24">
-        <v>58815</v>
+        <v>50738</v>
       </c>
       <c r="G24">
-        <v>649</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11178959</v>
+        <v>11178941</v>
       </c>
       <c r="B25">
-        <v>16897</v>
+        <v>16900</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F25">
-        <v>58816</v>
+        <v>50739</v>
       </c>
       <c r="G25">
-        <v>659</v>
+        <v>649</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>11178928</v>
+        <v>11178917</v>
       </c>
       <c r="B26">
-        <v>16880</v>
+        <v>16921</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F26">
-        <v>58817</v>
+        <v>58808</v>
       </c>
       <c r="G26">
-        <v>549</v>
+        <v>479</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11178965</v>
+        <v>11178969</v>
       </c>
       <c r="B27">
-        <v>16904</v>
+        <v>16910</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F27">
-        <v>58818</v>
+        <v>58827</v>
       </c>
       <c r="G27">
-        <v>535</v>
+        <v>679</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>11178937</v>
+        <v>11178918</v>
       </c>
       <c r="B28">
-        <v>16901</v>
+        <v>16923</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F28">
-        <v>58819</v>
+        <v>58832</v>
       </c>
       <c r="G28">
-        <v>739</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11178948</v>
+        <v>11178946</v>
       </c>
       <c r="B29">
-        <v>16915</v>
+        <v>16913</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E29" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F29">
-        <v>58821</v>
+        <v>58814</v>
       </c>
       <c r="G29">
-        <v>899</v>
+        <v>689</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>64</v>
+      <c r="A30">
+        <v>11178973</v>
       </c>
       <c r="B30">
-        <v>16971</v>
+        <v>16925</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F30">
-        <v>58846</v>
+        <v>58815</v>
       </c>
       <c r="G30">
-        <v>869</v>
+        <v>649</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11178944</v>
+        <v>11178959</v>
       </c>
       <c r="B31">
-        <v>16909</v>
+        <v>16897</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E31" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F31">
-        <v>58826</v>
+        <v>58816</v>
       </c>
       <c r="G31">
-        <v>679</v>
+        <v>659</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11178952</v>
+        <v>11178928</v>
       </c>
       <c r="B32">
-        <v>16875</v>
+        <v>16880</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F32">
-        <v>58828</v>
+        <v>58817</v>
       </c>
       <c r="G32">
-        <v>689</v>
+        <v>549</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11178971</v>
+        <v>11178965</v>
       </c>
       <c r="B33">
-        <v>16911</v>
+        <v>16904</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F33">
-        <v>58829</v>
+        <v>58818</v>
       </c>
       <c r="G33">
-        <v>679</v>
+        <v>535</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>11178920</v>
+        <v>11178937</v>
       </c>
       <c r="B34">
-        <v>16902</v>
+        <v>16901</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F34">
-        <v>58830</v>
+        <v>58819</v>
       </c>
       <c r="G34">
-        <v>369</v>
+        <v>739</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>11178922</v>
+        <v>11178948</v>
       </c>
       <c r="B35">
-        <v>16879</v>
+        <v>16915</v>
       </c>
       <c r="C35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="F35">
-        <v>58831</v>
+        <v>58821</v>
       </c>
       <c r="G35">
-        <v>349</v>
+        <v>899</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>11178945</v>
+      <c r="A36" t="s">
+        <v>64</v>
       </c>
       <c r="B36">
-        <v>16924</v>
+        <v>16971</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F36">
-        <v>58835</v>
+        <v>58846</v>
       </c>
       <c r="G36">
-        <v>899</v>
+        <v>869</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>11179005</v>
+        <v>11178944</v>
       </c>
       <c r="B37">
-        <v>16906</v>
+        <v>16909</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E37" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F37">
-        <v>58823</v>
+        <v>58826</v>
       </c>
       <c r="G37">
-        <v>889</v>
+        <v>679</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>11178930</v>
+        <v>11178952</v>
       </c>
       <c r="B38">
-        <v>16882</v>
+        <v>16875</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E38" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F38">
-        <v>58824</v>
+        <v>58828</v>
       </c>
       <c r="G38">
-        <v>535</v>
+        <v>689</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>11178966</v>
+        <v>11178971</v>
       </c>
       <c r="B39">
-        <v>16905</v>
+        <v>16911</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E39" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F39">
-        <v>58825</v>
+        <v>58829</v>
       </c>
       <c r="G39">
-        <v>535</v>
+        <v>679</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>11187369</v>
+        <v>11178920</v>
       </c>
       <c r="B40">
-        <v>16908</v>
+        <v>16902</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F40">
-        <v>58848</v>
+        <v>58830</v>
       </c>
       <c r="G40">
-        <v>869</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>11187370</v>
+        <v>11178922</v>
       </c>
       <c r="B41">
-        <v>16958</v>
+        <v>16879</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E41" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F41">
-        <v>58838</v>
+        <v>58831</v>
       </c>
       <c r="G41">
-        <v>679</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>11187372</v>
+        <v>11178945</v>
       </c>
       <c r="B42">
-        <v>16959</v>
+        <v>16924</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E42" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F42">
-        <v>58839</v>
+        <v>58835</v>
       </c>
       <c r="G42">
-        <v>369</v>
+        <v>899</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>64</v>
+      <c r="A43">
+        <v>11179005</v>
       </c>
       <c r="B43">
-        <v>16978</v>
+        <v>16906</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F43">
-        <v>58836</v>
+        <v>58823</v>
       </c>
       <c r="G43">
-        <v>189</v>
+        <v>889</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>64</v>
+      <c r="A44">
+        <v>11178930</v>
       </c>
       <c r="B44">
-        <v>16955</v>
+        <v>16882</v>
       </c>
       <c r="C44" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E44" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F44">
-        <v>58840</v>
+        <v>58824</v>
       </c>
       <c r="G44">
-        <v>1099</v>
+        <v>535</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>64</v>
+      <c r="A45">
+        <v>11178966</v>
       </c>
       <c r="B45">
-        <v>16955</v>
+        <v>16905</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E45" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F45">
-        <v>58842</v>
+        <v>58825</v>
       </c>
       <c r="G45">
-        <v>1099</v>
+        <v>535</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>11178949</v>
+        <v>11187369</v>
       </c>
       <c r="B46">
-        <v>16912</v>
+        <v>16908</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E46" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F46">
-        <v>58822</v>
+        <v>58848</v>
       </c>
       <c r="G46">
-        <v>679</v>
+        <v>869</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>11178957</v>
+        <v>11187370</v>
       </c>
       <c r="B47">
-        <v>16919</v>
+        <v>16958</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E47" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F47">
-        <v>58820</v>
+        <v>58838</v>
       </c>
       <c r="G47">
-        <v>999</v>
+        <v>679</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>64</v>
+      <c r="A48">
+        <v>11187372</v>
       </c>
       <c r="B48">
-        <v>16780</v>
+        <v>16959</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E48" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F48">
-        <v>58753</v>
+        <v>58839</v>
       </c>
       <c r="G48">
-        <v>689</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -12244,22 +12241,22 @@
         <v>64</v>
       </c>
       <c r="B49">
-        <v>16781</v>
+        <v>16978</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E49" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F49">
-        <v>58755</v>
+        <v>58836</v>
       </c>
       <c r="G49">
-        <v>689</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -12267,1648 +12264,1786 @@
         <v>64</v>
       </c>
       <c r="B50">
-        <v>16721</v>
+        <v>16955</v>
       </c>
       <c r="C50" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D50" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F50">
-        <v>58757</v>
+        <v>58840</v>
       </c>
       <c r="G50">
-        <v>649</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>11179003</v>
+      <c r="A51" t="s">
+        <v>64</v>
       </c>
       <c r="B51">
-        <v>16885</v>
+        <v>16955</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F51">
-        <v>58812</v>
+        <v>58842</v>
       </c>
       <c r="G51">
-        <v>499</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>11179004</v>
+        <v>11178949</v>
       </c>
       <c r="B52">
-        <v>16899</v>
+        <v>16912</v>
       </c>
       <c r="C52" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F52">
-        <v>58813</v>
+        <v>58822</v>
       </c>
       <c r="G52">
-        <v>699</v>
+        <v>679</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>11178954</v>
+        <v>11178957</v>
       </c>
       <c r="B53">
-        <v>16877</v>
+        <v>16919</v>
       </c>
       <c r="C53" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D53" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E53" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F53">
-        <v>58777</v>
+        <v>58820</v>
       </c>
       <c r="G53">
-        <v>719</v>
+        <v>999</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>11178943</v>
+      <c r="A54" t="s">
+        <v>64</v>
       </c>
       <c r="B54">
-        <v>16918</v>
+        <v>16780</v>
       </c>
       <c r="C54" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E54" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F54">
-        <v>58802</v>
+        <v>58753</v>
       </c>
       <c r="G54">
         <v>689</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>11178970</v>
+      <c r="A55" t="s">
+        <v>64</v>
       </c>
       <c r="B55">
-        <v>16896</v>
+        <v>16781</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E55" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F55">
-        <v>58803</v>
+        <v>58755</v>
       </c>
       <c r="G55">
-        <v>699</v>
+        <v>689</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>11178953</v>
+      <c r="A56" t="s">
+        <v>64</v>
       </c>
       <c r="B56">
-        <v>16876</v>
+        <v>16721</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E56" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F56">
-        <v>58804</v>
+        <v>58757</v>
       </c>
       <c r="G56">
-        <v>689</v>
+        <v>649</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>11178921</v>
+        <v>11179003</v>
       </c>
       <c r="B57">
-        <v>16878</v>
+        <v>16885</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D57" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E57" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F57">
-        <v>58805</v>
+        <v>58812</v>
       </c>
       <c r="G57">
-        <v>349</v>
+        <v>499</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>11178926</v>
+        <v>11179004</v>
       </c>
       <c r="B58">
-        <v>16903</v>
+        <v>16899</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D58" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E58" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F58">
-        <v>58806</v>
+        <v>58813</v>
       </c>
       <c r="G58">
-        <v>529</v>
+        <v>699</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>11178964</v>
+        <v>11178954</v>
       </c>
       <c r="B59">
-        <v>16883</v>
+        <v>16877</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D59" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E59" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F59">
-        <v>58807</v>
+        <v>58777</v>
       </c>
       <c r="G59">
-        <v>249</v>
+        <v>719</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>11178972</v>
+        <v>11178943</v>
       </c>
       <c r="B60">
-        <v>16917</v>
+        <v>16918</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F60">
-        <v>58809</v>
+        <v>58802</v>
       </c>
       <c r="G60">
-        <v>889</v>
+        <v>689</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>11178938</v>
+        <v>11178970</v>
       </c>
       <c r="B61">
-        <v>16898</v>
+        <v>16896</v>
       </c>
       <c r="C61" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E61" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F61">
-        <v>58810</v>
+        <v>58803</v>
       </c>
       <c r="G61">
-        <v>599</v>
+        <v>699</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>11178919</v>
+        <v>11178953</v>
       </c>
       <c r="B62">
-        <v>16922</v>
+        <v>16876</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E62" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F62">
-        <v>58811</v>
+        <v>58804</v>
       </c>
       <c r="G62">
-        <v>439</v>
+        <v>689</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>11176705</v>
+        <v>11178921</v>
       </c>
       <c r="B63">
-        <v>16678</v>
+        <v>16878</v>
       </c>
       <c r="C63" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E63" t="s">
-        <v>131</v>
-      </c>
-      <c r="F63" t="s">
-        <v>21</v>
+        <v>119</v>
+      </c>
+      <c r="F63">
+        <v>58805</v>
+      </c>
+      <c r="G63">
+        <v>349</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>11176712</v>
+        <v>11178926</v>
       </c>
       <c r="B64">
-        <v>16679</v>
+        <v>16903</v>
       </c>
       <c r="C64" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E64" t="s">
-        <v>133</v>
-      </c>
-      <c r="F64" t="s">
-        <v>21</v>
+        <v>121</v>
+      </c>
+      <c r="F64">
+        <v>58806</v>
+      </c>
+      <c r="G64">
+        <v>529</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>11178947</v>
+        <v>11178964</v>
       </c>
       <c r="B65">
-        <v>16914</v>
+        <v>16883</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E65" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F65">
-        <v>58795</v>
+        <v>58807</v>
       </c>
       <c r="G65">
-        <v>899</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>64</v>
+      <c r="A66">
+        <v>11178972</v>
       </c>
       <c r="B66">
-        <v>16531</v>
+        <v>16917</v>
       </c>
       <c r="C66" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E66" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F66">
-        <v>58769</v>
+        <v>58809</v>
       </c>
       <c r="G66">
-        <v>1099</v>
+        <v>889</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>64</v>
+      <c r="A67">
+        <v>11178938</v>
       </c>
       <c r="B67">
-        <v>16531</v>
+        <v>16898</v>
       </c>
       <c r="C67" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D67" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E67" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F67">
-        <v>58775</v>
+        <v>58810</v>
       </c>
       <c r="G67">
-        <v>1099</v>
+        <v>599</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>64</v>
+      <c r="A68">
+        <v>11178919</v>
       </c>
       <c r="B68">
-        <v>16532</v>
+        <v>16922</v>
       </c>
       <c r="C68" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D68" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E68" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F68">
-        <v>58771</v>
+        <v>58811</v>
       </c>
       <c r="G68">
-        <v>999</v>
+        <v>439</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>64</v>
+      <c r="A69">
+        <v>11176705</v>
       </c>
       <c r="B69">
-        <v>16532</v>
+        <v>16678</v>
       </c>
       <c r="C69" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D69" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E69" t="s">
-        <v>141</v>
-      </c>
-      <c r="F69">
-        <v>58773</v>
-      </c>
-      <c r="G69">
-        <v>899</v>
+        <v>131</v>
+      </c>
+      <c r="F69" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>11177964</v>
+        <v>11176712</v>
       </c>
       <c r="B70">
-        <v>16607</v>
+        <v>16679</v>
       </c>
       <c r="C70" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D70" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E70" t="s">
-        <v>143</v>
-      </c>
-      <c r="F70">
-        <v>58785</v>
-      </c>
-      <c r="G70">
-        <v>669</v>
+        <v>133</v>
+      </c>
+      <c r="F70" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>11177937</v>
+        <v>11178947</v>
       </c>
       <c r="B71">
-        <v>16611</v>
+        <v>16914</v>
       </c>
       <c r="C71" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D71" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E71" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F71">
-        <v>58761</v>
+        <v>58795</v>
       </c>
       <c r="G71">
-        <v>539</v>
+        <v>899</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>11176721</v>
+      <c r="A72" t="s">
+        <v>64</v>
       </c>
       <c r="B72">
-        <v>16662</v>
+        <v>16531</v>
       </c>
       <c r="C72" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D72" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E72" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F72">
-        <v>58779</v>
+        <v>58769</v>
       </c>
       <c r="G72">
-        <v>969</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>11176711</v>
+      <c r="A73" t="s">
+        <v>64</v>
       </c>
       <c r="B73">
-        <v>16669</v>
+        <v>16531</v>
       </c>
       <c r="C73" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D73" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E73" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F73">
-        <v>58765</v>
+        <v>58775</v>
       </c>
       <c r="G73">
-        <v>569</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>11176700</v>
+      <c r="A74" t="s">
+        <v>64</v>
       </c>
       <c r="B74">
-        <v>16670</v>
+        <v>16532</v>
       </c>
       <c r="C74" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E74" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F74">
-        <v>58783</v>
+        <v>58771</v>
       </c>
       <c r="G74">
-        <v>399</v>
+        <v>999</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>11176703</v>
+      <c r="A75" t="s">
+        <v>64</v>
       </c>
       <c r="B75">
-        <v>16673</v>
+        <v>16532</v>
       </c>
       <c r="C75" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="D75" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E75" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="F75">
-        <v>58797</v>
+        <v>58773</v>
       </c>
       <c r="G75">
-        <v>369</v>
+        <v>899</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>11176704</v>
+        <v>11177964</v>
       </c>
       <c r="B76">
-        <v>16674</v>
+        <v>16607</v>
       </c>
       <c r="C76" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D76" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E76" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F76">
-        <v>58798</v>
+        <v>58785</v>
       </c>
       <c r="G76">
-        <v>499</v>
+        <v>669</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>11176722</v>
+        <v>11177937</v>
       </c>
       <c r="B77">
-        <v>16675</v>
+        <v>16611</v>
       </c>
       <c r="C77" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D77" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E77" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F77">
-        <v>58799</v>
+        <v>58761</v>
       </c>
       <c r="G77">
-        <v>689</v>
+        <v>539</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>11176718</v>
+        <v>11176721</v>
       </c>
       <c r="B78">
-        <v>16676</v>
+        <v>16662</v>
       </c>
       <c r="C78" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D78" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="E78" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="F78">
-        <v>58800</v>
+        <v>58779</v>
       </c>
       <c r="G78">
-        <v>669</v>
+        <v>969</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>11176723</v>
+        <v>11176711</v>
       </c>
       <c r="B79">
-        <v>16677</v>
+        <v>16669</v>
       </c>
       <c r="C79" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D79" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E79" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="F79">
-        <v>58801</v>
+        <v>58765</v>
       </c>
       <c r="G79">
-        <v>889</v>
+        <v>569</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>11176724</v>
+        <v>11176700</v>
       </c>
       <c r="B80">
-        <v>16672</v>
+        <v>16670</v>
       </c>
       <c r="C80" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="E80" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F80">
-        <v>58763</v>
+        <v>58783</v>
       </c>
       <c r="G80">
-        <v>999</v>
+        <v>399</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>11176717</v>
+        <v>11176703</v>
       </c>
       <c r="B81">
-        <v>16671</v>
+        <v>16673</v>
       </c>
       <c r="C81" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D81" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E81" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F81">
-        <v>58796</v>
+        <v>58797</v>
       </c>
       <c r="G81">
-        <v>489</v>
+        <v>369</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>11176716</v>
+        <v>11176704</v>
       </c>
       <c r="B82">
-        <v>16668</v>
+        <v>16674</v>
       </c>
       <c r="C82" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D82" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E82" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F82">
-        <v>58781</v>
+        <v>58798</v>
       </c>
       <c r="G82">
-        <v>899</v>
+        <v>499</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>11176612</v>
+        <v>11176722</v>
       </c>
       <c r="B83">
-        <v>16608</v>
+        <v>16675</v>
       </c>
       <c r="C83" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D83" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E83" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F83">
-        <v>52575</v>
+        <v>58799</v>
       </c>
       <c r="G83">
-        <v>659</v>
+        <v>689</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>11176610</v>
+        <v>11176718</v>
       </c>
       <c r="B84">
-        <v>16609</v>
+        <v>16676</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D84" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E84" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="F84">
-        <v>52577</v>
+        <v>58800</v>
       </c>
       <c r="G84">
-        <v>717</v>
+        <v>669</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>11176710</v>
+        <v>11176723</v>
       </c>
       <c r="B85">
-        <v>16664</v>
+        <v>16677</v>
       </c>
       <c r="C85" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E85" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F85">
-        <v>58791</v>
+        <v>58801</v>
       </c>
       <c r="G85">
-        <v>529</v>
+        <v>889</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>11176701</v>
+        <v>11176724</v>
       </c>
       <c r="B86">
-        <v>16665</v>
+        <v>16672</v>
       </c>
       <c r="C86" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="E86" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F86">
-        <v>58792</v>
+        <v>58763</v>
       </c>
       <c r="G86">
-        <v>489</v>
+        <v>999</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>11176702</v>
+        <v>11176717</v>
       </c>
       <c r="B87">
-        <v>16666</v>
+        <v>16671</v>
       </c>
       <c r="C87" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D87" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E87" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F87">
-        <v>58793</v>
+        <v>58796</v>
       </c>
       <c r="G87">
-        <v>459</v>
+        <v>489</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>11176715</v>
+        <v>11176716</v>
       </c>
       <c r="B88">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="C88" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D88" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E88" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F88">
-        <v>58794</v>
+        <v>58781</v>
       </c>
       <c r="G88">
-        <v>679</v>
+        <v>899</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>11176699</v>
+        <v>11176612</v>
       </c>
       <c r="B89">
-        <v>16663</v>
+        <v>16608</v>
       </c>
       <c r="C89" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D89" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E89" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F89">
-        <v>58767</v>
+        <v>52575</v>
       </c>
       <c r="G89">
-        <v>499</v>
+        <v>659</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>11177607</v>
+        <v>11176610</v>
       </c>
       <c r="B90">
-        <v>16680</v>
+        <v>16609</v>
       </c>
       <c r="C90" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D90" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E90" t="s">
-        <v>183</v>
-      </c>
-      <c r="F90" t="s">
-        <v>184</v>
+        <v>171</v>
+      </c>
+      <c r="F90">
+        <v>52577</v>
       </c>
       <c r="G90">
-        <v>32</v>
+        <v>717</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>64</v>
+      <c r="A91">
+        <v>11176710</v>
       </c>
       <c r="B91">
-        <v>16729</v>
+        <v>16664</v>
       </c>
       <c r="C91" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="D91" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E91" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="F91">
-        <v>52617</v>
+        <v>58791</v>
       </c>
       <c r="G91">
-        <v>59</v>
+        <v>529</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>64</v>
+      <c r="A92">
+        <v>11176701</v>
       </c>
       <c r="B92">
-        <v>16771</v>
+        <v>16665</v>
       </c>
       <c r="C92" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="D92" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E92" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F92">
-        <v>52615</v>
+        <v>58792</v>
       </c>
       <c r="G92">
-        <v>109</v>
+        <v>489</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>11176714</v>
+        <v>11176702</v>
       </c>
       <c r="B93">
-        <v>16659</v>
+        <v>16666</v>
       </c>
       <c r="C93" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D93" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="E93" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F93">
-        <v>52609</v>
+        <v>58793</v>
       </c>
       <c r="G93">
-        <v>677</v>
+        <v>459</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>11176719</v>
+        <v>11176715</v>
       </c>
       <c r="B94">
-        <v>16660</v>
+        <v>16667</v>
       </c>
       <c r="C94" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D94" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E94" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="F94">
-        <v>52610</v>
+        <v>58794</v>
       </c>
       <c r="G94">
-        <v>739</v>
+        <v>679</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>11176708</v>
+        <v>11176699</v>
       </c>
       <c r="B95">
-        <v>16658</v>
+        <v>16663</v>
       </c>
       <c r="C95" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D95" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E95" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="F95">
-        <v>52608</v>
+        <v>58767</v>
       </c>
       <c r="G95">
-        <v>567</v>
+        <v>499</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>11176720</v>
+        <v>11177607</v>
       </c>
       <c r="B96">
-        <v>16661</v>
+        <v>16680</v>
       </c>
       <c r="C96" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D96" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E96" t="s">
-        <v>196</v>
-      </c>
-      <c r="F96">
-        <v>52612</v>
+        <v>183</v>
+      </c>
+      <c r="F96" t="s">
+        <v>184</v>
       </c>
       <c r="G96">
-        <v>839</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>11174775</v>
+      <c r="A97" t="s">
+        <v>64</v>
       </c>
       <c r="B97">
-        <v>16551</v>
+        <v>16729</v>
       </c>
       <c r="C97" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D97" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E97" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F97">
-        <v>52596</v>
+        <v>52617</v>
       </c>
       <c r="G97">
-        <v>457</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <v>11177276</v>
+      <c r="A98" t="s">
+        <v>64</v>
       </c>
       <c r="B98">
-        <v>16559</v>
+        <v>16771</v>
       </c>
       <c r="C98" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D98" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E98" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="F98">
-        <v>52597</v>
+        <v>52615</v>
       </c>
       <c r="G98">
-        <v>689</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>11174806</v>
+        <v>11176714</v>
       </c>
       <c r="B99">
-        <v>16557</v>
+        <v>16659</v>
       </c>
       <c r="C99" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="D99" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="E99" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F99">
-        <v>52598</v>
+        <v>52609</v>
       </c>
       <c r="G99">
-        <v>729</v>
+        <v>677</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>11174811</v>
+        <v>11176719</v>
       </c>
       <c r="B100">
-        <v>16546</v>
+        <v>16660</v>
       </c>
       <c r="C100" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D100" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E100" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F100">
-        <v>52600</v>
+        <v>52610</v>
       </c>
       <c r="G100">
-        <v>839</v>
+        <v>739</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>64</v>
+      <c r="A101">
+        <v>11176708</v>
       </c>
       <c r="B101">
-        <v>16775</v>
+        <v>16658</v>
       </c>
       <c r="C101" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D101" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E101" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="F101">
-        <v>52606</v>
+        <v>52608</v>
       </c>
       <c r="G101">
-        <v>169</v>
+        <v>567</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>11174791</v>
+        <v>11176720</v>
       </c>
       <c r="B102">
-        <v>16572</v>
+        <v>16661</v>
       </c>
       <c r="C102" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D102" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E102" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="F102">
-        <v>52582</v>
+        <v>52612</v>
       </c>
       <c r="G102">
-        <v>59</v>
+        <v>839</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>64</v>
+      <c r="A103">
+        <v>11174775</v>
       </c>
       <c r="B103">
-        <v>16770</v>
+        <v>16551</v>
       </c>
       <c r="C103" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D103" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E103" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F103">
-        <v>52616</v>
+        <v>52596</v>
       </c>
       <c r="G103">
-        <v>109</v>
+        <v>457</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>11174803</v>
+        <v>11177276</v>
       </c>
       <c r="B104">
-        <v>16549</v>
+        <v>16559</v>
       </c>
       <c r="C104" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D104" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E104" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F104">
-        <v>52591</v>
+        <v>52597</v>
       </c>
       <c r="G104">
-        <v>1399</v>
+        <v>689</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>11174810</v>
+        <v>11174806</v>
       </c>
       <c r="B105">
-        <v>16555</v>
+        <v>16557</v>
       </c>
       <c r="C105" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D105" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="E105" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F105">
-        <v>52595</v>
+        <v>52598</v>
       </c>
       <c r="G105">
-        <v>999</v>
+        <v>729</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>11174776</v>
+        <v>11174811</v>
       </c>
       <c r="B106">
-        <v>16550</v>
+        <v>16546</v>
       </c>
       <c r="C106" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D106" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E106" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F106">
-        <v>52585</v>
+        <v>52600</v>
       </c>
       <c r="G106">
-        <v>429</v>
+        <v>839</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107">
-        <v>11174801</v>
+      <c r="A107" t="s">
+        <v>64</v>
       </c>
       <c r="B107">
-        <v>16548</v>
+        <v>16775</v>
       </c>
       <c r="C107" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D107" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="E107" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F107">
-        <v>52586</v>
+        <v>52606</v>
       </c>
       <c r="G107">
-        <v>689</v>
+        <v>169</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>11177275</v>
+        <v>11174791</v>
       </c>
       <c r="B108">
-        <v>16558</v>
+        <v>16572</v>
       </c>
       <c r="C108" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D108" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E108" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F108">
-        <v>52587</v>
+        <v>52582</v>
       </c>
       <c r="G108">
-        <v>689</v>
+        <v>59</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109">
-        <v>11175037</v>
+      <c r="A109" t="s">
+        <v>64</v>
       </c>
       <c r="B109">
-        <v>16573</v>
+        <v>16770</v>
       </c>
       <c r="C109" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D109" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E109" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F109">
-        <v>52588</v>
+        <v>52616</v>
       </c>
       <c r="G109">
-        <v>444</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>11174795</v>
+        <v>11174803</v>
       </c>
       <c r="B110">
-        <v>16543</v>
+        <v>16549</v>
       </c>
       <c r="C110" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E110" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F110">
-        <v>52589</v>
+        <v>52591</v>
       </c>
       <c r="G110">
-        <v>549</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>64</v>
+      <c r="A111">
+        <v>11174810</v>
       </c>
       <c r="B111">
-        <v>16769</v>
+        <v>16555</v>
       </c>
       <c r="C111" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="D111" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="E111" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F111">
-        <v>52614</v>
+        <v>52595</v>
       </c>
       <c r="G111">
-        <v>109</v>
+        <v>999</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
-        <v>11174779</v>
+        <v>11174776</v>
       </c>
       <c r="B112">
-        <v>16540</v>
+        <v>16550</v>
       </c>
       <c r="C112" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D112" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E112" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F112">
-        <v>52584</v>
+        <v>52585</v>
       </c>
       <c r="G112">
-        <v>567</v>
+        <v>429</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>11174804</v>
+        <v>11174801</v>
       </c>
       <c r="B113">
-        <v>16541</v>
+        <v>16548</v>
       </c>
       <c r="C113" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="D113" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="E113" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F113">
-        <v>52593</v>
+        <v>52586</v>
       </c>
       <c r="G113">
-        <v>889</v>
+        <v>689</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114">
-        <v>11174798</v>
+        <v>11177275</v>
       </c>
       <c r="B114">
-        <v>16552</v>
+        <v>16558</v>
       </c>
       <c r="C114" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D114" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="E114" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F114">
-        <v>52578</v>
+        <v>52587</v>
       </c>
       <c r="G114">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>11174808</v>
+        <v>11175037</v>
       </c>
       <c r="B115">
-        <v>16545</v>
+        <v>16573</v>
       </c>
       <c r="C115" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D115" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E115" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F115">
-        <v>52579</v>
+        <v>52588</v>
       </c>
       <c r="G115">
-        <v>749</v>
+        <v>444</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>11177274</v>
+        <v>11174795</v>
       </c>
       <c r="B116">
-        <v>16547</v>
+        <v>16543</v>
       </c>
       <c r="C116" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D116" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E116" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F116">
-        <v>52580</v>
+        <v>52589</v>
       </c>
       <c r="G116">
-        <v>669</v>
+        <v>549</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117">
-        <v>11174800</v>
+      <c r="A117" t="s">
+        <v>64</v>
       </c>
       <c r="B117">
-        <v>16553</v>
+        <v>16769</v>
       </c>
       <c r="C117" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D117" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="E117" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F117">
-        <v>52581</v>
+        <v>52614</v>
       </c>
       <c r="G117">
-        <v>669</v>
+        <v>109</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>11174807</v>
+        <v>11174779</v>
       </c>
       <c r="B118">
-        <v>16554</v>
+        <v>16540</v>
       </c>
       <c r="C118" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="D118" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E118" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F118">
-        <v>52601</v>
+        <v>52584</v>
       </c>
       <c r="G118">
-        <v>649</v>
+        <v>567</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>11177277</v>
+        <v>11174804</v>
       </c>
       <c r="B119">
-        <v>16544</v>
+        <v>16541</v>
       </c>
       <c r="C119" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D119" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E119" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F119">
-        <v>52602</v>
+        <v>52593</v>
       </c>
       <c r="G119">
-        <v>489</v>
+        <v>889</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>11174790</v>
+        <v>11174798</v>
       </c>
       <c r="B120">
-        <v>16542</v>
+        <v>16552</v>
       </c>
       <c r="C120" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="D120" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="E120" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F120">
-        <v>52603</v>
+        <v>52578</v>
       </c>
       <c r="G120">
-        <v>349</v>
+        <v>649</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
+        <v>11174808</v>
+      </c>
+      <c r="B121">
+        <v>16545</v>
+      </c>
+      <c r="C121" t="s">
+        <v>233</v>
+      </c>
+      <c r="D121" t="s">
+        <v>234</v>
+      </c>
+      <c r="E121" t="s">
+        <v>234</v>
+      </c>
+      <c r="F121">
+        <v>52579</v>
+      </c>
+      <c r="G121">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>11177274</v>
+      </c>
+      <c r="B122">
+        <v>16547</v>
+      </c>
+      <c r="C122" t="s">
+        <v>235</v>
+      </c>
+      <c r="D122" t="s">
+        <v>236</v>
+      </c>
+      <c r="E122" t="s">
+        <v>236</v>
+      </c>
+      <c r="F122">
+        <v>52580</v>
+      </c>
+      <c r="G122">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>11174800</v>
+      </c>
+      <c r="B123">
+        <v>16553</v>
+      </c>
+      <c r="C123" t="s">
+        <v>237</v>
+      </c>
+      <c r="D123" t="s">
+        <v>238</v>
+      </c>
+      <c r="E123" t="s">
+        <v>238</v>
+      </c>
+      <c r="F123">
+        <v>52581</v>
+      </c>
+      <c r="G123">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>11174807</v>
+      </c>
+      <c r="B124">
+        <v>16554</v>
+      </c>
+      <c r="C124" t="s">
+        <v>239</v>
+      </c>
+      <c r="D124" t="s">
+        <v>240</v>
+      </c>
+      <c r="E124" t="s">
+        <v>240</v>
+      </c>
+      <c r="F124">
+        <v>52601</v>
+      </c>
+      <c r="G124">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>11177277</v>
+      </c>
+      <c r="B125">
+        <v>16544</v>
+      </c>
+      <c r="C125" t="s">
+        <v>241</v>
+      </c>
+      <c r="D125" t="s">
+        <v>242</v>
+      </c>
+      <c r="E125" t="s">
+        <v>242</v>
+      </c>
+      <c r="F125">
+        <v>52602</v>
+      </c>
+      <c r="G125">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>11174790</v>
+      </c>
+      <c r="B126">
+        <v>16542</v>
+      </c>
+      <c r="C126" t="s">
+        <v>243</v>
+      </c>
+      <c r="D126" t="s">
+        <v>244</v>
+      </c>
+      <c r="E126" t="s">
+        <v>244</v>
+      </c>
+      <c r="F126">
+        <v>52603</v>
+      </c>
+      <c r="G126">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127">
         <v>11174799</v>
       </c>
-      <c r="B121">
+      <c r="B127">
         <v>16556</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C127" t="s">
         <v>245</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D127" t="s">
         <v>246</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E127" t="s">
         <v>246</v>
       </c>
-      <c r="F121">
+      <c r="F127">
         <v>52604</v>
       </c>
-      <c r="G121">
+      <c r="G127">
         <v>609</v>
       </c>
     </row>
@@ -61581,19 +61716,19 @@
       </c>
     </row>
     <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="19" t="s">
+      <c r="A89" s="15" t="s">
         <v>3428</v>
       </c>
-      <c r="B89" s="19" t="s">
+      <c r="B89" s="15" t="s">
         <v>3433</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>3428</v>
       </c>
-      <c r="D89" s="19" t="s">
+      <c r="D89" s="15" t="s">
         <v>1150</v>
       </c>
-      <c r="E89" s="20">
+      <c r="E89" s="16">
         <v>16247</v>
       </c>
     </row>
@@ -64301,19 +64436,19 @@
       </c>
     </row>
     <row r="249" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="19" t="s">
+      <c r="A249" s="15" t="s">
         <v>3419</v>
       </c>
-      <c r="B249" s="19" t="s">
+      <c r="B249" s="15" t="s">
         <v>3420</v>
       </c>
       <c r="C249" s="15" t="s">
         <v>3446</v>
       </c>
-      <c r="D249" s="19" t="s">
+      <c r="D249" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="E249" s="20">
+      <c r="E249" s="16">
         <v>7680</v>
       </c>
     </row>
@@ -65457,19 +65592,19 @@
       </c>
     </row>
     <row r="317" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A317" s="19" t="s">
+      <c r="A317" s="15" t="s">
         <v>3423</v>
       </c>
-      <c r="B317" s="19" t="s">
+      <c r="B317" s="15" t="s">
         <v>3423</v>
       </c>
       <c r="C317" s="15" t="s">
         <v>3450</v>
       </c>
-      <c r="D317" s="19" t="s">
+      <c r="D317" s="15" t="s">
         <v>786</v>
       </c>
-      <c r="E317" s="20">
+      <c r="E317" s="16">
         <v>1254</v>
       </c>
     </row>
@@ -68126,19 +68261,19 @@
       </c>
     </row>
     <row r="474" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A474" s="19" t="s">
+      <c r="A474" s="15" t="s">
         <v>3418</v>
       </c>
-      <c r="B474" s="19" t="s">
+      <c r="B474" s="15" t="s">
         <v>3418</v>
       </c>
       <c r="C474" s="15" t="s">
         <v>3445</v>
       </c>
-      <c r="D474" s="19" t="s">
+      <c r="D474" s="15" t="s">
         <v>629</v>
       </c>
-      <c r="E474" s="20">
+      <c r="E474" s="16">
         <v>205429</v>
       </c>
     </row>
@@ -78598,19 +78733,19 @@
       </c>
     </row>
     <row r="1090" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1090" s="19" t="s">
+      <c r="A1090" s="15" t="s">
         <v>3425</v>
       </c>
-      <c r="B1090" s="19" t="s">
+      <c r="B1090" s="15" t="s">
         <v>3435</v>
       </c>
       <c r="C1090" s="15" t="s">
         <v>3435</v>
       </c>
-      <c r="D1090" s="19" t="s">
+      <c r="D1090" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="E1090" s="20">
+      <c r="E1090" s="16">
         <v>16543</v>
       </c>
     </row>
@@ -79295,19 +79430,19 @@
       </c>
     </row>
     <row r="1131" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1131" s="19" t="s">
+      <c r="A1131" s="15" t="s">
         <v>3425</v>
       </c>
-      <c r="B1131" s="19" t="s">
+      <c r="B1131" s="15" t="s">
         <v>3435</v>
       </c>
       <c r="C1131" s="15" t="s">
         <v>3435</v>
       </c>
-      <c r="D1131" s="19" t="s">
+      <c r="D1131" s="15" t="s">
         <v>1391</v>
       </c>
-      <c r="E1131" s="20">
+      <c r="E1131" s="16">
         <v>16474</v>
       </c>
     </row>

--- a/Lista_Precios_Base.xlsx
+++ b/Lista_Precios_Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A532BEC4-51B6-41BE-9E11-723F7B293040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909339AD-62C0-4629-BD08-0414282E8AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10138" uniqueCount="3810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10148" uniqueCount="3816">
   <si>
     <t>SKU INTL</t>
   </si>
@@ -11513,6 +11513,24 @@
   </si>
   <si>
     <t>Xm25Tz14Glass</t>
+  </si>
+  <si>
+    <t>SS VAC WTR BTL 12OZ LAC ANNIVERSARY FY26</t>
+  </si>
+  <si>
+    <t>SS VAC VAC TMBLR 12OZ LAC ANNIVERSARY FY26</t>
+  </si>
+  <si>
+    <t>STN MUG 14OZ LAC ANNIVERSARY FY26</t>
+  </si>
+  <si>
+    <t>PLSTC HOT &amp; CLD CUP 24OZ LAC CORE FY25</t>
+  </si>
+  <si>
+    <t>GLASS CLD CUP BEARISTA BEAR STRAW CHARM 20OZ LAC HOL FY26</t>
+  </si>
+  <si>
+    <t>SII26BearGlass</t>
   </si>
 </sst>
 </file>
@@ -11674,7 +11692,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -11719,6 +11737,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11838,8 +11857,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G127" totalsRowShown="0">
-  <autoFilter ref="A1:G127" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G132" totalsRowShown="0">
+  <autoFilter ref="A1:G132" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU INTL"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CÓDIGO DIA"/>
@@ -12140,7 +12159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" customWidth="1"/>
@@ -12175,118 +12194,73 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>17357</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>50749</v>
-      </c>
-      <c r="G2">
-        <v>489</v>
+      <c r="A2" s="16">
+        <v>11186647</v>
+      </c>
+      <c r="B2" s="16">
+        <v>17298</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>3810</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>3754</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>17358</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>50749</v>
-      </c>
-      <c r="G3">
-        <v>489</v>
+      <c r="A3" s="16">
+        <v>11186648</v>
+      </c>
+      <c r="B3" s="16">
+        <v>16989</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>3811</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>3753</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>17359</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>50749</v>
-      </c>
-      <c r="G4">
-        <v>489</v>
+      <c r="A4" s="16">
+        <v>11186632</v>
+      </c>
+      <c r="B4" s="16">
+        <v>17299</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>3812</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>3623</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>17360</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>50749</v>
-      </c>
-      <c r="G5">
-        <v>489</v>
+      <c r="A5" s="16">
+        <v>11160979</v>
+      </c>
+      <c r="B5" s="16">
+        <v>16960</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>3813</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>3748</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>17361</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>50749</v>
-      </c>
-      <c r="G6">
-        <v>489</v>
+      <c r="A6" s="16">
+        <v>11173043</v>
+      </c>
+      <c r="B6" s="16">
+        <v>16477</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>3814</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>3815</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -12294,10 +12268,10 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>17362</v>
+        <v>17357</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -12313,207 +12287,207 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>11186659</v>
+      <c r="A8" t="s">
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>16999</v>
+        <v>17358</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>50754</v>
+        <v>50749</v>
       </c>
       <c r="G8">
-        <v>689</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>11186658</v>
+      <c r="A9" t="s">
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>16998</v>
+        <v>17359</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>50753</v>
+        <v>50749</v>
       </c>
       <c r="G9">
-        <v>679</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>11186646</v>
+      <c r="A10" t="s">
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>16997</v>
+        <v>17360</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>50751</v>
+        <v>50749</v>
       </c>
       <c r="G10">
-        <v>679</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>11186650</v>
+      <c r="A11" t="s">
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>16995</v>
+        <v>17361</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>50755</v>
+        <v>50749</v>
       </c>
       <c r="G11">
-        <v>649</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11179885</v>
+      <c r="A12" t="s">
+        <v>7</v>
       </c>
       <c r="B12">
-        <v>16777</v>
+        <v>17362</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>50746</v>
+        <v>50749</v>
       </c>
       <c r="G12">
-        <v>689</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>11179880</v>
+        <v>11186659</v>
       </c>
       <c r="B13">
-        <v>16610</v>
+        <v>16999</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>50747</v>
+        <v>50754</v>
       </c>
       <c r="G13">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>11157547</v>
+        <v>11186658</v>
       </c>
       <c r="B14">
-        <v>15857</v>
+        <v>16998</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>58834</v>
+        <v>50753</v>
       </c>
       <c r="G14">
-        <v>689</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>7</v>
+      <c r="A15">
+        <v>11186646</v>
       </c>
       <c r="B15">
-        <v>16977</v>
+        <v>16997</v>
       </c>
       <c r="C15" t="s">
-        <v>2761</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>58751</v>
+        <v>50751</v>
       </c>
       <c r="G15">
-        <v>179</v>
+        <v>679</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>11176587</v>
+        <v>11186650</v>
       </c>
       <c r="B16">
-        <v>16720</v>
+        <v>16995</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>50740</v>
+        <v>50755</v>
       </c>
       <c r="G16">
         <v>649</v>
@@ -12521,45 +12495,45 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1176593</v>
+        <v>11179885</v>
       </c>
       <c r="B17">
-        <v>16793</v>
+        <v>16777</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>50741</v>
+        <v>50746</v>
       </c>
       <c r="G17">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>11176592</v>
+        <v>11179880</v>
       </c>
       <c r="B18">
-        <v>16779</v>
+        <v>16610</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F18">
-        <v>50742</v>
+        <v>50747</v>
       </c>
       <c r="G18">
         <v>649</v>
@@ -12567,275 +12541,275 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>11176586</v>
+        <v>11157547</v>
       </c>
       <c r="B19">
-        <v>16719</v>
+        <v>15857</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>50743</v>
+        <v>58834</v>
       </c>
       <c r="G19">
-        <v>669</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>11176597</v>
+      <c r="A20" t="s">
+        <v>7</v>
       </c>
       <c r="B20">
-        <v>16784</v>
+        <v>16977</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>2761</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>50745</v>
+        <v>58751</v>
       </c>
       <c r="G20">
-        <v>369</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>11178956</v>
+        <v>11176587</v>
       </c>
       <c r="B21">
-        <v>16916</v>
+        <v>16720</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>50735</v>
+        <v>50740</v>
       </c>
       <c r="G21">
-        <v>999</v>
+        <v>649</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>11178933</v>
+        <v>1176593</v>
       </c>
       <c r="B22">
-        <v>16881</v>
+        <v>16793</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F22">
-        <v>50736</v>
+        <v>50741</v>
       </c>
       <c r="G22">
-        <v>529</v>
+        <v>649</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>11178934</v>
+        <v>11176592</v>
       </c>
       <c r="B23">
-        <v>16884</v>
+        <v>16779</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>50737</v>
+        <v>50742</v>
       </c>
       <c r="G23">
-        <v>529</v>
+        <v>649</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11178935</v>
+        <v>11176586</v>
       </c>
       <c r="B24">
-        <v>16920</v>
+        <v>16719</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F24">
-        <v>50738</v>
+        <v>50743</v>
       </c>
       <c r="G24">
-        <v>459</v>
+        <v>669</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11178941</v>
+        <v>11176597</v>
       </c>
       <c r="B25">
-        <v>16900</v>
+        <v>16784</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F25">
-        <v>50739</v>
+        <v>50745</v>
       </c>
       <c r="G25">
-        <v>649</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>11178917</v>
+        <v>11178956</v>
       </c>
       <c r="B26">
-        <v>16921</v>
+        <v>16916</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F26">
-        <v>58808</v>
+        <v>50735</v>
       </c>
       <c r="G26">
-        <v>479</v>
+        <v>999</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11178969</v>
+        <v>11178933</v>
       </c>
       <c r="B27">
-        <v>16910</v>
+        <v>16881</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F27">
-        <v>58827</v>
+        <v>50736</v>
       </c>
       <c r="G27">
-        <v>679</v>
+        <v>529</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>11178918</v>
+        <v>11178934</v>
       </c>
       <c r="B28">
-        <v>16923</v>
+        <v>16884</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F28">
-        <v>58832</v>
+        <v>50737</v>
       </c>
       <c r="G28">
-        <v>489</v>
+        <v>529</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11178946</v>
+        <v>11178935</v>
       </c>
       <c r="B29">
-        <v>16913</v>
+        <v>16920</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F29">
-        <v>58814</v>
+        <v>50738</v>
       </c>
       <c r="G29">
-        <v>689</v>
+        <v>459</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>11178973</v>
+        <v>11178941</v>
       </c>
       <c r="B30">
-        <v>16925</v>
+        <v>16900</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F30">
-        <v>58815</v>
+        <v>50739</v>
       </c>
       <c r="G30">
         <v>649</v>
@@ -12843,505 +12817,505 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>11178959</v>
+        <v>11178917</v>
       </c>
       <c r="B31">
-        <v>16897</v>
+        <v>16921</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F31">
-        <v>58816</v>
+        <v>58808</v>
       </c>
       <c r="G31">
-        <v>659</v>
+        <v>479</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11178928</v>
+        <v>11178969</v>
       </c>
       <c r="B32">
-        <v>16880</v>
+        <v>16910</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F32">
-        <v>58817</v>
+        <v>58827</v>
       </c>
       <c r="G32">
-        <v>549</v>
+        <v>679</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11178965</v>
+        <v>11178918</v>
       </c>
       <c r="B33">
-        <v>16904</v>
+        <v>16923</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F33">
-        <v>58818</v>
+        <v>58832</v>
       </c>
       <c r="G33">
-        <v>535</v>
+        <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>11178937</v>
+        <v>11178946</v>
       </c>
       <c r="B34">
-        <v>16901</v>
+        <v>16913</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F34">
-        <v>58819</v>
+        <v>58814</v>
       </c>
       <c r="G34">
-        <v>739</v>
+        <v>689</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>11178948</v>
+        <v>11178973</v>
       </c>
       <c r="B35">
-        <v>16915</v>
+        <v>16925</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F35">
-        <v>58821</v>
+        <v>58815</v>
       </c>
       <c r="G35">
-        <v>899</v>
+        <v>649</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>70</v>
+      <c r="A36">
+        <v>11178959</v>
       </c>
       <c r="B36">
-        <v>16971</v>
+        <v>16897</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F36">
-        <v>58846</v>
+        <v>58816</v>
       </c>
       <c r="G36">
-        <v>869</v>
+        <v>659</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>11178944</v>
+        <v>11178928</v>
       </c>
       <c r="B37">
-        <v>16909</v>
+        <v>16880</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F37">
-        <v>58826</v>
+        <v>58817</v>
       </c>
       <c r="G37">
-        <v>679</v>
+        <v>549</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>11178952</v>
+        <v>11178965</v>
       </c>
       <c r="B38">
-        <v>16875</v>
+        <v>16904</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F38">
-        <v>58828</v>
+        <v>58818</v>
       </c>
       <c r="G38">
-        <v>689</v>
+        <v>535</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>11178971</v>
+        <v>11178937</v>
       </c>
       <c r="B39">
-        <v>16911</v>
+        <v>16901</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F39">
-        <v>58829</v>
+        <v>58819</v>
       </c>
       <c r="G39">
-        <v>679</v>
+        <v>739</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>11178920</v>
+        <v>11178948</v>
       </c>
       <c r="B40">
-        <v>16902</v>
+        <v>16915</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F40">
-        <v>58830</v>
+        <v>58821</v>
       </c>
       <c r="G40">
-        <v>369</v>
+        <v>899</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>11178922</v>
+      <c r="A41" t="s">
+        <v>70</v>
       </c>
       <c r="B41">
-        <v>16879</v>
+        <v>16971</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E41" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F41">
-        <v>58831</v>
+        <v>58846</v>
       </c>
       <c r="G41">
-        <v>349</v>
+        <v>869</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>11178945</v>
+        <v>11178944</v>
       </c>
       <c r="B42">
-        <v>16924</v>
+        <v>16909</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F42">
-        <v>58835</v>
+        <v>58826</v>
       </c>
       <c r="G42">
-        <v>899</v>
+        <v>679</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>11179005</v>
+        <v>11178952</v>
       </c>
       <c r="B43">
-        <v>16906</v>
+        <v>16875</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E43" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F43">
-        <v>58823</v>
+        <v>58828</v>
       </c>
       <c r="G43">
-        <v>889</v>
+        <v>689</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>11178930</v>
+        <v>11178971</v>
       </c>
       <c r="B44">
-        <v>16882</v>
+        <v>16911</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D44" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F44">
-        <v>58824</v>
+        <v>58829</v>
       </c>
       <c r="G44">
-        <v>535</v>
+        <v>679</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>11178966</v>
+        <v>11178920</v>
       </c>
       <c r="B45">
-        <v>16905</v>
+        <v>16902</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F45">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="G45">
-        <v>535</v>
+        <v>369</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>11187369</v>
+        <v>11178922</v>
       </c>
       <c r="B46">
-        <v>16908</v>
+        <v>16879</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D46" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F46">
-        <v>58848</v>
+        <v>58831</v>
       </c>
       <c r="G46">
-        <v>869</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>11187370</v>
+        <v>11178945</v>
       </c>
       <c r="B47">
-        <v>16958</v>
+        <v>16924</v>
       </c>
       <c r="C47" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D47" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E47" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F47">
-        <v>58838</v>
+        <v>58835</v>
       </c>
       <c r="G47">
-        <v>679</v>
+        <v>899</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>11187372</v>
+        <v>11179005</v>
       </c>
       <c r="B48">
-        <v>16959</v>
+        <v>16906</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F48">
-        <v>58839</v>
+        <v>58823</v>
       </c>
       <c r="G48">
-        <v>369</v>
+        <v>889</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>70</v>
+      <c r="A49">
+        <v>11178930</v>
       </c>
       <c r="B49">
-        <v>16978</v>
+        <v>16882</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E49" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F49">
-        <v>58836</v>
+        <v>58824</v>
       </c>
       <c r="G49">
-        <v>189</v>
+        <v>535</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>70</v>
+      <c r="A50">
+        <v>11178966</v>
       </c>
       <c r="B50">
-        <v>16955</v>
+        <v>16905</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E50" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F50">
-        <v>58840</v>
+        <v>58825</v>
       </c>
       <c r="G50">
-        <v>1099</v>
+        <v>535</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>70</v>
+      <c r="A51">
+        <v>11187369</v>
       </c>
       <c r="B51">
-        <v>16955</v>
+        <v>16908</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D51" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E51" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F51">
-        <v>58842</v>
+        <v>58848</v>
       </c>
       <c r="G51">
-        <v>1099</v>
+        <v>869</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>11178949</v>
+        <v>11187370</v>
       </c>
       <c r="B52">
-        <v>16912</v>
+        <v>16958</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D52" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E52" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F52">
-        <v>58822</v>
+        <v>58838</v>
       </c>
       <c r="G52">
         <v>679</v>
@@ -13349,25 +13323,25 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>11178957</v>
+        <v>11187372</v>
       </c>
       <c r="B53">
-        <v>16919</v>
+        <v>16959</v>
       </c>
       <c r="C53" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D53" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F53">
-        <v>58820</v>
+        <v>58839</v>
       </c>
       <c r="G53">
-        <v>999</v>
+        <v>369</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -13375,22 +13349,22 @@
         <v>70</v>
       </c>
       <c r="B54">
-        <v>16780</v>
+        <v>16978</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E54" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F54">
-        <v>58753</v>
+        <v>58836</v>
       </c>
       <c r="G54">
-        <v>689</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -13398,22 +13372,22 @@
         <v>70</v>
       </c>
       <c r="B55">
-        <v>16781</v>
+        <v>16955</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D55" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E55" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F55">
-        <v>58755</v>
+        <v>58840</v>
       </c>
       <c r="G55">
-        <v>689</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -13421,841 +13395,841 @@
         <v>70</v>
       </c>
       <c r="B56">
-        <v>16721</v>
+        <v>16955</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E56" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F56">
-        <v>58757</v>
+        <v>58842</v>
       </c>
       <c r="G56">
-        <v>649</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>11179003</v>
+        <v>11178949</v>
       </c>
       <c r="B57">
-        <v>16885</v>
+        <v>16912</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E57" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="F57">
-        <v>58812</v>
+        <v>58822</v>
       </c>
       <c r="G57">
-        <v>499</v>
+        <v>679</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>11179004</v>
+        <v>11178957</v>
       </c>
       <c r="B58">
-        <v>16899</v>
+        <v>16919</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E58" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F58">
-        <v>58813</v>
+        <v>58820</v>
       </c>
       <c r="G58">
-        <v>699</v>
+        <v>999</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>11178954</v>
+      <c r="A59" t="s">
+        <v>70</v>
       </c>
       <c r="B59">
-        <v>16877</v>
+        <v>16780</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D59" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E59" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F59">
-        <v>58777</v>
+        <v>58753</v>
       </c>
       <c r="G59">
-        <v>719</v>
+        <v>689</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>11178943</v>
+      <c r="A60" t="s">
+        <v>70</v>
       </c>
       <c r="B60">
-        <v>16918</v>
+        <v>16781</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D60" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F60">
-        <v>58802</v>
+        <v>58755</v>
       </c>
       <c r="G60">
         <v>689</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>11178970</v>
+      <c r="A61" t="s">
+        <v>70</v>
       </c>
       <c r="B61">
-        <v>16896</v>
+        <v>16721</v>
       </c>
       <c r="C61" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D61" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E61" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F61">
-        <v>58803</v>
+        <v>58757</v>
       </c>
       <c r="G61">
-        <v>699</v>
+        <v>649</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>11178953</v>
+        <v>11179003</v>
       </c>
       <c r="B62">
-        <v>16876</v>
+        <v>16885</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E62" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="F62">
-        <v>58804</v>
+        <v>58812</v>
       </c>
       <c r="G62">
-        <v>689</v>
+        <v>499</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>11178921</v>
+        <v>11179004</v>
       </c>
       <c r="B63">
-        <v>16878</v>
+        <v>16899</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D63" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E63" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F63">
-        <v>58805</v>
+        <v>58813</v>
       </c>
       <c r="G63">
-        <v>349</v>
+        <v>699</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>11178926</v>
+        <v>11178954</v>
       </c>
       <c r="B64">
-        <v>16903</v>
+        <v>16877</v>
       </c>
       <c r="C64" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F64">
-        <v>58806</v>
+        <v>58777</v>
       </c>
       <c r="G64">
-        <v>529</v>
+        <v>719</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>11178964</v>
+        <v>11178943</v>
       </c>
       <c r="B65">
-        <v>16883</v>
+        <v>16918</v>
       </c>
       <c r="C65" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E65" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F65">
-        <v>58807</v>
+        <v>58802</v>
       </c>
       <c r="G65">
-        <v>249</v>
+        <v>689</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>11178972</v>
+        <v>11178970</v>
       </c>
       <c r="B66">
-        <v>16917</v>
+        <v>16896</v>
       </c>
       <c r="C66" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D66" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E66" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F66">
-        <v>58809</v>
+        <v>58803</v>
       </c>
       <c r="G66">
-        <v>889</v>
+        <v>699</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>11178938</v>
+        <v>11178953</v>
       </c>
       <c r="B67">
-        <v>16898</v>
+        <v>16876</v>
       </c>
       <c r="C67" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D67" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E67" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F67">
-        <v>58810</v>
+        <v>58804</v>
       </c>
       <c r="G67">
-        <v>599</v>
+        <v>689</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>11178919</v>
+        <v>11178921</v>
       </c>
       <c r="B68">
-        <v>16922</v>
+        <v>16878</v>
       </c>
       <c r="C68" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E68" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F68">
-        <v>58811</v>
+        <v>58805</v>
       </c>
       <c r="G68">
-        <v>439</v>
+        <v>349</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>11176705</v>
+        <v>11178926</v>
       </c>
       <c r="B69">
-        <v>16678</v>
+        <v>16903</v>
       </c>
       <c r="C69" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D69" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E69" t="s">
-        <v>137</v>
-      </c>
-      <c r="F69" t="s">
-        <v>7</v>
+        <v>127</v>
+      </c>
+      <c r="F69">
+        <v>58806</v>
+      </c>
+      <c r="G69">
+        <v>529</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>11176712</v>
+        <v>11178964</v>
       </c>
       <c r="B70">
-        <v>16679</v>
+        <v>16883</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D70" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E70" t="s">
-        <v>139</v>
-      </c>
-      <c r="F70" t="s">
-        <v>7</v>
+        <v>129</v>
+      </c>
+      <c r="F70">
+        <v>58807</v>
+      </c>
+      <c r="G70">
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>11178947</v>
+        <v>11178972</v>
       </c>
       <c r="B71">
-        <v>16914</v>
+        <v>16917</v>
       </c>
       <c r="C71" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D71" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E71" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F71">
-        <v>58795</v>
+        <v>58809</v>
       </c>
       <c r="G71">
-        <v>899</v>
+        <v>889</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>70</v>
+      <c r="A72">
+        <v>11178938</v>
       </c>
       <c r="B72">
-        <v>16531</v>
+        <v>16898</v>
       </c>
       <c r="C72" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D72" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E72" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F72">
-        <v>58769</v>
+        <v>58810</v>
       </c>
       <c r="G72">
-        <v>1099</v>
+        <v>599</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>70</v>
+      <c r="A73">
+        <v>11178919</v>
       </c>
       <c r="B73">
-        <v>16531</v>
+        <v>16922</v>
       </c>
       <c r="C73" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D73" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E73" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="F73">
-        <v>58775</v>
+        <v>58811</v>
       </c>
       <c r="G73">
-        <v>1099</v>
+        <v>439</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>70</v>
+      <c r="A74">
+        <v>11176705</v>
       </c>
       <c r="B74">
-        <v>16532</v>
+        <v>16678</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="D74" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E74" t="s">
-        <v>146</v>
-      </c>
-      <c r="F74">
-        <v>58771</v>
-      </c>
-      <c r="G74">
-        <v>999</v>
+        <v>137</v>
+      </c>
+      <c r="F74" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>70</v>
+      <c r="A75">
+        <v>11176712</v>
       </c>
       <c r="B75">
-        <v>16532</v>
+        <v>16679</v>
       </c>
       <c r="C75" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D75" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E75" t="s">
-        <v>147</v>
-      </c>
-      <c r="F75">
-        <v>58773</v>
-      </c>
-      <c r="G75">
-        <v>899</v>
+        <v>139</v>
+      </c>
+      <c r="F75" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>11177964</v>
+        <v>11178947</v>
       </c>
       <c r="B76">
-        <v>16607</v>
+        <v>16914</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D76" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E76" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F76">
-        <v>58785</v>
+        <v>58795</v>
       </c>
       <c r="G76">
-        <v>669</v>
+        <v>899</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>11177937</v>
+      <c r="A77" t="s">
+        <v>70</v>
       </c>
       <c r="B77">
-        <v>16611</v>
+        <v>16531</v>
       </c>
       <c r="C77" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D77" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E77" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F77">
-        <v>58761</v>
+        <v>58769</v>
       </c>
       <c r="G77">
-        <v>539</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>11176721</v>
+      <c r="A78" t="s">
+        <v>70</v>
       </c>
       <c r="B78">
-        <v>16662</v>
+        <v>16531</v>
       </c>
       <c r="C78" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D78" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E78" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F78">
-        <v>58779</v>
+        <v>58775</v>
       </c>
       <c r="G78">
-        <v>969</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>11176711</v>
+      <c r="A79" t="s">
+        <v>70</v>
       </c>
       <c r="B79">
-        <v>16669</v>
+        <v>16532</v>
       </c>
       <c r="C79" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D79" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E79" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F79">
-        <v>58765</v>
+        <v>58771</v>
       </c>
       <c r="G79">
-        <v>569</v>
+        <v>999</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>11176700</v>
+      <c r="A80" t="s">
+        <v>70</v>
       </c>
       <c r="B80">
-        <v>16670</v>
+        <v>16532</v>
       </c>
       <c r="C80" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D80" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E80" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F80">
-        <v>58783</v>
+        <v>58773</v>
       </c>
       <c r="G80">
-        <v>399</v>
+        <v>899</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>11176703</v>
+        <v>11177964</v>
       </c>
       <c r="B81">
-        <v>16673</v>
+        <v>16607</v>
       </c>
       <c r="C81" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D81" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E81" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F81">
-        <v>58797</v>
+        <v>58785</v>
       </c>
       <c r="G81">
-        <v>369</v>
+        <v>669</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>11176704</v>
+        <v>11177937</v>
       </c>
       <c r="B82">
-        <v>16674</v>
+        <v>16611</v>
       </c>
       <c r="C82" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D82" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E82" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F82">
-        <v>58798</v>
+        <v>58761</v>
       </c>
       <c r="G82">
-        <v>499</v>
+        <v>539</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>11176722</v>
+        <v>11176721</v>
       </c>
       <c r="B83">
-        <v>16675</v>
+        <v>16662</v>
       </c>
       <c r="C83" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D83" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E83" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F83">
-        <v>58799</v>
+        <v>58779</v>
       </c>
       <c r="G83">
-        <v>689</v>
+        <v>969</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>11176718</v>
+        <v>11176711</v>
       </c>
       <c r="B84">
-        <v>16676</v>
+        <v>16669</v>
       </c>
       <c r="C84" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D84" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E84" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F84">
-        <v>58800</v>
+        <v>58765</v>
       </c>
       <c r="G84">
-        <v>669</v>
+        <v>569</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>11176723</v>
+        <v>11176700</v>
       </c>
       <c r="B85">
-        <v>16677</v>
+        <v>16670</v>
       </c>
       <c r="C85" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D85" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E85" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F85">
-        <v>58801</v>
+        <v>58783</v>
       </c>
       <c r="G85">
-        <v>889</v>
+        <v>399</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>11176724</v>
+        <v>11176703</v>
       </c>
       <c r="B86">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="C86" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D86" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E86" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F86">
-        <v>58763</v>
+        <v>58797</v>
       </c>
       <c r="G86">
-        <v>999</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>11176717</v>
+        <v>11176704</v>
       </c>
       <c r="B87">
-        <v>16671</v>
+        <v>16674</v>
       </c>
       <c r="C87" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D87" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E87" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F87">
-        <v>58796</v>
+        <v>58798</v>
       </c>
       <c r="G87">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>11176716</v>
+        <v>11176722</v>
       </c>
       <c r="B88">
-        <v>16668</v>
+        <v>16675</v>
       </c>
       <c r="C88" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D88" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E88" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F88">
-        <v>58781</v>
+        <v>58799</v>
       </c>
       <c r="G88">
-        <v>899</v>
+        <v>689</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>11176612</v>
+        <v>11176718</v>
       </c>
       <c r="B89">
-        <v>16608</v>
+        <v>16676</v>
       </c>
       <c r="C89" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D89" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E89" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F89">
-        <v>52575</v>
+        <v>58800</v>
       </c>
       <c r="G89">
-        <v>659</v>
+        <v>669</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>11176610</v>
+        <v>11176723</v>
       </c>
       <c r="B90">
-        <v>16609</v>
+        <v>16677</v>
       </c>
       <c r="C90" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D90" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E90" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F90">
-        <v>52577</v>
+        <v>58801</v>
       </c>
       <c r="G90">
-        <v>717</v>
+        <v>889</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>11176710</v>
+        <v>11176724</v>
       </c>
       <c r="B91">
-        <v>16664</v>
+        <v>16672</v>
       </c>
       <c r="C91" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D91" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E91" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F91">
-        <v>58791</v>
+        <v>58763</v>
       </c>
       <c r="G91">
-        <v>529</v>
+        <v>999</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>11176701</v>
+        <v>11176717</v>
       </c>
       <c r="B92">
-        <v>16665</v>
+        <v>16671</v>
       </c>
       <c r="C92" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D92" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E92" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F92">
-        <v>58792</v>
+        <v>58796</v>
       </c>
       <c r="G92">
         <v>489</v>
@@ -14263,806 +14237,921 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>11176702</v>
+        <v>11176716</v>
       </c>
       <c r="B93">
-        <v>16666</v>
+        <v>16668</v>
       </c>
       <c r="C93" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D93" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E93" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F93">
-        <v>58793</v>
+        <v>58781</v>
       </c>
       <c r="G93">
-        <v>459</v>
+        <v>899</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>11176715</v>
+        <v>11176612</v>
       </c>
       <c r="B94">
-        <v>16667</v>
+        <v>16608</v>
       </c>
       <c r="C94" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D94" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E94" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="F94">
-        <v>58794</v>
+        <v>52575</v>
       </c>
       <c r="G94">
-        <v>679</v>
+        <v>659</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>11176699</v>
+        <v>11176610</v>
       </c>
       <c r="B95">
-        <v>16663</v>
+        <v>16609</v>
       </c>
       <c r="C95" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D95" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E95" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="F95">
-        <v>58767</v>
+        <v>52577</v>
       </c>
       <c r="G95">
-        <v>499</v>
+        <v>717</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>11177607</v>
+        <v>11176710</v>
       </c>
       <c r="B96">
-        <v>16680</v>
+        <v>16664</v>
       </c>
       <c r="C96" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D96" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E96" t="s">
-        <v>189</v>
-      </c>
-      <c r="F96" t="s">
-        <v>190</v>
+        <v>179</v>
+      </c>
+      <c r="F96">
+        <v>58791</v>
       </c>
       <c r="G96">
-        <v>32</v>
+        <v>529</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>70</v>
+      <c r="A97">
+        <v>11176701</v>
       </c>
       <c r="B97">
-        <v>16729</v>
+        <v>16665</v>
       </c>
       <c r="C97" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D97" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E97" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="F97">
-        <v>52617</v>
+        <v>58792</v>
       </c>
       <c r="G97">
-        <v>59</v>
+        <v>489</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>70</v>
+      <c r="A98">
+        <v>11176702</v>
       </c>
       <c r="B98">
-        <v>16771</v>
+        <v>16666</v>
       </c>
       <c r="C98" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D98" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E98" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F98">
-        <v>52615</v>
+        <v>58793</v>
       </c>
       <c r="G98">
-        <v>109</v>
+        <v>459</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>11176714</v>
+        <v>11176715</v>
       </c>
       <c r="B99">
-        <v>16659</v>
+        <v>16667</v>
       </c>
       <c r="C99" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D99" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="E99" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F99">
-        <v>52609</v>
+        <v>58794</v>
       </c>
       <c r="G99">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>11176719</v>
+        <v>11176699</v>
       </c>
       <c r="B100">
-        <v>16660</v>
+        <v>16663</v>
       </c>
       <c r="C100" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D100" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E100" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F100">
-        <v>52610</v>
+        <v>58767</v>
       </c>
       <c r="G100">
-        <v>739</v>
+        <v>499</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>11176708</v>
+        <v>11177607</v>
       </c>
       <c r="B101">
-        <v>16658</v>
+        <v>16680</v>
       </c>
       <c r="C101" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D101" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E101" t="s">
-        <v>200</v>
-      </c>
-      <c r="F101">
-        <v>52608</v>
+        <v>189</v>
+      </c>
+      <c r="F101" t="s">
+        <v>190</v>
       </c>
       <c r="G101">
-        <v>567</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>11176720</v>
+      <c r="A102" t="s">
+        <v>70</v>
       </c>
       <c r="B102">
-        <v>16661</v>
+        <v>16729</v>
       </c>
       <c r="C102" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D102" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E102" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F102">
-        <v>52612</v>
+        <v>52617</v>
       </c>
       <c r="G102">
-        <v>839</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>11174775</v>
+      <c r="A103" t="s">
+        <v>70</v>
       </c>
       <c r="B103">
-        <v>16551</v>
+        <v>16771</v>
       </c>
       <c r="C103" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D103" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="E103" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F103">
-        <v>52596</v>
+        <v>52615</v>
       </c>
       <c r="G103">
-        <v>457</v>
+        <v>109</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>11177276</v>
+        <v>11176714</v>
       </c>
       <c r="B104">
-        <v>16559</v>
+        <v>16659</v>
       </c>
       <c r="C104" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D104" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E104" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F104">
-        <v>52597</v>
+        <v>52609</v>
       </c>
       <c r="G104">
-        <v>689</v>
+        <v>677</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>11174806</v>
+        <v>11176719</v>
       </c>
       <c r="B105">
-        <v>16557</v>
+        <v>16660</v>
       </c>
       <c r="C105" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D105" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E105" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="F105">
-        <v>52598</v>
+        <v>52610</v>
       </c>
       <c r="G105">
-        <v>729</v>
+        <v>739</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>11174811</v>
+        <v>11176708</v>
       </c>
       <c r="B106">
-        <v>16546</v>
+        <v>16658</v>
       </c>
       <c r="C106" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D106" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E106" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F106">
-        <v>52600</v>
+        <v>52608</v>
       </c>
       <c r="G106">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>11176720</v>
+      </c>
+      <c r="B107">
+        <v>16661</v>
+      </c>
+      <c r="C107" t="s">
+        <v>201</v>
+      </c>
+      <c r="D107" t="s">
+        <v>202</v>
+      </c>
+      <c r="E107" t="s">
+        <v>202</v>
+      </c>
+      <c r="F107">
+        <v>52612</v>
+      </c>
+      <c r="G107">
         <v>839</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>70</v>
-      </c>
-      <c r="B107">
-        <v>16775</v>
-      </c>
-      <c r="C107" t="s">
-        <v>211</v>
-      </c>
-      <c r="D107" t="s">
-        <v>212</v>
-      </c>
-      <c r="E107" t="s">
-        <v>212</v>
-      </c>
-      <c r="F107">
-        <v>52606</v>
-      </c>
-      <c r="G107">
-        <v>169</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>11174791</v>
+        <v>11174775</v>
       </c>
       <c r="B108">
-        <v>16572</v>
+        <v>16551</v>
       </c>
       <c r="C108" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D108" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E108" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F108">
-        <v>52582</v>
+        <v>52596</v>
       </c>
       <c r="G108">
-        <v>59</v>
+        <v>457</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>70</v>
+      <c r="A109">
+        <v>11177276</v>
       </c>
       <c r="B109">
-        <v>16770</v>
+        <v>16559</v>
       </c>
       <c r="C109" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D109" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="E109" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F109">
-        <v>52616</v>
+        <v>52597</v>
       </c>
       <c r="G109">
-        <v>109</v>
+        <v>689</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>11174803</v>
+        <v>11174806</v>
       </c>
       <c r="B110">
-        <v>16549</v>
+        <v>16557</v>
       </c>
       <c r="C110" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D110" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E110" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F110">
-        <v>52591</v>
+        <v>52598</v>
       </c>
       <c r="G110">
-        <v>1399</v>
+        <v>729</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>11174810</v>
+        <v>11174811</v>
       </c>
       <c r="B111">
-        <v>16555</v>
+        <v>16546</v>
       </c>
       <c r="C111" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D111" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E111" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F111">
-        <v>52595</v>
+        <v>52600</v>
       </c>
       <c r="G111">
-        <v>999</v>
+        <v>839</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <v>11174776</v>
+      <c r="A112" t="s">
+        <v>70</v>
       </c>
       <c r="B112">
-        <v>16550</v>
+        <v>16775</v>
       </c>
       <c r="C112" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D112" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="E112" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F112">
-        <v>52585</v>
+        <v>52606</v>
       </c>
       <c r="G112">
-        <v>429</v>
+        <v>169</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113">
-        <v>11174801</v>
+        <v>11174791</v>
       </c>
       <c r="B113">
-        <v>16548</v>
+        <v>16572</v>
       </c>
       <c r="C113" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E113" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="F113">
-        <v>52586</v>
+        <v>52582</v>
       </c>
       <c r="G113">
-        <v>689</v>
+        <v>59</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114">
-        <v>11177275</v>
+      <c r="A114" t="s">
+        <v>70</v>
       </c>
       <c r="B114">
-        <v>16558</v>
+        <v>16770</v>
       </c>
       <c r="C114" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D114" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E114" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="F114">
-        <v>52587</v>
+        <v>52616</v>
       </c>
       <c r="G114">
-        <v>689</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>11175037</v>
+        <v>11174803</v>
       </c>
       <c r="B115">
-        <v>16573</v>
+        <v>16549</v>
       </c>
       <c r="C115" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D115" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E115" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="F115">
-        <v>52588</v>
+        <v>52591</v>
       </c>
       <c r="G115">
-        <v>444</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>11174795</v>
+        <v>11174810</v>
       </c>
       <c r="B116">
-        <v>16543</v>
+        <v>16555</v>
       </c>
       <c r="C116" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D116" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E116" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F116">
-        <v>52589</v>
+        <v>52595</v>
       </c>
       <c r="G116">
-        <v>549</v>
+        <v>999</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>70</v>
+      <c r="A117">
+        <v>11174776</v>
       </c>
       <c r="B117">
-        <v>16769</v>
+        <v>16550</v>
       </c>
       <c r="C117" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D117" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E117" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F117">
-        <v>52614</v>
+        <v>52585</v>
       </c>
       <c r="G117">
-        <v>109</v>
+        <v>429</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>11174779</v>
+        <v>11174801</v>
       </c>
       <c r="B118">
-        <v>16540</v>
+        <v>16548</v>
       </c>
       <c r="C118" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D118" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E118" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="F118">
-        <v>52584</v>
+        <v>52586</v>
       </c>
       <c r="G118">
-        <v>567</v>
+        <v>689</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>11174804</v>
+        <v>11177275</v>
       </c>
       <c r="B119">
-        <v>16541</v>
+        <v>16558</v>
       </c>
       <c r="C119" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D119" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E119" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="F119">
-        <v>52593</v>
+        <v>52587</v>
       </c>
       <c r="G119">
-        <v>889</v>
+        <v>689</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>11174798</v>
+        <v>11175037</v>
       </c>
       <c r="B120">
-        <v>16552</v>
+        <v>16573</v>
       </c>
       <c r="C120" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D120" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E120" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="F120">
-        <v>52578</v>
+        <v>52588</v>
       </c>
       <c r="G120">
-        <v>649</v>
+        <v>444</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>11174808</v>
+        <v>11174795</v>
       </c>
       <c r="B121">
-        <v>16545</v>
+        <v>16543</v>
       </c>
       <c r="C121" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D121" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="E121" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="F121">
-        <v>52579</v>
+        <v>52589</v>
       </c>
       <c r="G121">
-        <v>749</v>
+        <v>549</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122">
-        <v>11177274</v>
+      <c r="A122" t="s">
+        <v>70</v>
       </c>
       <c r="B122">
-        <v>16547</v>
+        <v>16769</v>
       </c>
       <c r="C122" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D122" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E122" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="F122">
-        <v>52580</v>
+        <v>52614</v>
       </c>
       <c r="G122">
-        <v>669</v>
+        <v>109</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123">
-        <v>11174800</v>
+        <v>11174779</v>
       </c>
       <c r="B123">
-        <v>16553</v>
+        <v>16540</v>
       </c>
       <c r="C123" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D123" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E123" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F123">
-        <v>52581</v>
+        <v>52584</v>
       </c>
       <c r="G123">
-        <v>669</v>
+        <v>567</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>11174807</v>
+        <v>11174804</v>
       </c>
       <c r="B124">
-        <v>16554</v>
+        <v>16541</v>
       </c>
       <c r="C124" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D124" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E124" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F124">
-        <v>52601</v>
+        <v>52593</v>
       </c>
       <c r="G124">
-        <v>649</v>
+        <v>889</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125">
-        <v>11177277</v>
+        <v>11174798</v>
       </c>
       <c r="B125">
-        <v>16544</v>
+        <v>16552</v>
       </c>
       <c r="C125" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D125" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E125" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F125">
-        <v>52602</v>
+        <v>52578</v>
       </c>
       <c r="G125">
-        <v>489</v>
+        <v>649</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>11174790</v>
+        <v>11174808</v>
       </c>
       <c r="B126">
-        <v>16542</v>
+        <v>16545</v>
       </c>
       <c r="C126" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D126" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E126" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F126">
-        <v>52603</v>
+        <v>52579</v>
       </c>
       <c r="G126">
-        <v>349</v>
+        <v>749</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
+        <v>11177274</v>
+      </c>
+      <c r="B127">
+        <v>16547</v>
+      </c>
+      <c r="C127" t="s">
+        <v>241</v>
+      </c>
+      <c r="D127" t="s">
+        <v>242</v>
+      </c>
+      <c r="E127" t="s">
+        <v>242</v>
+      </c>
+      <c r="F127">
+        <v>52580</v>
+      </c>
+      <c r="G127">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>11174800</v>
+      </c>
+      <c r="B128">
+        <v>16553</v>
+      </c>
+      <c r="C128" t="s">
+        <v>243</v>
+      </c>
+      <c r="D128" t="s">
+        <v>244</v>
+      </c>
+      <c r="E128" t="s">
+        <v>244</v>
+      </c>
+      <c r="F128">
+        <v>52581</v>
+      </c>
+      <c r="G128">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>11174807</v>
+      </c>
+      <c r="B129">
+        <v>16554</v>
+      </c>
+      <c r="C129" t="s">
+        <v>245</v>
+      </c>
+      <c r="D129" t="s">
+        <v>246</v>
+      </c>
+      <c r="E129" t="s">
+        <v>246</v>
+      </c>
+      <c r="F129">
+        <v>52601</v>
+      </c>
+      <c r="G129">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>11177277</v>
+      </c>
+      <c r="B130">
+        <v>16544</v>
+      </c>
+      <c r="C130" t="s">
+        <v>247</v>
+      </c>
+      <c r="D130" t="s">
+        <v>248</v>
+      </c>
+      <c r="E130" t="s">
+        <v>248</v>
+      </c>
+      <c r="F130">
+        <v>52602</v>
+      </c>
+      <c r="G130">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>11174790</v>
+      </c>
+      <c r="B131">
+        <v>16542</v>
+      </c>
+      <c r="C131" t="s">
+        <v>249</v>
+      </c>
+      <c r="D131" t="s">
+        <v>250</v>
+      </c>
+      <c r="E131" t="s">
+        <v>250</v>
+      </c>
+      <c r="F131">
+        <v>52603</v>
+      </c>
+      <c r="G131">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132">
         <v>11174799</v>
       </c>
-      <c r="B127">
+      <c r="B132">
         <v>16556</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C132" t="s">
         <v>251</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D132" t="s">
         <v>252</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E132" t="s">
         <v>252</v>
       </c>
-      <c r="F127">
+      <c r="F132">
         <v>52604</v>
       </c>
-      <c r="G127">
+      <c r="G132">
         <v>609</v>
       </c>
     </row>

--- a/Lista_Precios_Base.xlsx
+++ b/Lista_Precios_Base.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909339AD-62C0-4629-BD08-0414282E8AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B20A1C6-F9F3-48E5-BEF8-98F3F491FDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10148" uniqueCount="3816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10175" uniqueCount="3838">
   <si>
     <t>SKU INTL</t>
   </si>
@@ -11531,6 +11531,72 @@
   </si>
   <si>
     <t>SII26BearGlass</t>
+  </si>
+  <si>
+    <t>SS VAC TMBLR 12OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>SS VAC TMBLR CHARM PSL 16OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>SS CLD CUP  STRAW TOPPER PSL 16OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>PLSTC CLD CUP  CONFETTI LID PSL 24OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>PLSTC WTR BTL PSL  24OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>SS VAC CLD CUP CARRY LOOP 24OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>SS VAC TMBLR 24OZ LAC FALL FY26</t>
+  </si>
+  <si>
+    <t>Reusable México</t>
+  </si>
+  <si>
+    <t>GLASS CLD CUP MOTTLED LUSTER 18OZ LAC ANNIVERSARY FY26</t>
+  </si>
+  <si>
+    <t>SS VAC VAC TMBLR CHARM 16OZ LAC ANNIVERSARY FY26</t>
+  </si>
+  <si>
+    <t>SS VAC TMBLR 20OZ LAC ANNIVERSARY FY26</t>
+  </si>
+  <si>
+    <t>Fl26SS12psl</t>
+  </si>
+  <si>
+    <t>Fl26SS16pslCharm</t>
+  </si>
+  <si>
+    <t>Fl26SSCCpsl</t>
+  </si>
+  <si>
+    <t>Fl26CC24psl</t>
+  </si>
+  <si>
+    <t>Fl26PPBTL24</t>
+  </si>
+  <si>
+    <t>Fl26SSCCBrown</t>
+  </si>
+  <si>
+    <t>Fl26ThruST16Brown</t>
+  </si>
+  <si>
+    <t>Fl26ResuAMx</t>
+  </si>
+  <si>
+    <t>Fl26Glass18Aniv</t>
+  </si>
+  <si>
+    <t>Fl26SS16AnivCharm</t>
+  </si>
+  <si>
+    <t>Fl26SS20Hand</t>
   </si>
 </sst>
 </file>
@@ -11692,7 +11758,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -11738,12 +11804,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF7A4D00"/>
@@ -11753,6 +11825,9 @@
           <bgColor rgb="FFFFF4CC"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -11857,11 +11932,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G132" totalsRowShown="0">
-  <autoFilter ref="A1:G132" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Base_Campaña" displayName="Base_Campaña" ref="A1:G143" totalsRowShown="0">
+  <autoFilter ref="A1:G143" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="SKU INTL"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CÓDIGO DIA"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CÓDIGO DIA" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Descripción SCI"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="NOMBRE POS"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="NOMBRE INVENTARIO"/>
@@ -11925,19 +12000,19 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="NOMBRE POS"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="NOMBRE INVENTARIO"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="SKU POS"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="C2" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="C2" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla6" displayName="Tabla6" ref="A1:C1706" totalsRowShown="0" headerRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabla6" displayName="Tabla6" ref="A1:C1706" totalsRowShown="0" headerRowBorderDxfId="5">
   <autoFilter ref="A1:C1706" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID WOE" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Codigo DIA" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Descripcion SAP" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="ID WOE" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Codigo DIA" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Descripcion SAP" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12159,11 +12234,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" customWidth="1"/>
-    <col min="2" max="2" width="15.69921875" customWidth="1"/>
+    <col min="2" max="2" width="15.69921875" style="17" customWidth="1"/>
     <col min="3" max="3" width="74.19921875" customWidth="1"/>
     <col min="4" max="4" width="18.5" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
@@ -12174,7 +12249,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -12194,1059 +12269,1002 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="16">
+      <c r="A2">
+        <v>11186645</v>
+      </c>
+      <c r="B2" s="17">
+        <v>16996</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3816</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>11186652</v>
+      </c>
+      <c r="B3" s="17">
+        <v>17297</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3817</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>11186653</v>
+      </c>
+      <c r="B4" s="17">
+        <v>17343</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3818</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>11186638</v>
+      </c>
+      <c r="B5" s="17">
+        <v>17303</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3819</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>11186639</v>
+      </c>
+      <c r="B6" s="17">
+        <v>16969</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3820</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>11186665</v>
+      </c>
+      <c r="B7" s="17">
+        <v>17336</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3821</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>11186666</v>
+      </c>
+      <c r="B8" s="17">
+        <v>17337</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3822</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3833</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="17">
+        <v>16889</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3823</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3834</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>11186644</v>
+      </c>
+      <c r="B10" s="17">
+        <v>16972</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3824</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>11186654</v>
+      </c>
+      <c r="B11" s="17">
+        <v>16990</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3825</v>
+      </c>
+      <c r="E11" t="s">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11186660</v>
+      </c>
+      <c r="B12" s="17">
+        <v>17338</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3826</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3837</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
         <v>11186647</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B13" s="18">
         <v>17298</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C13" s="16" t="s">
         <v>3810</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="D13" t="s">
         <v>3754</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="16">
+      <c r="E13" s="16" t="s">
+        <v>3754</v>
+      </c>
+      <c r="F13">
+        <v>50756</v>
+      </c>
+      <c r="G13">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
         <v>11186648</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B14" s="18">
         <v>16989</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C14" s="16" t="s">
         <v>3811</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="D14" t="s">
         <v>3753</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="16">
+      <c r="E14" s="16" t="s">
+        <v>3753</v>
+      </c>
+      <c r="F14">
+        <v>50757</v>
+      </c>
+      <c r="G14">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="16">
         <v>11186632</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B15" s="18">
         <v>17299</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C15" s="16" t="s">
         <v>3812</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="D15" t="s">
         <v>3623</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="16">
+      <c r="E15" s="16" t="s">
+        <v>3623</v>
+      </c>
+      <c r="F15">
+        <v>50758</v>
+      </c>
+      <c r="G15">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="16">
         <v>11160979</v>
       </c>
-      <c r="B5" s="16">
-        <v>16960</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="B16" s="18">
+        <v>16900</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>3813</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="D16" t="s">
         <v>3748</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="E16" s="16" t="s">
+        <v>3748</v>
+      </c>
+      <c r="F16">
+        <v>50759</v>
+      </c>
+      <c r="G16">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="16">
         <v>11173043</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B17" s="18">
         <v>16477</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C17" s="16" t="s">
         <v>3814</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="D17" t="s">
         <v>3815</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="E17" s="16" t="s">
+        <v>3815</v>
+      </c>
+      <c r="F17">
+        <v>52508</v>
+      </c>
+      <c r="G17">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B18" s="17">
         <v>17357</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C18" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D18" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E18" t="s">
         <v>9</v>
       </c>
-      <c r="F7">
+      <c r="F18">
         <v>50749</v>
       </c>
-      <c r="G7">
+      <c r="G18">
         <v>489</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B19" s="17">
         <v>17358</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D19" t="s">
         <v>9</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E19" t="s">
         <v>9</v>
       </c>
-      <c r="F8">
+      <c r="F19">
         <v>50749</v>
       </c>
-      <c r="G8">
+      <c r="G19">
         <v>489</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>17359</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9">
-        <v>50749</v>
-      </c>
-      <c r="G9">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>17360</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10">
-        <v>50749</v>
-      </c>
-      <c r="G10">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11">
-        <v>17361</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11">
-        <v>50749</v>
-      </c>
-      <c r="G11">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12">
-        <v>17362</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12">
-        <v>50749</v>
-      </c>
-      <c r="G12">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>11186659</v>
-      </c>
-      <c r="B13">
-        <v>16999</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13">
-        <v>50754</v>
-      </c>
-      <c r="G13">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>11186658</v>
-      </c>
-      <c r="B14">
-        <v>16998</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14">
-        <v>50753</v>
-      </c>
-      <c r="G14">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>11186646</v>
-      </c>
-      <c r="B15">
-        <v>16997</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15">
-        <v>50751</v>
-      </c>
-      <c r="G15">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>11186650</v>
-      </c>
-      <c r="B16">
-        <v>16995</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16">
-        <v>50755</v>
-      </c>
-      <c r="G16">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>11179885</v>
-      </c>
-      <c r="B17">
-        <v>16777</v>
-      </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17">
-        <v>50746</v>
-      </c>
-      <c r="G17">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>11179880</v>
-      </c>
-      <c r="B18">
-        <v>16610</v>
-      </c>
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18">
-        <v>50747</v>
-      </c>
-      <c r="G18">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>11157547</v>
-      </c>
-      <c r="B19">
-        <v>15857</v>
-      </c>
-      <c r="C19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19">
-        <v>58834</v>
-      </c>
-      <c r="G19">
-        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
-      <c r="B20">
-        <v>16977</v>
+      <c r="B20" s="17">
+        <v>17359</v>
       </c>
       <c r="C20" t="s">
-        <v>2761</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>58751</v>
+        <v>50749</v>
       </c>
       <c r="G20">
-        <v>179</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>11176587</v>
-      </c>
-      <c r="B21">
-        <v>16720</v>
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="17">
+        <v>17360</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F21">
-        <v>50740</v>
+        <v>50749</v>
       </c>
       <c r="G21">
-        <v>649</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>1176593</v>
-      </c>
-      <c r="B22">
-        <v>16793</v>
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="17">
+        <v>17361</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>50741</v>
+        <v>50749</v>
       </c>
       <c r="G22">
-        <v>649</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>11176592</v>
-      </c>
-      <c r="B23">
-        <v>16779</v>
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="17">
+        <v>17362</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>50742</v>
+        <v>50749</v>
       </c>
       <c r="G23">
-        <v>649</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>11176586</v>
-      </c>
-      <c r="B24">
-        <v>16719</v>
+        <v>11186659</v>
+      </c>
+      <c r="B24" s="17">
+        <v>16999</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>50743</v>
+        <v>50754</v>
       </c>
       <c r="G24">
-        <v>669</v>
+        <v>689</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>11176597</v>
-      </c>
-      <c r="B25">
-        <v>16784</v>
+        <v>11186658</v>
+      </c>
+      <c r="B25" s="17">
+        <v>16998</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F25">
-        <v>50745</v>
+        <v>50753</v>
       </c>
       <c r="G25">
-        <v>369</v>
+        <v>679</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>11178956</v>
-      </c>
-      <c r="B26">
-        <v>16916</v>
+        <v>11186646</v>
+      </c>
+      <c r="B26" s="17">
+        <v>16997</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>50735</v>
+        <v>50751</v>
       </c>
       <c r="G26">
-        <v>999</v>
+        <v>679</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>11178933</v>
-      </c>
-      <c r="B27">
-        <v>16881</v>
+        <v>11186650</v>
+      </c>
+      <c r="B27" s="17">
+        <v>16995</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>50736</v>
+        <v>50755</v>
       </c>
       <c r="G27">
-        <v>529</v>
+        <v>649</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>11178934</v>
-      </c>
-      <c r="B28">
-        <v>16884</v>
+        <v>11179885</v>
+      </c>
+      <c r="B28" s="17">
+        <v>16777</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F28">
-        <v>50737</v>
+        <v>50746</v>
       </c>
       <c r="G28">
-        <v>529</v>
+        <v>689</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>11178935</v>
-      </c>
-      <c r="B29">
-        <v>16920</v>
+        <v>11179880</v>
+      </c>
+      <c r="B29" s="17">
+        <v>16610</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F29">
-        <v>50738</v>
+        <v>50747</v>
       </c>
       <c r="G29">
-        <v>459</v>
+        <v>649</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>11178941</v>
-      </c>
-      <c r="B30">
-        <v>16900</v>
+        <v>11157547</v>
+      </c>
+      <c r="B30" s="17">
+        <v>15857</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F30">
-        <v>50739</v>
+        <v>58834</v>
       </c>
       <c r="G30">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>11178917</v>
-      </c>
-      <c r="B31">
-        <v>16921</v>
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="17">
+        <v>16977</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>2761</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>58808</v>
+        <v>58751</v>
       </c>
       <c r="G31">
-        <v>479</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>11178969</v>
-      </c>
-      <c r="B32">
-        <v>16910</v>
+        <v>11176587</v>
+      </c>
+      <c r="B32" s="17">
+        <v>16720</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F32">
-        <v>58827</v>
+        <v>50740</v>
       </c>
       <c r="G32">
-        <v>679</v>
+        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11178918</v>
-      </c>
-      <c r="B33">
-        <v>16923</v>
+        <v>1176593</v>
+      </c>
+      <c r="B33" s="17">
+        <v>16793</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F33">
-        <v>58832</v>
+        <v>50741</v>
       </c>
       <c r="G33">
-        <v>489</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>11178946</v>
-      </c>
-      <c r="B34">
-        <v>16913</v>
+        <v>11176592</v>
+      </c>
+      <c r="B34" s="17">
+        <v>16779</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>58814</v>
+        <v>50742</v>
       </c>
       <c r="G34">
-        <v>689</v>
+        <v>649</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>11178973</v>
-      </c>
-      <c r="B35">
-        <v>16925</v>
+        <v>11176586</v>
+      </c>
+      <c r="B35" s="17">
+        <v>16719</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="F35">
-        <v>58815</v>
+        <v>50743</v>
       </c>
       <c r="G35">
-        <v>649</v>
+        <v>669</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>11178959</v>
-      </c>
-      <c r="B36">
-        <v>16897</v>
+        <v>11176597</v>
+      </c>
+      <c r="B36" s="17">
+        <v>16784</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F36">
-        <v>58816</v>
+        <v>50745</v>
       </c>
       <c r="G36">
-        <v>659</v>
+        <v>369</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>11178928</v>
-      </c>
-      <c r="B37">
-        <v>16880</v>
+        <v>11178956</v>
+      </c>
+      <c r="B37" s="17">
+        <v>16916</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="F37">
-        <v>58817</v>
+        <v>50735</v>
       </c>
       <c r="G37">
-        <v>549</v>
+        <v>999</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>11178965</v>
-      </c>
-      <c r="B38">
-        <v>16904</v>
+        <v>11178933</v>
+      </c>
+      <c r="B38" s="17">
+        <v>16881</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F38">
-        <v>58818</v>
+        <v>50736</v>
       </c>
       <c r="G38">
-        <v>535</v>
+        <v>529</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>11178937</v>
-      </c>
-      <c r="B39">
-        <v>16901</v>
+        <v>11178934</v>
+      </c>
+      <c r="B39" s="17">
+        <v>16884</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="F39">
-        <v>58819</v>
+        <v>50737</v>
       </c>
       <c r="G39">
-        <v>739</v>
+        <v>529</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>11178948</v>
-      </c>
-      <c r="B40">
-        <v>16915</v>
+        <v>11178935</v>
+      </c>
+      <c r="B40" s="17">
+        <v>16920</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D40" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="F40">
-        <v>58821</v>
+        <v>50738</v>
       </c>
       <c r="G40">
-        <v>899</v>
+        <v>459</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41">
-        <v>16971</v>
+      <c r="A41">
+        <v>11178941</v>
+      </c>
+      <c r="B41" s="17">
+        <v>16900</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="F41">
-        <v>58846</v>
+        <v>50739</v>
       </c>
       <c r="G41">
-        <v>869</v>
+        <v>649</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>11178944</v>
-      </c>
-      <c r="B42">
-        <v>16909</v>
+        <v>11178917</v>
+      </c>
+      <c r="B42" s="17">
+        <v>16921</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="E42" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="F42">
-        <v>58826</v>
+        <v>58808</v>
       </c>
       <c r="G42">
-        <v>679</v>
+        <v>479</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>11178952</v>
-      </c>
-      <c r="B43">
-        <v>16875</v>
+        <v>11178969</v>
+      </c>
+      <c r="B43" s="17">
+        <v>16910</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="F43">
-        <v>58828</v>
+        <v>58827</v>
       </c>
       <c r="G43">
-        <v>689</v>
+        <v>679</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>11178971</v>
-      </c>
-      <c r="B44">
-        <v>16911</v>
+        <v>11178918</v>
+      </c>
+      <c r="B44" s="17">
+        <v>16923</v>
       </c>
       <c r="C44" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D44" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="E44" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="F44">
-        <v>58829</v>
+        <v>58832</v>
       </c>
       <c r="G44">
-        <v>679</v>
+        <v>489</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>11178920</v>
-      </c>
-      <c r="B45">
-        <v>16902</v>
+        <v>11178946</v>
+      </c>
+      <c r="B45" s="17">
+        <v>16913</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E45" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="F45">
-        <v>58830</v>
+        <v>58814</v>
       </c>
       <c r="G45">
-        <v>369</v>
+        <v>689</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>11178922</v>
-      </c>
-      <c r="B46">
-        <v>16879</v>
+        <v>11178973</v>
+      </c>
+      <c r="B46" s="17">
+        <v>16925</v>
       </c>
       <c r="C46" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="F46">
-        <v>58831</v>
+        <v>58815</v>
       </c>
       <c r="G46">
-        <v>349</v>
+        <v>649</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>11178945</v>
-      </c>
-      <c r="B47">
-        <v>16924</v>
+        <v>11178959</v>
+      </c>
+      <c r="B47" s="17">
+        <v>16897</v>
       </c>
       <c r="C47" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D47" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="E47" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="F47">
-        <v>58835</v>
+        <v>58816</v>
       </c>
       <c r="G47">
-        <v>899</v>
+        <v>659</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>11179005</v>
-      </c>
-      <c r="B48">
-        <v>16906</v>
+        <v>11178928</v>
+      </c>
+      <c r="B48" s="17">
+        <v>16880</v>
       </c>
       <c r="C48" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E48" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F48">
-        <v>58823</v>
+        <v>58817</v>
       </c>
       <c r="G48">
-        <v>889</v>
+        <v>549</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>11178930</v>
-      </c>
-      <c r="B49">
-        <v>16882</v>
+        <v>11178965</v>
+      </c>
+      <c r="B49" s="17">
+        <v>16904</v>
       </c>
       <c r="C49" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="E49" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="F49">
-        <v>58824</v>
+        <v>58818</v>
       </c>
       <c r="G49">
         <v>535</v>
@@ -13254,1465 +13272,1465 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>11178966</v>
-      </c>
-      <c r="B50">
-        <v>16905</v>
+        <v>11178937</v>
+      </c>
+      <c r="B50" s="17">
+        <v>16901</v>
       </c>
       <c r="C50" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="F50">
-        <v>58825</v>
+        <v>58819</v>
       </c>
       <c r="G50">
-        <v>535</v>
+        <v>739</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>11187369</v>
-      </c>
-      <c r="B51">
-        <v>16908</v>
+        <v>11178948</v>
+      </c>
+      <c r="B51" s="17">
+        <v>16915</v>
       </c>
       <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51">
+        <v>58821</v>
+      </c>
+      <c r="G51">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="17">
+        <v>16971</v>
+      </c>
+      <c r="C52" t="s">
         <v>71</v>
       </c>
-      <c r="D51" t="s">
-        <v>91</v>
-      </c>
-      <c r="E51" t="s">
-        <v>91</v>
-      </c>
-      <c r="F51">
-        <v>58848</v>
-      </c>
-      <c r="G51">
+      <c r="D52" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" t="s">
+        <v>72</v>
+      </c>
+      <c r="F52">
+        <v>58846</v>
+      </c>
+      <c r="G52">
         <v>869</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>11187370</v>
-      </c>
-      <c r="B52">
-        <v>16958</v>
-      </c>
-      <c r="C52" t="s">
-        <v>92</v>
-      </c>
-      <c r="D52" t="s">
-        <v>93</v>
-      </c>
-      <c r="E52" t="s">
-        <v>93</v>
-      </c>
-      <c r="F52">
-        <v>58838</v>
-      </c>
-      <c r="G52">
-        <v>679</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>11187372</v>
-      </c>
-      <c r="B53">
-        <v>16959</v>
+        <v>11178944</v>
+      </c>
+      <c r="B53" s="17">
+        <v>16909</v>
       </c>
       <c r="C53" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D53" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E53" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F53">
-        <v>58839</v>
+        <v>58826</v>
       </c>
       <c r="G53">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>11178952</v>
+      </c>
+      <c r="B54" s="17">
+        <v>16875</v>
+      </c>
+      <c r="C54" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54">
+        <v>58828</v>
+      </c>
+      <c r="G54">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>11178971</v>
+      </c>
+      <c r="B55" s="17">
+        <v>16911</v>
+      </c>
+      <c r="C55" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" t="s">
+        <v>78</v>
+      </c>
+      <c r="F55">
+        <v>58829</v>
+      </c>
+      <c r="G55">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>11178920</v>
+      </c>
+      <c r="B56" s="17">
+        <v>16902</v>
+      </c>
+      <c r="C56" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" t="s">
+        <v>80</v>
+      </c>
+      <c r="F56">
+        <v>58830</v>
+      </c>
+      <c r="G56">
         <v>369</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>70</v>
-      </c>
-      <c r="B54">
-        <v>16978</v>
-      </c>
-      <c r="C54" t="s">
-        <v>96</v>
-      </c>
-      <c r="D54" t="s">
-        <v>97</v>
-      </c>
-      <c r="E54" t="s">
-        <v>97</v>
-      </c>
-      <c r="F54">
-        <v>58836</v>
-      </c>
-      <c r="G54">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55">
-        <v>16955</v>
-      </c>
-      <c r="C55" t="s">
-        <v>98</v>
-      </c>
-      <c r="D55" t="s">
-        <v>99</v>
-      </c>
-      <c r="E55" t="s">
-        <v>99</v>
-      </c>
-      <c r="F55">
-        <v>58840</v>
-      </c>
-      <c r="G55">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56">
-        <v>16955</v>
-      </c>
-      <c r="C56" t="s">
-        <v>100</v>
-      </c>
-      <c r="D56" t="s">
-        <v>101</v>
-      </c>
-      <c r="E56" t="s">
-        <v>101</v>
-      </c>
-      <c r="F56">
-        <v>58842</v>
-      </c>
-      <c r="G56">
-        <v>1099</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>11178949</v>
-      </c>
-      <c r="B57">
-        <v>16912</v>
+        <v>11178922</v>
+      </c>
+      <c r="B57" s="17">
+        <v>16879</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D57" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E57" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="F57">
-        <v>58822</v>
+        <v>58831</v>
       </c>
       <c r="G57">
-        <v>679</v>
+        <v>349</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>11178957</v>
-      </c>
-      <c r="B58">
-        <v>16919</v>
+        <v>11178945</v>
+      </c>
+      <c r="B58" s="17">
+        <v>16924</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="E58" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="F58">
-        <v>58820</v>
+        <v>58835</v>
       </c>
       <c r="G58">
-        <v>999</v>
+        <v>899</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>70</v>
-      </c>
-      <c r="B59">
-        <v>16780</v>
+      <c r="A59">
+        <v>11179005</v>
+      </c>
+      <c r="B59" s="17">
+        <v>16906</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="F59">
-        <v>58753</v>
+        <v>58823</v>
       </c>
       <c r="G59">
-        <v>689</v>
+        <v>889</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60">
-        <v>16781</v>
+      <c r="A60">
+        <v>11178930</v>
+      </c>
+      <c r="B60" s="17">
+        <v>16882</v>
       </c>
       <c r="C60" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="E60" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="F60">
-        <v>58755</v>
+        <v>58824</v>
       </c>
       <c r="G60">
-        <v>689</v>
+        <v>535</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>70</v>
-      </c>
-      <c r="B61">
-        <v>16721</v>
+      <c r="A61">
+        <v>11178966</v>
+      </c>
+      <c r="B61" s="17">
+        <v>16905</v>
       </c>
       <c r="C61" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="D61" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="E61" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="F61">
-        <v>58757</v>
+        <v>58825</v>
       </c>
       <c r="G61">
-        <v>649</v>
+        <v>535</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>11179003</v>
-      </c>
-      <c r="B62">
-        <v>16885</v>
+        <v>11187369</v>
+      </c>
+      <c r="B62" s="17">
+        <v>16908</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="E62" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="F62">
-        <v>58812</v>
+        <v>58848</v>
       </c>
       <c r="G62">
-        <v>499</v>
+        <v>869</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>11179004</v>
-      </c>
-      <c r="B63">
-        <v>16899</v>
+        <v>11187370</v>
+      </c>
+      <c r="B63" s="17">
+        <v>16958</v>
       </c>
       <c r="C63" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="E63" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="F63">
-        <v>58813</v>
+        <v>58838</v>
       </c>
       <c r="G63">
-        <v>699</v>
+        <v>679</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>11178954</v>
-      </c>
-      <c r="B64">
-        <v>16877</v>
+        <v>11187372</v>
+      </c>
+      <c r="B64" s="17">
+        <v>16959</v>
       </c>
       <c r="C64" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="D64" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="E64" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="F64">
-        <v>58777</v>
+        <v>58839</v>
       </c>
       <c r="G64">
-        <v>719</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>11178943</v>
-      </c>
-      <c r="B65">
-        <v>16918</v>
+      <c r="A65" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="17">
+        <v>16978</v>
       </c>
       <c r="C65" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D65" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="E65" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="F65">
-        <v>58802</v>
+        <v>58836</v>
       </c>
       <c r="G65">
-        <v>689</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>11178970</v>
-      </c>
-      <c r="B66">
-        <v>16896</v>
+      <c r="A66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="17">
+        <v>16955</v>
       </c>
       <c r="C66" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="D66" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="E66" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="F66">
-        <v>58803</v>
+        <v>58840</v>
       </c>
       <c r="G66">
-        <v>699</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>11178953</v>
-      </c>
-      <c r="B67">
-        <v>16876</v>
+      <c r="A67" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="17">
+        <v>16955</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="E67" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="F67">
-        <v>58804</v>
+        <v>58842</v>
       </c>
       <c r="G67">
-        <v>689</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>11178921</v>
-      </c>
-      <c r="B68">
-        <v>16878</v>
+        <v>11178949</v>
+      </c>
+      <c r="B68" s="17">
+        <v>16912</v>
       </c>
       <c r="C68" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="D68" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="F68">
-        <v>58805</v>
+        <v>58822</v>
       </c>
       <c r="G68">
-        <v>349</v>
+        <v>679</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>11178926</v>
-      </c>
-      <c r="B69">
-        <v>16903</v>
+        <v>11178957</v>
+      </c>
+      <c r="B69" s="17">
+        <v>16919</v>
       </c>
       <c r="C69" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E69" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="F69">
-        <v>58806</v>
+        <v>58820</v>
       </c>
       <c r="G69">
-        <v>529</v>
+        <v>999</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>11178964</v>
-      </c>
-      <c r="B70">
-        <v>16883</v>
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" s="17">
+        <v>16780</v>
       </c>
       <c r="C70" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="D70" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E70" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="F70">
-        <v>58807</v>
+        <v>58753</v>
       </c>
       <c r="G70">
-        <v>249</v>
+        <v>689</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>11178972</v>
-      </c>
-      <c r="B71">
-        <v>16917</v>
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="17">
+        <v>16781</v>
       </c>
       <c r="C71" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="D71" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E71" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F71">
-        <v>58809</v>
+        <v>58755</v>
       </c>
       <c r="G71">
-        <v>889</v>
+        <v>689</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>11178938</v>
-      </c>
-      <c r="B72">
-        <v>16898</v>
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="17">
+        <v>16721</v>
       </c>
       <c r="C72" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="D72" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="E72" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F72">
-        <v>58810</v>
+        <v>58757</v>
       </c>
       <c r="G72">
-        <v>599</v>
+        <v>649</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>11178919</v>
-      </c>
-      <c r="B73">
-        <v>16922</v>
+        <v>11179003</v>
+      </c>
+      <c r="B73" s="17">
+        <v>16885</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E73" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="F73">
-        <v>58811</v>
+        <v>58812</v>
       </c>
       <c r="G73">
-        <v>439</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>11176705</v>
-      </c>
-      <c r="B74">
-        <v>16678</v>
+        <v>11179004</v>
+      </c>
+      <c r="B74" s="17">
+        <v>16899</v>
       </c>
       <c r="C74" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="E74" t="s">
-        <v>137</v>
-      </c>
-      <c r="F74" t="s">
-        <v>7</v>
+        <v>115</v>
+      </c>
+      <c r="F74">
+        <v>58813</v>
+      </c>
+      <c r="G74">
+        <v>699</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>11176712</v>
-      </c>
-      <c r="B75">
-        <v>16679</v>
+        <v>11178954</v>
+      </c>
+      <c r="B75" s="17">
+        <v>16877</v>
       </c>
       <c r="C75" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="D75" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E75" t="s">
-        <v>139</v>
-      </c>
-      <c r="F75" t="s">
-        <v>7</v>
+        <v>117</v>
+      </c>
+      <c r="F75">
+        <v>58777</v>
+      </c>
+      <c r="G75">
+        <v>719</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>11178947</v>
-      </c>
-      <c r="B76">
-        <v>16914</v>
+        <v>11178943</v>
+      </c>
+      <c r="B76" s="17">
+        <v>16918</v>
       </c>
       <c r="C76" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="D76" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E76" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="F76">
-        <v>58795</v>
+        <v>58802</v>
       </c>
       <c r="G76">
-        <v>899</v>
+        <v>689</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>70</v>
-      </c>
-      <c r="B77">
-        <v>16531</v>
+      <c r="A77">
+        <v>11178970</v>
+      </c>
+      <c r="B77" s="17">
+        <v>16896</v>
       </c>
       <c r="C77" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="D77" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="E77" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="F77">
-        <v>58769</v>
+        <v>58803</v>
       </c>
       <c r="G77">
-        <v>1099</v>
+        <v>699</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>70</v>
-      </c>
-      <c r="B78">
-        <v>16531</v>
+      <c r="A78">
+        <v>11178953</v>
+      </c>
+      <c r="B78" s="17">
+        <v>16876</v>
       </c>
       <c r="C78" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D78" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="E78" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="F78">
-        <v>58775</v>
+        <v>58804</v>
       </c>
       <c r="G78">
-        <v>1099</v>
+        <v>689</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>70</v>
-      </c>
-      <c r="B79">
-        <v>16532</v>
+      <c r="A79">
+        <v>11178921</v>
+      </c>
+      <c r="B79" s="17">
+        <v>16878</v>
       </c>
       <c r="C79" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D79" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E79" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F79">
-        <v>58771</v>
+        <v>58805</v>
       </c>
       <c r="G79">
-        <v>999</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>70</v>
-      </c>
-      <c r="B80">
-        <v>16532</v>
+      <c r="A80">
+        <v>11178926</v>
+      </c>
+      <c r="B80" s="17">
+        <v>16903</v>
       </c>
       <c r="C80" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="D80" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="E80" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="F80">
-        <v>58773</v>
+        <v>58806</v>
       </c>
       <c r="G80">
-        <v>899</v>
+        <v>529</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>11177964</v>
-      </c>
-      <c r="B81">
-        <v>16607</v>
+        <v>11178964</v>
+      </c>
+      <c r="B81" s="17">
+        <v>16883</v>
       </c>
       <c r="C81" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D81" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="E81" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="F81">
-        <v>58785</v>
+        <v>58807</v>
       </c>
       <c r="G81">
-        <v>669</v>
+        <v>249</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>11177937</v>
-      </c>
-      <c r="B82">
-        <v>16611</v>
+        <v>11178972</v>
+      </c>
+      <c r="B82" s="17">
+        <v>16917</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D82" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="E82" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F82">
-        <v>58761</v>
+        <v>58809</v>
       </c>
       <c r="G82">
-        <v>539</v>
+        <v>889</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>11176721</v>
-      </c>
-      <c r="B83">
-        <v>16662</v>
+        <v>11178938</v>
+      </c>
+      <c r="B83" s="17">
+        <v>16898</v>
       </c>
       <c r="C83" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="E83" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="F83">
-        <v>58779</v>
+        <v>58810</v>
       </c>
       <c r="G83">
-        <v>969</v>
+        <v>599</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>11176711</v>
-      </c>
-      <c r="B84">
-        <v>16669</v>
+        <v>11178919</v>
+      </c>
+      <c r="B84" s="17">
+        <v>16922</v>
       </c>
       <c r="C84" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="D84" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="E84" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="F84">
-        <v>58765</v>
+        <v>58811</v>
       </c>
       <c r="G84">
-        <v>569</v>
+        <v>439</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>11176700</v>
-      </c>
-      <c r="B85">
-        <v>16670</v>
+        <v>11176705</v>
+      </c>
+      <c r="B85" s="17">
+        <v>16678</v>
       </c>
       <c r="C85" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E85" t="s">
-        <v>157</v>
-      </c>
-      <c r="F85">
-        <v>58783</v>
-      </c>
-      <c r="G85">
-        <v>399</v>
+        <v>137</v>
+      </c>
+      <c r="F85" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>11176703</v>
-      </c>
-      <c r="B86">
-        <v>16673</v>
+        <v>11176712</v>
+      </c>
+      <c r="B86" s="17">
+        <v>16679</v>
       </c>
       <c r="C86" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E86" t="s">
-        <v>159</v>
-      </c>
-      <c r="F86">
-        <v>58797</v>
-      </c>
-      <c r="G86">
-        <v>369</v>
+        <v>139</v>
+      </c>
+      <c r="F86" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>11176704</v>
-      </c>
-      <c r="B87">
-        <v>16674</v>
+        <v>11178947</v>
+      </c>
+      <c r="B87" s="17">
+        <v>16914</v>
       </c>
       <c r="C87" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D87" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="E87" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="F87">
-        <v>58798</v>
+        <v>58795</v>
       </c>
       <c r="G87">
-        <v>499</v>
+        <v>899</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>11176722</v>
-      </c>
-      <c r="B88">
-        <v>16675</v>
+      <c r="A88" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88" s="17">
+        <v>16531</v>
       </c>
       <c r="C88" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D88" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="E88" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="F88">
-        <v>58799</v>
+        <v>58769</v>
       </c>
       <c r="G88">
-        <v>689</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>11176718</v>
-      </c>
-      <c r="B89">
-        <v>16676</v>
+      <c r="A89" t="s">
+        <v>70</v>
+      </c>
+      <c r="B89" s="17">
+        <v>16531</v>
       </c>
       <c r="C89" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="D89" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E89" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="F89">
-        <v>58800</v>
+        <v>58775</v>
       </c>
       <c r="G89">
-        <v>669</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>11176723</v>
-      </c>
-      <c r="B90">
-        <v>16677</v>
+      <c r="A90" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90" s="17">
+        <v>16532</v>
       </c>
       <c r="C90" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D90" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="F90">
-        <v>58801</v>
+        <v>58771</v>
       </c>
       <c r="G90">
-        <v>889</v>
+        <v>999</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>11176724</v>
-      </c>
-      <c r="B91">
-        <v>16672</v>
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" s="17">
+        <v>16532</v>
       </c>
       <c r="C91" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="D91" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="E91" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="F91">
-        <v>58763</v>
+        <v>58773</v>
       </c>
       <c r="G91">
-        <v>999</v>
+        <v>899</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>11176717</v>
-      </c>
-      <c r="B92">
-        <v>16671</v>
+        <v>11177964</v>
+      </c>
+      <c r="B92" s="17">
+        <v>16607</v>
       </c>
       <c r="C92" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D92" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E92" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="F92">
-        <v>58796</v>
+        <v>58785</v>
       </c>
       <c r="G92">
-        <v>489</v>
+        <v>669</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>11176716</v>
-      </c>
-      <c r="B93">
-        <v>16668</v>
+        <v>11177937</v>
+      </c>
+      <c r="B93" s="17">
+        <v>16611</v>
       </c>
       <c r="C93" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="D93" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="E93" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="F93">
-        <v>58781</v>
+        <v>58761</v>
       </c>
       <c r="G93">
-        <v>899</v>
+        <v>539</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>11176612</v>
-      </c>
-      <c r="B94">
-        <v>16608</v>
+        <v>11176721</v>
+      </c>
+      <c r="B94" s="17">
+        <v>16662</v>
       </c>
       <c r="C94" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="D94" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="E94" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="F94">
-        <v>52575</v>
+        <v>58779</v>
       </c>
       <c r="G94">
-        <v>659</v>
+        <v>969</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>11176610</v>
-      </c>
-      <c r="B95">
-        <v>16609</v>
+        <v>11176711</v>
+      </c>
+      <c r="B95" s="17">
+        <v>16669</v>
       </c>
       <c r="C95" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="E95" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="F95">
-        <v>52577</v>
+        <v>58765</v>
       </c>
       <c r="G95">
-        <v>717</v>
+        <v>569</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>11176710</v>
-      </c>
-      <c r="B96">
-        <v>16664</v>
+        <v>11176700</v>
+      </c>
+      <c r="B96" s="17">
+        <v>16670</v>
       </c>
       <c r="C96" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="D96" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="E96" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="F96">
-        <v>58791</v>
+        <v>58783</v>
       </c>
       <c r="G96">
-        <v>529</v>
+        <v>399</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>11176701</v>
-      </c>
-      <c r="B97">
-        <v>16665</v>
+        <v>11176703</v>
+      </c>
+      <c r="B97" s="17">
+        <v>16673</v>
       </c>
       <c r="C97" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="D97" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="E97" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="F97">
-        <v>58792</v>
+        <v>58797</v>
       </c>
       <c r="G97">
-        <v>489</v>
+        <v>369</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>11176702</v>
-      </c>
-      <c r="B98">
-        <v>16666</v>
+        <v>11176704</v>
+      </c>
+      <c r="B98" s="17">
+        <v>16674</v>
       </c>
       <c r="C98" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="D98" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="E98" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="F98">
-        <v>58793</v>
+        <v>58798</v>
       </c>
       <c r="G98">
-        <v>459</v>
+        <v>499</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>11176715</v>
-      </c>
-      <c r="B99">
-        <v>16667</v>
+        <v>11176722</v>
+      </c>
+      <c r="B99" s="17">
+        <v>16675</v>
       </c>
       <c r="C99" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="D99" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="E99" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="F99">
-        <v>58794</v>
+        <v>58799</v>
       </c>
       <c r="G99">
-        <v>679</v>
+        <v>689</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>11176699</v>
-      </c>
-      <c r="B100">
-        <v>16663</v>
+        <v>11176718</v>
+      </c>
+      <c r="B100" s="17">
+        <v>16676</v>
       </c>
       <c r="C100" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="D100" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="E100" t="s">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="F100">
-        <v>58767</v>
+        <v>58800</v>
       </c>
       <c r="G100">
-        <v>499</v>
+        <v>669</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>11177607</v>
-      </c>
-      <c r="B101">
-        <v>16680</v>
+        <v>11176723</v>
+      </c>
+      <c r="B101" s="17">
+        <v>16677</v>
       </c>
       <c r="C101" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="D101" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="E101" t="s">
-        <v>189</v>
-      </c>
-      <c r="F101" t="s">
-        <v>190</v>
+        <v>167</v>
+      </c>
+      <c r="F101">
+        <v>58801</v>
       </c>
       <c r="G101">
-        <v>32</v>
+        <v>889</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>70</v>
-      </c>
-      <c r="B102">
-        <v>16729</v>
+      <c r="A102">
+        <v>11176724</v>
+      </c>
+      <c r="B102" s="17">
+        <v>16672</v>
       </c>
       <c r="C102" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="D102" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="E102" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="F102">
-        <v>52617</v>
+        <v>58763</v>
       </c>
       <c r="G102">
-        <v>59</v>
+        <v>999</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>70</v>
-      </c>
-      <c r="B103">
-        <v>16771</v>
+      <c r="A103">
+        <v>11176717</v>
+      </c>
+      <c r="B103" s="17">
+        <v>16671</v>
       </c>
       <c r="C103" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="D103" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="E103" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="F103">
-        <v>52615</v>
+        <v>58796</v>
       </c>
       <c r="G103">
-        <v>109</v>
+        <v>489</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>11176714</v>
-      </c>
-      <c r="B104">
-        <v>16659</v>
+        <v>11176716</v>
+      </c>
+      <c r="B104" s="17">
+        <v>16668</v>
       </c>
       <c r="C104" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="D104" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="E104" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="F104">
-        <v>52609</v>
+        <v>58781</v>
       </c>
       <c r="G104">
-        <v>677</v>
+        <v>899</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>11176719</v>
-      </c>
-      <c r="B105">
-        <v>16660</v>
+        <v>11176612</v>
+      </c>
+      <c r="B105" s="17">
+        <v>16608</v>
       </c>
       <c r="C105" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="D105" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="E105" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="F105">
-        <v>52610</v>
+        <v>52575</v>
       </c>
       <c r="G105">
-        <v>739</v>
+        <v>659</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>11176708</v>
-      </c>
-      <c r="B106">
-        <v>16658</v>
+        <v>11176610</v>
+      </c>
+      <c r="B106" s="17">
+        <v>16609</v>
       </c>
       <c r="C106" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D106" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="E106" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="F106">
-        <v>52608</v>
+        <v>52577</v>
       </c>
       <c r="G106">
-        <v>567</v>
+        <v>717</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>11176720</v>
-      </c>
-      <c r="B107">
-        <v>16661</v>
+        <v>11176710</v>
+      </c>
+      <c r="B107" s="17">
+        <v>16664</v>
       </c>
       <c r="C107" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="D107" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="E107" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F107">
-        <v>52612</v>
+        <v>58791</v>
       </c>
       <c r="G107">
-        <v>839</v>
+        <v>529</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>11174775</v>
-      </c>
-      <c r="B108">
-        <v>16551</v>
+        <v>11176701</v>
+      </c>
+      <c r="B108" s="17">
+        <v>16665</v>
       </c>
       <c r="C108" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="D108" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="E108" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="F108">
-        <v>52596</v>
+        <v>58792</v>
       </c>
       <c r="G108">
-        <v>457</v>
+        <v>489</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>11177276</v>
-      </c>
-      <c r="B109">
-        <v>16559</v>
+        <v>11176702</v>
+      </c>
+      <c r="B109" s="17">
+        <v>16666</v>
       </c>
       <c r="C109" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="D109" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="E109" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="F109">
-        <v>52597</v>
+        <v>58793</v>
       </c>
       <c r="G109">
-        <v>689</v>
+        <v>459</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
-        <v>11174806</v>
-      </c>
-      <c r="B110">
-        <v>16557</v>
+        <v>11176715</v>
+      </c>
+      <c r="B110" s="17">
+        <v>16667</v>
       </c>
       <c r="C110" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="D110" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="E110" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="F110">
-        <v>52598</v>
+        <v>58794</v>
       </c>
       <c r="G110">
-        <v>729</v>
+        <v>679</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111">
-        <v>11174811</v>
-      </c>
-      <c r="B111">
-        <v>16546</v>
+        <v>11176699</v>
+      </c>
+      <c r="B111" s="17">
+        <v>16663</v>
       </c>
       <c r="C111" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="D111" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="E111" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="F111">
-        <v>52600</v>
+        <v>58767</v>
       </c>
       <c r="G111">
-        <v>839</v>
+        <v>499</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+      <c r="A112">
+        <v>11177607</v>
+      </c>
+      <c r="B112" s="17">
+        <v>16680</v>
+      </c>
+      <c r="C112" t="s">
+        <v>188</v>
+      </c>
+      <c r="D112" t="s">
+        <v>189</v>
+      </c>
+      <c r="E112" t="s">
+        <v>189</v>
+      </c>
+      <c r="F112" t="s">
+        <v>190</v>
+      </c>
+      <c r="G112">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>70</v>
       </c>
-      <c r="B112">
-        <v>16775</v>
-      </c>
-      <c r="C112" t="s">
-        <v>211</v>
-      </c>
-      <c r="D112" t="s">
-        <v>212</v>
-      </c>
-      <c r="E112" t="s">
-        <v>212</v>
-      </c>
-      <c r="F112">
-        <v>52606</v>
-      </c>
-      <c r="G112">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <v>11174791</v>
-      </c>
-      <c r="B113">
-        <v>16572</v>
+      <c r="B113" s="17">
+        <v>16729</v>
       </c>
       <c r="C113" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="D113" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="E113" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="F113">
-        <v>52582</v>
+        <v>52617</v>
       </c>
       <c r="G113">
         <v>59</v>
@@ -14722,20 +14740,20 @@
       <c r="A114" t="s">
         <v>70</v>
       </c>
-      <c r="B114">
-        <v>16770</v>
+      <c r="B114" s="17">
+        <v>16771</v>
       </c>
       <c r="C114" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="D114" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="E114" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="F114">
-        <v>52616</v>
+        <v>52615</v>
       </c>
       <c r="G114">
         <v>109</v>
@@ -14743,415 +14761,668 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
-        <v>11174803</v>
-      </c>
-      <c r="B115">
-        <v>16549</v>
+        <v>11176714</v>
+      </c>
+      <c r="B115" s="17">
+        <v>16659</v>
       </c>
       <c r="C115" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="D115" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="E115" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="F115">
-        <v>52591</v>
+        <v>52609</v>
       </c>
       <c r="G115">
-        <v>1399</v>
+        <v>677</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
-        <v>11174810</v>
-      </c>
-      <c r="B116">
-        <v>16555</v>
+        <v>11176719</v>
+      </c>
+      <c r="B116" s="17">
+        <v>16660</v>
       </c>
       <c r="C116" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="D116" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="E116" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="F116">
-        <v>52595</v>
+        <v>52610</v>
       </c>
       <c r="G116">
-        <v>999</v>
+        <v>739</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117">
-        <v>11174776</v>
-      </c>
-      <c r="B117">
-        <v>16550</v>
+        <v>11176708</v>
+      </c>
+      <c r="B117" s="17">
+        <v>16658</v>
       </c>
       <c r="C117" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="D117" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="E117" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="F117">
-        <v>52585</v>
+        <v>52608</v>
       </c>
       <c r="G117">
-        <v>429</v>
+        <v>567</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
-        <v>11174801</v>
-      </c>
-      <c r="B118">
-        <v>16548</v>
+        <v>11176720</v>
+      </c>
+      <c r="B118" s="17">
+        <v>16661</v>
       </c>
       <c r="C118" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="D118" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="E118" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="F118">
-        <v>52586</v>
+        <v>52612</v>
       </c>
       <c r="G118">
-        <v>689</v>
+        <v>839</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
-        <v>11177275</v>
-      </c>
-      <c r="B119">
-        <v>16558</v>
+        <v>11174775</v>
+      </c>
+      <c r="B119" s="17">
+        <v>16551</v>
       </c>
       <c r="C119" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="D119" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="E119" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="F119">
-        <v>52587</v>
+        <v>52596</v>
       </c>
       <c r="G119">
-        <v>689</v>
+        <v>457</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120">
-        <v>11175037</v>
-      </c>
-      <c r="B120">
-        <v>16573</v>
+        <v>11177276</v>
+      </c>
+      <c r="B120" s="17">
+        <v>16559</v>
       </c>
       <c r="C120" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="D120" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="E120" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="F120">
-        <v>52588</v>
+        <v>52597</v>
       </c>
       <c r="G120">
-        <v>444</v>
+        <v>689</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
-        <v>11174795</v>
-      </c>
-      <c r="B121">
-        <v>16543</v>
+        <v>11174806</v>
+      </c>
+      <c r="B121" s="17">
+        <v>16557</v>
       </c>
       <c r="C121" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="D121" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="E121" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="F121">
-        <v>52589</v>
+        <v>52598</v>
       </c>
       <c r="G121">
-        <v>549</v>
+        <v>729</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+      <c r="A122">
+        <v>11174811</v>
+      </c>
+      <c r="B122" s="17">
+        <v>16546</v>
+      </c>
+      <c r="C122" t="s">
+        <v>209</v>
+      </c>
+      <c r="D122" t="s">
+        <v>210</v>
+      </c>
+      <c r="E122" t="s">
+        <v>210</v>
+      </c>
+      <c r="F122">
+        <v>52600</v>
+      </c>
+      <c r="G122">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
         <v>70</v>
       </c>
-      <c r="B122">
-        <v>16769</v>
-      </c>
-      <c r="C122" t="s">
-        <v>231</v>
-      </c>
-      <c r="D122" t="s">
-        <v>232</v>
-      </c>
-      <c r="E122" t="s">
-        <v>232</v>
-      </c>
-      <c r="F122">
-        <v>52614</v>
-      </c>
-      <c r="G122">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123">
-        <v>11174779</v>
-      </c>
-      <c r="B123">
-        <v>16540</v>
+      <c r="B123" s="17">
+        <v>16775</v>
       </c>
       <c r="C123" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="D123" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="E123" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="F123">
-        <v>52584</v>
+        <v>52606</v>
       </c>
       <c r="G123">
-        <v>567</v>
+        <v>169</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124">
-        <v>11174804</v>
-      </c>
-      <c r="B124">
-        <v>16541</v>
+        <v>11174791</v>
+      </c>
+      <c r="B124" s="17">
+        <v>16572</v>
       </c>
       <c r="C124" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="D124" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E124" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="F124">
-        <v>52593</v>
+        <v>52582</v>
       </c>
       <c r="G124">
-        <v>889</v>
+        <v>59</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125">
-        <v>11174798</v>
-      </c>
-      <c r="B125">
-        <v>16552</v>
+      <c r="A125" t="s">
+        <v>70</v>
+      </c>
+      <c r="B125" s="17">
+        <v>16770</v>
       </c>
       <c r="C125" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="D125" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="E125" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="F125">
-        <v>52578</v>
+        <v>52616</v>
       </c>
       <c r="G125">
-        <v>649</v>
+        <v>109</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
-        <v>11174808</v>
-      </c>
-      <c r="B126">
-        <v>16545</v>
+        <v>11174803</v>
+      </c>
+      <c r="B126" s="17">
+        <v>16549</v>
       </c>
       <c r="C126" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="D126" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="E126" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="F126">
-        <v>52579</v>
+        <v>52591</v>
       </c>
       <c r="G126">
-        <v>749</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
-        <v>11177274</v>
-      </c>
-      <c r="B127">
-        <v>16547</v>
+        <v>11174810</v>
+      </c>
+      <c r="B127" s="17">
+        <v>16555</v>
       </c>
       <c r="C127" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="D127" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="E127" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="F127">
-        <v>52580</v>
+        <v>52595</v>
       </c>
       <c r="G127">
-        <v>669</v>
+        <v>999</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128">
-        <v>11174800</v>
-      </c>
-      <c r="B128">
-        <v>16553</v>
+        <v>11174776</v>
+      </c>
+      <c r="B128" s="17">
+        <v>16550</v>
       </c>
       <c r="C128" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="D128" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="E128" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="F128">
-        <v>52581</v>
+        <v>52585</v>
       </c>
       <c r="G128">
-        <v>669</v>
+        <v>429</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
-        <v>11174807</v>
-      </c>
-      <c r="B129">
-        <v>16554</v>
+        <v>11174801</v>
+      </c>
+      <c r="B129" s="17">
+        <v>16548</v>
       </c>
       <c r="C129" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="D129" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="E129" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="F129">
-        <v>52601</v>
+        <v>52586</v>
       </c>
       <c r="G129">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
-        <v>11177277</v>
-      </c>
-      <c r="B130">
-        <v>16544</v>
+        <v>11177275</v>
+      </c>
+      <c r="B130" s="17">
+        <v>16558</v>
       </c>
       <c r="C130" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="D130" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="E130" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="F130">
-        <v>52602</v>
+        <v>52587</v>
       </c>
       <c r="G130">
-        <v>489</v>
+        <v>689</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131">
-        <v>11174790</v>
-      </c>
-      <c r="B131">
-        <v>16542</v>
+        <v>11175037</v>
+      </c>
+      <c r="B131" s="17">
+        <v>16573</v>
       </c>
       <c r="C131" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="D131" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="E131" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="F131">
-        <v>52603</v>
+        <v>52588</v>
       </c>
       <c r="G131">
-        <v>349</v>
+        <v>444</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132">
+        <v>11174795</v>
+      </c>
+      <c r="B132" s="17">
+        <v>16543</v>
+      </c>
+      <c r="C132" t="s">
+        <v>229</v>
+      </c>
+      <c r="D132" t="s">
+        <v>230</v>
+      </c>
+      <c r="E132" t="s">
+        <v>230</v>
+      </c>
+      <c r="F132">
+        <v>52589</v>
+      </c>
+      <c r="G132">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>70</v>
+      </c>
+      <c r="B133" s="17">
+        <v>16769</v>
+      </c>
+      <c r="C133" t="s">
+        <v>231</v>
+      </c>
+      <c r="D133" t="s">
+        <v>232</v>
+      </c>
+      <c r="E133" t="s">
+        <v>232</v>
+      </c>
+      <c r="F133">
+        <v>52614</v>
+      </c>
+      <c r="G133">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>11174779</v>
+      </c>
+      <c r="B134" s="17">
+        <v>16540</v>
+      </c>
+      <c r="C134" t="s">
+        <v>233</v>
+      </c>
+      <c r="D134" t="s">
+        <v>234</v>
+      </c>
+      <c r="E134" t="s">
+        <v>234</v>
+      </c>
+      <c r="F134">
+        <v>52584</v>
+      </c>
+      <c r="G134">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>11174804</v>
+      </c>
+      <c r="B135" s="17">
+        <v>16541</v>
+      </c>
+      <c r="C135" t="s">
+        <v>235</v>
+      </c>
+      <c r="D135" t="s">
+        <v>236</v>
+      </c>
+      <c r="E135" t="s">
+        <v>236</v>
+      </c>
+      <c r="F135">
+        <v>52593</v>
+      </c>
+      <c r="G135">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>11174798</v>
+      </c>
+      <c r="B136" s="17">
+        <v>16552</v>
+      </c>
+      <c r="C136" t="s">
+        <v>237</v>
+      </c>
+      <c r="D136" t="s">
+        <v>238</v>
+      </c>
+      <c r="E136" t="s">
+        <v>238</v>
+      </c>
+      <c r="F136">
+        <v>52578</v>
+      </c>
+      <c r="G136">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>11174808</v>
+      </c>
+      <c r="B137" s="17">
+        <v>16545</v>
+      </c>
+      <c r="C137" t="s">
+        <v>239</v>
+      </c>
+      <c r="D137" t="s">
+        <v>240</v>
+      </c>
+      <c r="E137" t="s">
+        <v>240</v>
+      </c>
+      <c r="F137">
+        <v>52579</v>
+      </c>
+      <c r="G137">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>11177274</v>
+      </c>
+      <c r="B138" s="17">
+        <v>16547</v>
+      </c>
+      <c r="C138" t="s">
+        <v>241</v>
+      </c>
+      <c r="D138" t="s">
+        <v>242</v>
+      </c>
+      <c r="E138" t="s">
+        <v>242</v>
+      </c>
+      <c r="F138">
+        <v>52580</v>
+      </c>
+      <c r="G138">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>11174800</v>
+      </c>
+      <c r="B139" s="17">
+        <v>16553</v>
+      </c>
+      <c r="C139" t="s">
+        <v>243</v>
+      </c>
+      <c r="D139" t="s">
+        <v>244</v>
+      </c>
+      <c r="E139" t="s">
+        <v>244</v>
+      </c>
+      <c r="F139">
+        <v>52581</v>
+      </c>
+      <c r="G139">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>11174807</v>
+      </c>
+      <c r="B140" s="17">
+        <v>16554</v>
+      </c>
+      <c r="C140" t="s">
+        <v>245</v>
+      </c>
+      <c r="D140" t="s">
+        <v>246</v>
+      </c>
+      <c r="E140" t="s">
+        <v>246</v>
+      </c>
+      <c r="F140">
+        <v>52601</v>
+      </c>
+      <c r="G140">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>11177277</v>
+      </c>
+      <c r="B141" s="17">
+        <v>16544</v>
+      </c>
+      <c r="C141" t="s">
+        <v>247</v>
+      </c>
+      <c r="D141" t="s">
+        <v>248</v>
+      </c>
+      <c r="E141" t="s">
+        <v>248</v>
+      </c>
+      <c r="F141">
+        <v>52602</v>
+      </c>
+      <c r="G141">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>11174790</v>
+      </c>
+      <c r="B142" s="17">
+        <v>16542</v>
+      </c>
+      <c r="C142" t="s">
+        <v>249</v>
+      </c>
+      <c r="D142" t="s">
+        <v>250</v>
+      </c>
+      <c r="E142" t="s">
+        <v>250</v>
+      </c>
+      <c r="F142">
+        <v>52603</v>
+      </c>
+      <c r="G142">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143">
         <v>11174799</v>
       </c>
-      <c r="B132">
+      <c r="B143" s="17">
         <v>16556</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C143" t="s">
         <v>251</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D143" t="s">
         <v>252</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E143" t="s">
         <v>252</v>
       </c>
-      <c r="F132">
+      <c r="F143">
         <v>52604</v>
       </c>
-      <c r="G132">
+      <c r="G143">
         <v>609</v>
       </c>
     </row>
